--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="2130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="2180">
   <si>
     <r>
       <rPr>
@@ -2975,6 +2975,75 @@
     <t>めぐまれる</t>
   </si>
   <si>
+    <t>工作，担任，尽力</t>
+  </si>
+  <si>
+    <t>DolphinDB株式会社に3年勤めている</t>
+  </si>
+  <si>
+    <t>在DolphinDB公司工作三年</t>
+  </si>
+  <si>
+    <t>勤める</t>
+  </si>
+  <si>
+    <t>つとめる</t>
+  </si>
+  <si>
+    <t>努める</t>
+  </si>
+  <si>
+    <t>开辟，创造</t>
+  </si>
+  <si>
+    <t>新しい境地を切り開く「きょうち」</t>
+  </si>
+  <si>
+    <t>开辟一个新天地</t>
+  </si>
+  <si>
+    <t>切り開く</t>
+  </si>
+  <si>
+    <t>きりひらく</t>
+  </si>
+  <si>
+    <t>自己の未来を切り開く</t>
+  </si>
+  <si>
+    <t>创造自己的未来</t>
+  </si>
+  <si>
+    <t>切り拓く</t>
+  </si>
+  <si>
+    <t>放一边，别管</t>
+  </si>
+  <si>
+    <t>放っておいたほうがいい</t>
+  </si>
+  <si>
+    <t>Let it go</t>
+  </si>
+  <si>
+    <t>放っておく</t>
+  </si>
+  <si>
+    <t>ほうっておく</t>
+  </si>
+  <si>
+    <t>放っておいて</t>
+  </si>
+  <si>
+    <t>ほうっておいて</t>
+  </si>
+  <si>
+    <t>放っておいた</t>
+  </si>
+  <si>
+    <t>ほうっておいた</t>
+  </si>
+  <si>
     <t>着く</t>
   </si>
   <si>
@@ -4177,12 +4246,6 @@
     <t>たれる</t>
   </si>
   <si>
-    <t>垂れています</t>
-  </si>
-  <si>
-    <t>たれています</t>
-  </si>
-  <si>
     <t>垂れたない</t>
   </si>
   <si>
@@ -4210,6 +4273,33 @@
     <t>さえずる</t>
   </si>
   <si>
+    <t>生锈</t>
+  </si>
+  <si>
+    <t>錆びる</t>
+  </si>
+  <si>
+    <t>さびる</t>
+  </si>
+  <si>
+    <t>錆びらない</t>
+  </si>
+  <si>
+    <t>さびらない</t>
+  </si>
+  <si>
+    <t>錆びて</t>
+  </si>
+  <si>
+    <t>さびて</t>
+  </si>
+  <si>
+    <t>錆びた</t>
+  </si>
+  <si>
+    <t>さびた</t>
+  </si>
+  <si>
     <t>誓う</t>
   </si>
   <si>
@@ -4964,6 +5054,66 @@
   </si>
   <si>
     <t>こいする</t>
+  </si>
+  <si>
+    <t>拯救</t>
+  </si>
+  <si>
+    <t>救う</t>
+  </si>
+  <si>
+    <t>すくう</t>
+  </si>
+  <si>
+    <t>救わない</t>
+  </si>
+  <si>
+    <t>すくわない</t>
+  </si>
+  <si>
+    <t>救って</t>
+  </si>
+  <si>
+    <t>すくって</t>
+  </si>
+  <si>
+    <t>救った</t>
+  </si>
+  <si>
+    <t>すくった</t>
+  </si>
+  <si>
+    <t>借助，借用</t>
+  </si>
+  <si>
+    <t>借りたお金はもう少し待ちて下さい</t>
+  </si>
+  <si>
+    <t>借的钱请你再缓几天</t>
+  </si>
+  <si>
+    <t>借りる</t>
+  </si>
+  <si>
+    <t>かりる</t>
+  </si>
+  <si>
+    <t>借りらない</t>
+  </si>
+  <si>
+    <t>かりらない</t>
+  </si>
+  <si>
+    <t>借りて</t>
+  </si>
+  <si>
+    <t>かりて</t>
+  </si>
+  <si>
+    <t>借りた</t>
+  </si>
+  <si>
+    <t>かりた</t>
   </si>
   <si>
     <t>支える</t>
@@ -9467,7 +9617,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE83"/>
+  <dimension ref="A1:AE88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="3" max="3" width="67.7777777777778" customWidth="1"/>
@@ -11866,7 +12016,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="81" ht="18" spans="1:8">
+    <row r="81" ht="18" spans="1:16">
       <c r="A81" s="2" t="s">
         <v>875</v>
       </c>
@@ -11886,7 +12036,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="82" ht="18" spans="1:8">
+    <row r="82" ht="18" spans="1:16">
       <c r="B82" s="13" t="s">
         <v>878</v>
       </c>
@@ -11903,7 +12053,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="83" customFormat="1" ht="18" spans="1:8">
+    <row r="83" customFormat="1" ht="18" spans="1:16">
       <c r="B83" t="s">
         <v>881</v>
       </c>
@@ -11924,6 +12074,127 @@
       </c>
       <c r="H83" t="s">
         <v>885</v>
+      </c>
+    </row>
+    <row r="84" ht="18" spans="1:16">
+      <c r="B84" t="s">
+        <v>886</v>
+      </c>
+      <c r="C84" t="s">
+        <v>887</v>
+      </c>
+      <c r="D84" t="s">
+        <v>888</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84" t="s">
+        <v>889</v>
+      </c>
+      <c r="H84" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="85" ht="18" spans="1:16">
+      <c r="B85" t="s">
+        <v>886</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>891</v>
+      </c>
+      <c r="H85" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="86" ht="18" spans="1:16">
+      <c r="B86" t="s">
+        <v>892</v>
+      </c>
+      <c r="C86" t="s">
+        <v>893</v>
+      </c>
+      <c r="D86" t="s">
+        <v>894</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="s">
+        <v>895</v>
+      </c>
+      <c r="H86" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="87" ht="18" spans="1:16">
+      <c r="B87" t="s">
+        <v>892</v>
+      </c>
+      <c r="C87" t="s">
+        <v>897</v>
+      </c>
+      <c r="D87" t="s">
+        <v>898</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>899</v>
+      </c>
+      <c r="H87" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="88" ht="18" spans="1:16">
+      <c r="B88" t="s">
+        <v>900</v>
+      </c>
+      <c r="C88" t="s">
+        <v>901</v>
+      </c>
+      <c r="D88" t="s">
+        <v>902</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>903</v>
+      </c>
+      <c r="H88" t="s">
+        <v>904</v>
+      </c>
+      <c r="M88" t="s">
+        <v>905</v>
+      </c>
+      <c r="N88" t="s">
+        <v>906</v>
+      </c>
+      <c r="O88" t="s">
+        <v>907</v>
+      </c>
+      <c r="P88" t="s">
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -12105,28 +12376,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>886</v>
+        <v>909</v>
       </c>
       <c r="H3" t="s">
-        <v>887</v>
+        <v>910</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>888</v>
+        <v>911</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>892</v>
+        <v>915</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>893</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" ht="31.2" customHeight="1" spans="2:31">
@@ -12137,7 +12408,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>894</v>
+        <v>917</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="2" t="s">
@@ -12155,73 +12426,73 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>895</v>
+        <v>918</v>
       </c>
       <c r="F5" t="s">
-        <v>896</v>
+        <v>919</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>897</v>
+        <v>920</v>
       </c>
       <c r="H5" t="s">
-        <v>898</v>
+        <v>921</v>
       </c>
       <c r="I5" t="s">
-        <v>899</v>
+        <v>922</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>900</v>
+        <v>923</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>901</v>
+        <v>924</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>906</v>
+        <v>929</v>
       </c>
     </row>
     <row r="6" ht="18" spans="2:31">
       <c r="C6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>907</v>
+        <v>930</v>
       </c>
       <c r="H6" t="s">
-        <v>908</v>
+        <v>931</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>909</v>
+        <v>932</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>912</v>
+        <v>935</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>914</v>
+        <v>937</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>550</v>
@@ -12230,16 +12501,16 @@
         <v>551</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>916</v>
+        <v>939</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>917</v>
+        <v>940</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>918</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7" ht="18" spans="2:31">
@@ -12250,7 +12521,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>919</v>
+        <v>942</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>728</v>
@@ -12259,16 +12530,16 @@
         <v>729</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>920</v>
+        <v>943</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>921</v>
+        <v>944</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>922</v>
+        <v>945</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>923</v>
+        <v>946</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>730</v>
@@ -12297,16 +12568,16 @@
         <v>729</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>924</v>
+        <v>947</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>921</v>
+        <v>944</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>925</v>
+        <v>948</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>923</v>
+        <v>946</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>735</v>
@@ -12329,37 +12600,37 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>926</v>
+        <v>949</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>927</v>
+        <v>950</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>928</v>
+        <v>951</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>929</v>
+        <v>952</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>930</v>
+        <v>953</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>931</v>
+        <v>954</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>932</v>
+        <v>955</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>934</v>
+        <v>957</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>935</v>
+        <v>958</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>936</v>
+        <v>959</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:31">
@@ -12370,38 +12641,38 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>937</v>
+        <v>960</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>940</v>
+        <v>963</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>941</v>
+        <v>964</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>944</v>
+        <v>967</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>945</v>
+        <v>968</v>
       </c>
       <c r="O10" t="s">
-        <v>946</v>
+        <v>969</v>
       </c>
       <c r="P10" t="s">
-        <v>947</v>
+        <v>970</v>
       </c>
     </row>
     <row r="11" ht="18" spans="2:31">
@@ -12412,16 +12683,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>948</v>
+        <v>971</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>949</v>
+        <v>972</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>950</v>
+        <v>973</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>951</v>
+        <v>974</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -12432,7 +12703,7 @@
     </row>
     <row r="12" ht="18" spans="2:31">
       <c r="B12" t="s">
-        <v>952</v>
+        <v>975</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>49</v>
@@ -12443,25 +12714,25 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>954</v>
+        <v>977</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>955</v>
+        <v>978</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>956</v>
+        <v>979</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" spans="2:31">
       <c r="B13" t="s">
-        <v>957</v>
+        <v>980</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>49</v>
@@ -12470,39 +12741,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>958</v>
+        <v>981</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>959</v>
+        <v>982</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>962</v>
+        <v>985</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>963</v>
+        <v>986</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>964</v>
+        <v>987</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>966</v>
+        <v>989</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>967</v>
+        <v>990</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="18" spans="2:31">
       <c r="B14" t="s">
-        <v>968</v>
+        <v>991</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>222</v>
@@ -12511,21 +12782,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>969</v>
+        <v>992</v>
       </c>
       <c r="F14" t="s">
-        <v>970</v>
+        <v>993</v>
       </c>
       <c r="G14" t="s">
-        <v>971</v>
+        <v>994</v>
       </c>
       <c r="H14" t="s">
-        <v>972</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" ht="18" spans="2:31">
       <c r="B15" t="s">
-        <v>973</v>
+        <v>996</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>49</v>
@@ -12534,18 +12805,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>974</v>
+        <v>997</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>975</v>
+        <v>998</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>976</v>
+        <v>999</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>977</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -12554,7 +12825,7 @@
     </row>
     <row r="16" ht="18" spans="2:31">
       <c r="B16" t="s">
-        <v>978</v>
+        <v>1001</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>49</v>
@@ -12563,10 +12834,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>374</v>
@@ -12577,7 +12848,7 @@
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="B17" t="s">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>49</v>
@@ -12586,19 +12857,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>982</v>
+        <v>1005</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>983</v>
+        <v>1006</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="B18" t="s">
-        <v>985</v>
+        <v>1008</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>49</v>
@@ -12609,15 +12880,15 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>986</v>
+        <v>1009</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>987</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>988</v>
+        <v>1011</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>49</v>
@@ -12628,15 +12899,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>989</v>
+        <v>1012</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>990</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>991</v>
+        <v>1014</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>49</v>
@@ -12645,10 +12916,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>992</v>
+        <v>1015</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>993</v>
+        <v>1016</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>347</v>
@@ -12665,21 +12936,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>995</v>
+        <v>1018</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>996</v>
+        <v>1019</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>997</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="B22" t="s">
-        <v>998</v>
+        <v>1021</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -12688,24 +12959,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>999</v>
+        <v>1022</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1000</v>
+        <v>1023</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1002</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>1003</v>
+        <v>1026</v>
       </c>
       <c r="B23" t="s">
-        <v>1004</v>
+        <v>1027</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -12716,30 +12987,30 @@
       <c r="E23" s="2"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1006</v>
+        <v>1029</v>
       </c>
       <c r="M23" t="s">
-        <v>1007</v>
+        <v>1030</v>
       </c>
       <c r="N23" t="s">
-        <v>1008</v>
+        <v>1031</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1009</v>
+        <v>1032</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1010</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="B24" t="s">
-        <v>1004</v>
+        <v>1027</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>49</v>
@@ -12750,30 +13021,30 @@
       <c r="E24" s="2"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2" t="s">
-        <v>1003</v>
+        <v>1026</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1011</v>
+        <v>1034</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1012</v>
+        <v>1035</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1013</v>
+        <v>1036</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1015</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="B25" t="s">
-        <v>1016</v>
+        <v>1039</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>49</v>
@@ -12782,28 +13053,28 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1017</v>
+        <v>1040</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1018</v>
+        <v>1041</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1019</v>
+        <v>1042</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1020</v>
+        <v>1043</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1022</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>1023</v>
+        <v>1046</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>49</v>
@@ -12812,27 +13083,27 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1024</v>
+        <v>1047</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1025</v>
+        <v>1048</v>
       </c>
       <c r="M26" t="s">
-        <v>1026</v>
+        <v>1049</v>
       </c>
       <c r="N26" t="s">
-        <v>1027</v>
+        <v>1050</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1029</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1030</v>
+        <v>1053</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -12841,21 +13112,21 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1031</v>
+        <v>1054</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1032</v>
+        <v>1055</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1033</v>
+        <v>1056</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1034</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1035</v>
+        <v>1058</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>49</v>
@@ -12864,33 +13135,33 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1036</v>
+        <v>1059</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1037</v>
+        <v>1060</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1038</v>
+        <v>1061</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1039</v>
+        <v>1062</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1040</v>
+        <v>1063</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1041</v>
+        <v>1064</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1042</v>
+        <v>1065</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1043</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1044</v>
+        <v>1067</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>49</v>
@@ -12899,39 +13170,39 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1045</v>
+        <v>1068</v>
       </c>
       <c r="F29" t="s">
-        <v>1046</v>
+        <v>1069</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1047</v>
+        <v>1070</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1048</v>
+        <v>1071</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1049</v>
+        <v>1072</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1050</v>
+        <v>1073</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1051</v>
+        <v>1074</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1052</v>
+        <v>1075</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1054</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1055</v>
+        <v>1078</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>222</v>
@@ -12940,21 +13211,21 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1056</v>
+        <v>1079</v>
       </c>
       <c r="F30" t="s">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1058</v>
+        <v>1081</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1059</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1060</v>
+        <v>1083</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>49</v>
@@ -12963,15 +13234,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1061</v>
+        <v>1084</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1062</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>49</v>
@@ -12980,33 +13251,33 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1064</v>
+        <v>1087</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1065</v>
+        <v>1088</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1066</v>
+        <v>1089</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1067</v>
+        <v>1090</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1068</v>
+        <v>1091</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1069</v>
+        <v>1092</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1070</v>
+        <v>1093</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1071</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1072</v>
+        <v>1095</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -13015,39 +13286,39 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1073</v>
+        <v>1096</v>
       </c>
       <c r="F33" t="s">
-        <v>1074</v>
+        <v>1097</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1075</v>
+        <v>1098</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1076</v>
+        <v>1099</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1077</v>
+        <v>1100</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1078</v>
+        <v>1101</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1079</v>
+        <v>1102</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1080</v>
+        <v>1103</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1081</v>
+        <v>1104</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1082</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1083</v>
+        <v>1106</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>49</v>
@@ -13056,33 +13327,33 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1084</v>
+        <v>1107</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1085</v>
+        <v>1108</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1086</v>
+        <v>1109</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1087</v>
+        <v>1110</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1088</v>
+        <v>1111</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1089</v>
+        <v>1112</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1090</v>
+        <v>1113</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1091</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1092</v>
+        <v>1115</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>49</v>
@@ -13091,33 +13362,33 @@
         <v>1</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1093</v>
+        <v>1116</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1094</v>
+        <v>1117</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>1095</v>
+        <v>1118</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1096</v>
+        <v>1119</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1097</v>
+        <v>1120</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1098</v>
+        <v>1121</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1099</v>
+        <v>1122</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1100</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1101</v>
+        <v>1124</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>49</v>
@@ -13126,39 +13397,39 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>1102</v>
+        <v>1125</v>
       </c>
       <c r="F36" t="s">
-        <v>1103</v>
+        <v>1126</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1104</v>
+        <v>1127</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1105</v>
+        <v>1128</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1106</v>
+        <v>1129</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1107</v>
+        <v>1130</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1108</v>
+        <v>1131</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1109</v>
+        <v>1132</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1110</v>
+        <v>1133</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1111</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1092</v>
+        <v>1115</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
@@ -13167,33 +13438,33 @@
         <v>1</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1112</v>
+        <v>1135</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1113</v>
+        <v>1136</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1114</v>
+        <v>1137</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1115</v>
+        <v>1138</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1116</v>
+        <v>1139</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1117</v>
+        <v>1140</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1118</v>
+        <v>1141</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1119</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1120</v>
+        <v>1143</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>815</v>
@@ -13202,16 +13473,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>1121</v>
+        <v>1144</v>
       </c>
       <c r="F38" t="s">
-        <v>1122</v>
+        <v>1145</v>
       </c>
       <c r="G38" t="s">
-        <v>1123</v>
+        <v>1146</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1124</v>
+        <v>1147</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -13222,10 +13493,10 @@
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="A39" t="s">
-        <v>1125</v>
+        <v>1148</v>
       </c>
       <c r="B39" t="s">
-        <v>1126</v>
+        <v>1149</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>49</v>
@@ -13237,30 +13508,30 @@
         <v>701</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1127</v>
+        <v>1150</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>1128</v>
+        <v>1151</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1129</v>
+        <v>1152</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1130</v>
+        <v>1153</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1131</v>
+        <v>1154</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1132</v>
+        <v>1155</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1133</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1134</v>
+        <v>1157</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>49</v>
@@ -13269,10 +13540,10 @@
         <v>2</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1135</v>
+        <v>1158</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>1136</v>
+        <v>1159</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -13283,10 +13554,10 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1137</v>
+        <v>1160</v>
       </c>
       <c r="B41" t="s">
-        <v>1138</v>
+        <v>1161</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>49</v>
@@ -13295,18 +13566,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1139</v>
+        <v>1162</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1140</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1139</v>
+        <v>1162</v>
       </c>
       <c r="B42" t="s">
-        <v>1141</v>
+        <v>1164</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -13315,10 +13586,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1137</v>
+        <v>1160</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1142</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
@@ -13329,10 +13600,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1143</v>
+        <v>1166</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1142</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
@@ -13343,33 +13614,33 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1144</v>
+        <v>1167</v>
       </c>
       <c r="F44" t="s">
-        <v>1145</v>
+        <v>1168</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1147</v>
+        <v>1170</v>
       </c>
       <c r="I44" t="s">
-        <v>1147</v>
+        <v>1170</v>
       </c>
       <c r="K44" t="s">
-        <v>1148</v>
+        <v>1171</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1149</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>1150</v>
+        <v>1173</v>
       </c>
       <c r="B45" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>49</v>
@@ -13378,34 +13649,34 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1152</v>
+        <v>1175</v>
       </c>
       <c r="F45" t="s">
-        <v>1153</v>
+        <v>1176</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1150</v>
+        <v>1173</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1154</v>
+        <v>1177</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1155</v>
+        <v>1178</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1156</v>
+        <v>1179</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1157</v>
+        <v>1180</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1158</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" t="s">
-        <v>1159</v>
+        <v>1182</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -13414,33 +13685,33 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1160</v>
+        <v>1183</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1161</v>
+        <v>1184</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1162</v>
+        <v>1185</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>1163</v>
+        <v>1186</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1164</v>
+        <v>1187</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1165</v>
+        <v>1188</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1166</v>
+        <v>1189</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1167</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="B47" t="s">
-        <v>1168</v>
+        <v>1191</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>49</v>
@@ -13449,15 +13720,15 @@
         <v>2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1169</v>
+        <v>1192</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1170</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1171</v>
+        <v>1194</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>49</v>
@@ -13466,30 +13737,30 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1172</v>
+        <v>1195</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1173</v>
+        <v>1196</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1174</v>
+        <v>1197</v>
       </c>
       <c r="N48" t="s">
-        <v>1175</v>
+        <v>1198</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1176</v>
+        <v>1199</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1177</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="B49" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>815</v>
@@ -13498,33 +13769,33 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1181</v>
+        <v>1204</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1185</v>
+        <v>1208</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1185</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="B50" t="s">
-        <v>1186</v>
+        <v>1209</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>49</v>
@@ -13533,36 +13804,36 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>1187</v>
+        <v>1210</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1188</v>
+        <v>1211</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1189</v>
+        <v>1212</v>
       </c>
       <c r="K50" t="s">
-        <v>1190</v>
+        <v>1213</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1191</v>
+        <v>1214</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1192</v>
+        <v>1215</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1194</v>
+        <v>1217</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1195</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="B51" t="s">
-        <v>1196</v>
+        <v>1219</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>222</v>
@@ -13571,21 +13842,21 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1197</v>
+        <v>1220</v>
       </c>
       <c r="F51" t="s">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1199</v>
+        <v>1222</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1200</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="B52" t="s">
-        <v>1196</v>
+        <v>1219</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -13594,21 +13865,21 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>1201</v>
+        <v>1224</v>
       </c>
       <c r="F52" t="s">
-        <v>1202</v>
+        <v>1225</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1203</v>
+        <v>1226</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1204</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="B53" t="s">
-        <v>1205</v>
+        <v>1228</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>49</v>
@@ -13617,33 +13888,33 @@
         <v>1</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1206</v>
+        <v>1229</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1207</v>
+        <v>1230</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>1208</v>
+        <v>1231</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>1209</v>
+        <v>1232</v>
       </c>
       <c r="M53" t="s">
-        <v>1210</v>
+        <v>1233</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1211</v>
+        <v>1234</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>1212</v>
+        <v>1235</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>1213</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="B54" t="s">
-        <v>1214</v>
+        <v>1237</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>815</v>
@@ -13652,33 +13923,33 @@
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1215</v>
+        <v>1238</v>
       </c>
       <c r="F54" t="s">
-        <v>1216</v>
+        <v>1239</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1217</v>
+        <v>1240</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1218</v>
+        <v>1241</v>
       </c>
       <c r="M54" t="s">
-        <v>1219</v>
+        <v>1242</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1220</v>
+        <v>1243</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1222</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="B55" t="s">
-        <v>1223</v>
+        <v>1246</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>49</v>
@@ -13687,10 +13958,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>1224</v>
+        <v>1247</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1225</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:16">
@@ -13701,30 +13972,30 @@
         <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1226</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="s">
-        <v>1227</v>
+        <v>1250</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1228</v>
+        <v>1251</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1229</v>
+        <v>1252</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1230</v>
+        <v>1253</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1231</v>
+        <v>1254</v>
       </c>
       <c r="O56" t="s">
-        <v>1232</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="B57" t="s">
-        <v>1233</v>
+        <v>1256</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>49</v>
@@ -13733,39 +14004,39 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1234</v>
+        <v>1257</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1235</v>
+        <v>1258</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1236</v>
+        <v>1259</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1237</v>
+        <v>1260</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>1238</v>
+        <v>1261</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>1239</v>
+        <v>1262</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1240</v>
+        <v>1263</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1241</v>
+        <v>1264</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>1242</v>
+        <v>1265</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1243</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="B58" t="s">
-        <v>1244</v>
+        <v>1267</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>
@@ -13774,39 +14045,39 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1245</v>
+        <v>1268</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1235</v>
+        <v>1258</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1246</v>
+        <v>1269</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1237</v>
+        <v>1260</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1247</v>
+        <v>1270</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1239</v>
+        <v>1262</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1248</v>
+        <v>1271</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1241</v>
+        <v>1264</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1249</v>
+        <v>1272</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1243</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="B59" t="s">
-        <v>1250</v>
+        <v>1273</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>815</v>
@@ -13815,39 +14086,39 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1251</v>
+        <v>1274</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1252</v>
+        <v>1275</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1253</v>
+        <v>1276</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1254</v>
+        <v>1277</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>1255</v>
+        <v>1278</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>1256</v>
+        <v>1279</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1257</v>
+        <v>1280</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1258</v>
+        <v>1281</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1259</v>
+        <v>1282</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1260</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="B60" t="s">
-        <v>1261</v>
+        <v>1284</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>49</v>
@@ -13856,39 +14127,39 @@
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>1262</v>
+        <v>1285</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1263</v>
+        <v>1286</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1264</v>
+        <v>1287</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1265</v>
+        <v>1288</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>1266</v>
+        <v>1289</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1267</v>
+        <v>1290</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1268</v>
+        <v>1291</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1269</v>
+        <v>1292</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1270</v>
+        <v>1293</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1271</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="B61" t="s">
-        <v>1272</v>
+        <v>1295</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>49</v>
@@ -13897,21 +14168,21 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>1273</v>
+        <v>1296</v>
       </c>
       <c r="F61" t="s">
-        <v>1274</v>
+        <v>1297</v>
       </c>
       <c r="G61" t="s">
-        <v>1275</v>
+        <v>1298</v>
       </c>
       <c r="H61" t="s">
-        <v>1276</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" t="s">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>815</v>
@@ -13920,39 +14191,35 @@
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>1278</v>
+        <v>1301</v>
       </c>
       <c r="H62" t="s">
-        <v>1279</v>
-      </c>
-      <c r="I62" t="s">
-        <v>1280</v>
-      </c>
-      <c r="J62" t="s">
-        <v>1281</v>
-      </c>
+        <v>1302</v>
+      </c>
+      <c r="I62"/>
+      <c r="J62"/>
       <c r="K62" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="L62" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="M62" t="s">
-        <v>1284</v>
+        <v>1305</v>
       </c>
       <c r="N62" t="s">
-        <v>1285</v>
+        <v>1306</v>
       </c>
       <c r="O62" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="P62" t="s">
-        <v>1287</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
       <c r="B63" t="s">
-        <v>1288</v>
+        <v>1309</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>49</v>
@@ -13961,14 +14228,46 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>1289</v>
+        <v>1310</v>
       </c>
       <c r="H63" t="s">
-        <v>1290</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
-      <c r="C64" s="2"/>
+      <c r="B64" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K64" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1316</v>
+      </c>
+      <c r="M64" t="s">
+        <v>1317</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1318</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1319</v>
+      </c>
+      <c r="P64" t="s">
+        <v>1320</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -13993,7 +14292,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" ht="18" spans="1:31">
@@ -14140,28 +14439,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1292</v>
+        <v>1322</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1293</v>
+        <v>1323</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1294</v>
+        <v>1324</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1295</v>
+        <v>1325</v>
       </c>
       <c r="N3" t="s">
-        <v>1296</v>
+        <v>1326</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1297</v>
+        <v>1327</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1298</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -14172,28 +14471,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1299</v>
+        <v>1329</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="I4" t="s">
-        <v>1301</v>
+        <v>1331</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1302</v>
+        <v>1332</v>
       </c>
       <c r="M4" t="s">
-        <v>1303</v>
+        <v>1333</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1304</v>
+        <v>1334</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1305</v>
+        <v>1335</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1306</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -14204,60 +14503,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1307</v>
+        <v>1337</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1308</v>
+        <v>1338</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1309</v>
+        <v>1339</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1311</v>
+        <v>1341</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1312</v>
+        <v>1342</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1313</v>
+        <v>1343</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1314</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1315</v>
+        <v>1345</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1316</v>
+        <v>1346</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1308</v>
+        <v>1338</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1317</v>
+        <v>1347</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1318</v>
+        <v>1348</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1312</v>
+        <v>1342</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1319</v>
+        <v>1349</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1314</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -14265,21 +14564,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1322</v>
+        <v>1352</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1323</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1324</v>
+        <v>1354</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -14288,15 +14587,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1325</v>
+        <v>1355</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1326</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1324</v>
+        <v>1354</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -14313,7 +14612,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1327</v>
+        <v>1357</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -14322,36 +14621,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1328</v>
+        <v>1358</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1329</v>
+        <v>1359</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1331</v>
+        <v>1361</v>
       </c>
       <c r="M10" t="s">
-        <v>1332</v>
+        <v>1362</v>
       </c>
       <c r="N10" t="s">
-        <v>1333</v>
+        <v>1363</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1334</v>
+        <v>1364</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1335</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1336</v>
+        <v>1366</v>
       </c>
       <c r="B11" t="s">
-        <v>1337</v>
+        <v>1367</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -14360,42 +14659,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1338</v>
+        <v>1368</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1339</v>
+        <v>1369</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1340</v>
+        <v>1370</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1341</v>
+        <v>1371</v>
       </c>
       <c r="M11" t="s">
-        <v>1342</v>
+        <v>1372</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1343</v>
+        <v>1373</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1344</v>
+        <v>1374</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1345</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1338</v>
+        <v>1368</v>
       </c>
       <c r="B12" t="s">
-        <v>1346</v>
+        <v>1376</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1347</v>
+        <v>1377</v>
       </c>
       <c r="D12" t="s">
-        <v>1348</v>
+        <v>1378</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -14404,33 +14703,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1336</v>
+        <v>1366</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1349</v>
+        <v>1379</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1351</v>
+        <v>1381</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1352</v>
+        <v>1382</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1353</v>
+        <v>1383</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1354</v>
+        <v>1384</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1355</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1356</v>
+        <v>1386</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -14439,39 +14738,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1357</v>
+        <v>1387</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1358</v>
+        <v>1388</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1359</v>
+        <v>1389</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1360</v>
+        <v>1390</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1361</v>
+        <v>1391</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1362</v>
+        <v>1392</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1363</v>
+        <v>1393</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1366</v>
+        <v>1396</v>
       </c>
       <c r="B14" t="s">
-        <v>1367</v>
+        <v>1397</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -14480,22 +14779,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1368</v>
+        <v>1398</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1369</v>
+        <v>1399</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1370</v>
+        <v>1400</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1371</v>
+        <v>1401</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1372</v>
+        <v>1402</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1373</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -14507,33 +14806,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1374</v>
+        <v>1404</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1375</v>
+        <v>1405</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1376</v>
+        <v>1406</v>
       </c>
       <c r="N15" t="s">
-        <v>1377</v>
+        <v>1407</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1378</v>
+        <v>1408</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1379</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1381</v>
+        <v>1411</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1382</v>
+        <v>1412</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -14542,18 +14841,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1383</v>
+        <v>1413</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1384</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1385</v>
+        <v>1415</v>
       </c>
       <c r="B17" t="s">
-        <v>1386</v>
+        <v>1416</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -14562,30 +14861,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1387</v>
+        <v>1417</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1388</v>
+        <v>1418</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1389</v>
+        <v>1419</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1390</v>
+        <v>1420</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1391</v>
+        <v>1421</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1392</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1393</v>
+        <v>1423</v>
       </c>
       <c r="B18" t="s">
-        <v>1394</v>
+        <v>1424</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -14594,27 +14893,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1396</v>
+        <v>1426</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1397</v>
+        <v>1427</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1398</v>
+        <v>1428</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1399</v>
+        <v>1429</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1400</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1401</v>
+        <v>1431</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -14623,30 +14922,30 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1393</v>
+        <v>1423</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1404</v>
+        <v>1434</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1406</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>1407</v>
+        <v>1437</v>
       </c>
       <c r="B20" t="s">
-        <v>1408</v>
+        <v>1438</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -14655,40 +14954,40 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1409</v>
+        <v>1439</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="K20" t="s">
-        <v>1411</v>
+        <v>1441</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1412</v>
+        <v>1442</v>
       </c>
       <c r="M20" t="s">
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1414</v>
+        <v>1444</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1415</v>
+        <v>1445</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1416</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
-        <v>1417</v>
+        <v>1447</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1418</v>
+        <v>1448</v>
       </c>
       <c r="D21" t="s">
-        <v>1419</v>
+        <v>1449</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -14697,34 +14996,34 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1420</v>
+        <v>1450</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1421</v>
+        <v>1451</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1422</v>
+        <v>1452</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1424</v>
+        <v>1454</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1425</v>
+        <v>1455</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1426</v>
+        <v>1456</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1427</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1428</v>
+        <v>1458</v>
       </c>
       <c r="C22" s="2"/>
       <c r="E22" t="s">
@@ -14734,33 +15033,33 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1429</v>
+        <v>1459</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1430</v>
+        <v>1460</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1431</v>
+        <v>1461</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1432</v>
+        <v>1462</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1433</v>
+        <v>1463</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1435</v>
+        <v>1465</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1436</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="B23" t="s">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="E23" t="s">
         <v>222</v>
@@ -14769,27 +15068,27 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1440</v>
+        <v>1470</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1442</v>
+        <v>1472</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1409</v>
+        <v>1439</v>
       </c>
       <c r="E24" t="s">
         <v>49</v>
@@ -14798,33 +15097,33 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1407</v>
+        <v>1437</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1444</v>
+        <v>1474</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1445</v>
+        <v>1475</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1446</v>
+        <v>1476</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1447</v>
+        <v>1477</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1448</v>
+        <v>1478</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1449</v>
+        <v>1479</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1450</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="B25" t="s">
-        <v>1451</v>
+        <v>1481</v>
       </c>
       <c r="E25" t="s">
         <v>222</v>
@@ -14833,27 +15132,27 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1452</v>
+        <v>1482</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1453</v>
+        <v>1483</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1454</v>
+        <v>1484</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1455</v>
+        <v>1485</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1456</v>
+        <v>1486</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1457</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1458</v>
+        <v>1488</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -14862,36 +15161,36 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1459</v>
+        <v>1489</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1460</v>
+        <v>1490</v>
       </c>
       <c r="I26" t="s">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1462</v>
+        <v>1492</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1463</v>
+        <v>1493</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1464</v>
+        <v>1494</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1465</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1466</v>
+        <v>1496</v>
       </c>
       <c r="C27" t="s">
-        <v>1467</v>
+        <v>1497</v>
       </c>
       <c r="D27" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="E27" t="s">
         <v>49</v>
@@ -14900,27 +15199,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1469</v>
+        <v>1499</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1470</v>
+        <v>1500</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1471</v>
+        <v>1501</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1472</v>
+        <v>1502</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1473</v>
+        <v>1503</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
       <c r="E28" t="s">
         <v>222</v>
@@ -14929,27 +15228,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1476</v>
+        <v>1506</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1477</v>
+        <v>1507</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1478</v>
+        <v>1508</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1482</v>
+        <v>1512</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -14958,10 +15257,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1484</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
@@ -14972,33 +15271,33 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1486</v>
+        <v>1516</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1487</v>
+        <v>1517</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1488</v>
+        <v>1518</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>1489</v>
+        <v>1519</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1490</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1491</v>
+        <v>1521</v>
       </c>
       <c r="C31" t="s">
-        <v>1492</v>
+        <v>1522</v>
       </c>
       <c r="D31" t="s">
-        <v>1493</v>
+        <v>1523</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
@@ -15007,21 +15306,21 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1494</v>
+        <v>1524</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1495</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1496</v>
+        <v>1526</v>
       </c>
       <c r="C32" t="s">
-        <v>1497</v>
+        <v>1527</v>
       </c>
       <c r="D32" t="s">
-        <v>1498</v>
+        <v>1528</v>
       </c>
       <c r="E32" t="s">
         <v>222</v>
@@ -15030,33 +15329,33 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1499</v>
+        <v>1529</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1500</v>
+        <v>1530</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1501</v>
+        <v>1531</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1502</v>
+        <v>1532</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1503</v>
+        <v>1533</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1504</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="C33" t="s">
-        <v>1506</v>
+        <v>1536</v>
       </c>
       <c r="D33" t="s">
-        <v>1507</v>
+        <v>1537</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>815</v>
@@ -15065,30 +15364,30 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1508</v>
+        <v>1538</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1509</v>
+        <v>1539</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1510</v>
+        <v>1540</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1511</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>1512</v>
+        <v>1542</v>
       </c>
       <c r="B34" t="s">
-        <v>1513</v>
+        <v>1543</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1514</v>
+        <v>1544</v>
       </c>
       <c r="D34" t="s">
-        <v>1515</v>
+        <v>1545</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>222</v>
@@ -15097,33 +15396,33 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1516</v>
+        <v>1546</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1517</v>
+        <v>1547</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1518</v>
+        <v>1548</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1519</v>
+        <v>1549</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1520</v>
+        <v>1550</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1521</v>
+        <v>1551</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1522</v>
+        <v>1552</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1523</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1524</v>
+        <v>1554</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -15132,27 +15431,27 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1525</v>
+        <v>1555</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1526</v>
+        <v>1556</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1527</v>
+        <v>1557</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1528</v>
+        <v>1558</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1529</v>
+        <v>1559</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1531</v>
+        <v>1561</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -15161,33 +15460,33 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1532</v>
+        <v>1562</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1533</v>
+        <v>1563</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1534</v>
+        <v>1564</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1535</v>
+        <v>1565</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1537</v>
+        <v>1567</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1538</v>
+        <v>1568</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1539</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1540</v>
+        <v>1570</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>815</v>
@@ -15196,10 +15495,86 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>1541</v>
+        <v>1571</v>
       </c>
       <c r="H37" t="s">
-        <v>1542</v>
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="38" ht="18" spans="1:16">
+      <c r="B38" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1574</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K38" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1578</v>
+      </c>
+      <c r="N38" t="s">
+        <v>1579</v>
+      </c>
+      <c r="O38" t="s">
+        <v>1580</v>
+      </c>
+      <c r="P38" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="39" ht="18" spans="1:16">
+      <c r="B39" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1585</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K39" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1588</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N39" t="s">
+        <v>1590</v>
+      </c>
+      <c r="O39" t="s">
+        <v>1591</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1592</v>
       </c>
     </row>
   </sheetData>
@@ -15374,16 +15749,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1543</v>
+        <v>1593</v>
       </c>
       <c r="B3" t="s">
-        <v>1544</v>
+        <v>1594</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1545</v>
+        <v>1595</v>
       </c>
       <c r="D3" t="s">
-        <v>1546</v>
+        <v>1596</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -15392,31 +15767,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1547</v>
+        <v>1597</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1548</v>
+        <v>1598</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1549</v>
+        <v>1599</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1552</v>
+        <v>1602</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1553</v>
+        <v>1603</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1554</v>
+        <v>1604</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -15426,42 +15801,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1555</v>
+        <v>1605</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1555</v>
+        <v>1605</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1557</v>
+        <v>1607</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1558</v>
+        <v>1608</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1559</v>
+        <v>1609</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1560</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1561</v>
+        <v>1611</v>
       </c>
       <c r="B4" t="s">
-        <v>1562</v>
+        <v>1612</v>
       </c>
       <c r="C4" t="s">
-        <v>1563</v>
+        <v>1613</v>
       </c>
       <c r="D4" t="s">
-        <v>1564</v>
+        <v>1614</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -15470,37 +15845,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1565</v>
+        <v>1615</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1566</v>
+        <v>1616</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1567</v>
+        <v>1617</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1568</v>
+        <v>1618</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1569</v>
+        <v>1619</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1570</v>
+        <v>1620</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1571</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1562</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="s">
-        <v>1572</v>
+        <v>1622</v>
       </c>
       <c r="D5" t="s">
-        <v>1564</v>
+        <v>1614</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -15509,54 +15884,54 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1573</v>
+        <v>1623</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1574</v>
+        <v>1624</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1576</v>
+        <v>1626</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1577</v>
+        <v>1627</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1578</v>
+        <v>1628</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1579</v>
+        <v>1629</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1580</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1581</v>
+        <v>1631</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1582</v>
+        <v>1632</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1583</v>
+        <v>1633</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1584</v>
+        <v>1634</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1585</v>
+        <v>1635</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1586</v>
+        <v>1636</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1587</v>
+        <v>1637</v>
       </c>
     </row>
   </sheetData>
@@ -15738,30 +16113,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1588</v>
+        <v>1638</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1589</v>
+        <v>1639</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1590</v>
+        <v>1640</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1591</v>
+        <v>1641</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1592</v>
+        <v>1642</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1593</v>
+        <v>1643</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1594</v>
+        <v>1644</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1595</v>
+        <v>1645</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -15771,16 +16146,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1596</v>
+        <v>1646</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1597</v>
+        <v>1647</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1598</v>
+        <v>1648</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1599</v>
+        <v>1649</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -15795,34 +16170,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1601</v>
+        <v>1651</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1602</v>
+        <v>1652</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1603</v>
+        <v>1653</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1604</v>
+        <v>1654</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1605</v>
+        <v>1655</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1606</v>
+        <v>1656</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1607</v>
+        <v>1657</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1608</v>
+        <v>1658</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1609</v>
+        <v>1659</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -15842,7 +16217,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1610</v>
+        <v>1660</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -15851,34 +16226,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1611</v>
+        <v>1661</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1612</v>
+        <v>1662</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1613</v>
+        <v>1663</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1614</v>
+        <v>1664</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1616</v>
+        <v>1666</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1617</v>
+        <v>1667</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1618</v>
+        <v>1668</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1619</v>
+        <v>1669</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -15888,16 +16263,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1621</v>
+        <v>1671</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1622</v>
+        <v>1672</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1623</v>
+        <v>1673</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1624</v>
+        <v>1674</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -15906,13 +16281,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1625</v>
+        <v>1675</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1626</v>
+        <v>1676</v>
       </c>
       <c r="D6" t="s">
-        <v>1627</v>
+        <v>1677</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -15921,30 +16296,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1628</v>
+        <v>1678</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1629</v>
+        <v>1679</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1630</v>
+        <v>1680</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1631</v>
+        <v>1681</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1632</v>
+        <v>1682</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1633</v>
+        <v>1683</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1634</v>
+        <v>1684</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1635</v>
+        <v>1685</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -15956,10 +16331,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1637</v>
+        <v>1687</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -15968,13 +16343,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1625</v>
+        <v>1675</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1638</v>
+        <v>1688</v>
       </c>
       <c r="D7" t="s">
-        <v>1627</v>
+        <v>1677</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -15983,34 +16358,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1637</v>
+        <v>1687</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1639</v>
+        <v>1689</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1640</v>
+        <v>1690</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1641</v>
+        <v>1691</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1642</v>
+        <v>1692</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1643</v>
+        <v>1693</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1644</v>
+        <v>1694</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1645</v>
+        <v>1695</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1646</v>
+        <v>1696</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -16030,7 +16405,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1647</v>
+        <v>1697</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -16039,75 +16414,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1648</v>
+        <v>1698</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1649</v>
+        <v>1699</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1651</v>
+        <v>1701</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1652</v>
+        <v>1702</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1653</v>
+        <v>1703</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1654</v>
+        <v>1704</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1655</v>
+        <v>1705</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1656</v>
+        <v>1706</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1657</v>
+        <v>1707</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1658</v>
+        <v>1708</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1659</v>
+        <v>1709</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1660</v>
+        <v>1710</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1661</v>
+        <v>1711</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1662</v>
+        <v>1712</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1557</v>
+        <v>1607</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1558</v>
+        <v>1608</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1555</v>
+        <v>1605</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1557</v>
+        <v>1607</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1558</v>
+        <v>1608</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1559</v>
+        <v>1609</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1560</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -16115,7 +16490,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1663</v>
+        <v>1713</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -16124,10 +16499,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1664</v>
+        <v>1714</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1665</v>
+        <v>1715</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -16160,7 +16535,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1666</v>
+        <v>1716</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -16169,10 +16544,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1667</v>
+        <v>1717</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1668</v>
+        <v>1718</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -16201,7 +16576,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1669</v>
+        <v>1719</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -16210,37 +16585,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1670</v>
+        <v>1720</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1671</v>
+        <v>1721</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1672</v>
+        <v>1722</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1673</v>
+        <v>1723</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1674</v>
+        <v>1724</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1675</v>
+        <v>1725</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1676</v>
+        <v>1726</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1677</v>
+        <v>1727</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1678</v>
+        <v>1728</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1679</v>
+        <v>1729</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1680</v>
+        <v>1730</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -16253,10 +16628,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1681</v>
+        <v>1731</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1682</v>
+        <v>1732</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -16264,7 +16639,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1683</v>
+        <v>1733</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -16273,20 +16648,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1684</v>
+        <v>1734</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1686</v>
+        <v>1736</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1687</v>
+        <v>1737</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -16308,10 +16683,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1688</v>
+        <v>1738</v>
       </c>
       <c r="B13" t="s">
-        <v>1689</v>
+        <v>1739</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -16320,20 +16695,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1690</v>
+        <v>1740</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1691</v>
+        <v>1741</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1692</v>
+        <v>1742</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1693</v>
+        <v>1743</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -16355,10 +16730,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1690</v>
+        <v>1740</v>
       </c>
       <c r="B14" t="s">
-        <v>1694</v>
+        <v>1744</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16367,20 +16742,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1688</v>
+        <v>1738</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1695</v>
+        <v>1745</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1696</v>
+        <v>1746</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1687</v>
+        <v>1737</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -16402,10 +16777,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1697</v>
+        <v>1747</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1698</v>
+        <v>1748</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -16415,39 +16790,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1699</v>
+        <v>1749</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1701</v>
+        <v>1751</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1702</v>
+        <v>1752</v>
       </c>
       <c r="K15" t="s">
-        <v>1703</v>
+        <v>1753</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1704</v>
+        <v>1754</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1705</v>
+        <v>1755</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1706</v>
+        <v>1756</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1707</v>
+        <v>1757</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1708</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1709</v>
+        <v>1759</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16456,34 +16831,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1710</v>
+        <v>1760</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1711</v>
+        <v>1761</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1712</v>
+        <v>1762</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1713</v>
+        <v>1763</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1714</v>
+        <v>1764</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1715</v>
+        <v>1765</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1716</v>
+        <v>1766</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1717</v>
+        <v>1767</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1718</v>
+        <v>1768</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1719</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -16494,7 +16869,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1720</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -16505,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1721</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -16516,10 +16891,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1722</v>
+        <v>1772</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1723</v>
+        <v>1773</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -16531,18 +16906,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1724</v>
+        <v>1774</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1723</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1725</v>
+        <v>1775</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1726</v>
+        <v>1776</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -16552,42 +16927,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1727</v>
+        <v>1777</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1728</v>
+        <v>1778</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1729</v>
+        <v>1779</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1730</v>
+        <v>1780</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1731</v>
+        <v>1781</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1732</v>
+        <v>1782</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1733</v>
+        <v>1783</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1734</v>
+        <v>1784</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1735</v>
+        <v>1785</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1736</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1737</v>
+        <v>1787</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1738</v>
+        <v>1788</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -16597,39 +16972,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1739</v>
+        <v>1789</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1728</v>
+        <v>1778</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1730</v>
+        <v>1780</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1740</v>
+        <v>1790</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1732</v>
+        <v>1782</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1741</v>
+        <v>1791</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1734</v>
+        <v>1784</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1742</v>
+        <v>1792</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1736</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>1743</v>
+        <v>1793</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1744</v>
+        <v>1794</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -16639,27 +17014,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1745</v>
+        <v>1795</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1746</v>
+        <v>1796</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1747</v>
+        <v>1797</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1748</v>
+        <v>1798</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1749</v>
+        <v>1799</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>1751</v>
+        <v>1801</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -16668,39 +17043,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1752</v>
+        <v>1802</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1753</v>
+        <v>1803</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1754</v>
+        <v>1804</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1755</v>
+        <v>1805</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1756</v>
+        <v>1806</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1757</v>
+        <v>1807</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1758</v>
+        <v>1808</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1759</v>
+        <v>1809</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1760</v>
+        <v>1810</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1761</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>1751</v>
+        <v>1801</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -16709,10 +17084,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1762</v>
+        <v>1812</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1763</v>
+        <v>1813</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -16725,7 +17100,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>1764</v>
+        <v>1814</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -16734,26 +17109,26 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1765</v>
+        <v>1815</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>951</v>
+        <v>974</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>1766</v>
+        <v>1816</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1767</v>
+        <v>1817</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1768</v>
+        <v>1818</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1769</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -16764,32 +17139,32 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>950</v>
+        <v>973</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>951</v>
+        <v>974</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>1770</v>
+        <v>1820</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1767</v>
+        <v>1817</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1771</v>
+        <v>1821</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1769</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
       <c r="B28" t="s">
-        <v>991</v>
+        <v>1014</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1772</v>
+        <v>1822</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -16799,39 +17174,39 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1773</v>
+        <v>1823</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1774</v>
+        <v>1824</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1775</v>
+        <v>1825</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1776</v>
+        <v>1826</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1777</v>
+        <v>1827</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1778</v>
+        <v>1828</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1779</v>
+        <v>1829</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1780</v>
+        <v>1830</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1781</v>
+        <v>1831</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1782</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
       <c r="B29" t="s">
-        <v>1035</v>
+        <v>1058</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>222</v>
@@ -16840,27 +17215,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1783</v>
+        <v>1833</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1784</v>
+        <v>1834</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1785</v>
+        <v>1835</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1786</v>
+        <v>1836</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1787</v>
+        <v>1837</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1788</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>1789</v>
+        <v>1839</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -16869,27 +17244,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1790</v>
+        <v>1840</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1791</v>
+        <v>1841</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1792</v>
+        <v>1842</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1793</v>
+        <v>1843</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>1794</v>
+        <v>1844</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1795</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>1796</v>
+        <v>1846</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -16898,27 +17273,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1797</v>
+        <v>1847</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1798</v>
+        <v>1848</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1799</v>
+        <v>1849</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1801</v>
+        <v>1851</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1802</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>1803</v>
+        <v>1853</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -16933,21 +17308,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1804</v>
+        <v>1854</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1805</v>
+        <v>1855</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1806</v>
+        <v>1856</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1807</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1808</v>
+        <v>1858</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -16956,22 +17331,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1809</v>
+        <v>1859</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1810</v>
+        <v>1860</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1811</v>
+        <v>1861</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1812</v>
+        <v>1862</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1813</v>
+        <v>1863</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1814</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -16981,30 +17356,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1815</v>
+        <v>1865</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1816</v>
+        <v>1866</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1817</v>
+        <v>1867</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1819</v>
+        <v>1869</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1820</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1821</v>
+        <v>1871</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -17013,10 +17388,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1822</v>
+        <v>1872</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1823</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -17027,30 +17402,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1824</v>
+        <v>1874</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1825</v>
+        <v>1875</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1826</v>
+        <v>1876</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1827</v>
+        <v>1877</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1828</v>
+        <v>1878</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1829</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1830</v>
+        <v>1880</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1831</v>
+        <v>1881</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -17059,30 +17434,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1832</v>
+        <v>1882</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1833</v>
+        <v>1883</v>
       </c>
       <c r="M38" t="s">
-        <v>1834</v>
+        <v>1884</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1835</v>
+        <v>1885</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>1836</v>
+        <v>1886</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1837</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1838</v>
+        <v>1888</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1839</v>
+        <v>1889</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -17092,18 +17467,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1840</v>
+        <v>1890</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1841</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1842</v>
+        <v>1892</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1843</v>
+        <v>1893</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -17113,22 +17488,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1628</v>
+        <v>1678</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1629</v>
+        <v>1679</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1632</v>
+        <v>1682</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1633</v>
+        <v>1683</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1634</v>
+        <v>1684</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1635</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -17141,15 +17516,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1844</v>
+        <v>1894</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1845</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>1846</v>
+        <v>1896</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -17158,54 +17533,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1847</v>
+        <v>1897</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1848</v>
+        <v>1898</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1849</v>
+        <v>1899</v>
       </c>
       <c r="N42" t="s">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>1851</v>
+        <v>1901</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>1852</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1853</v>
+        <v>1903</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1854</v>
+        <v>1904</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1848</v>
+        <v>1898</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1855</v>
+        <v>1905</v>
       </c>
       <c r="N43" t="s">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>1856</v>
+        <v>1906</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>1852</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1857</v>
+        <v>1907</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -17214,30 +17589,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1858</v>
+        <v>1908</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1848</v>
+        <v>1898</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1859</v>
+        <v>1909</v>
       </c>
       <c r="N44" t="s">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>1860</v>
+        <v>1910</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>1852</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>1861</v>
+        <v>1911</v>
       </c>
       <c r="C45" t="s">
-        <v>1862</v>
+        <v>1912</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -17246,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1863</v>
+        <v>1913</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -17254,10 +17629,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>1864</v>
+        <v>1914</v>
       </c>
       <c r="B46" t="s">
-        <v>1865</v>
+        <v>1915</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -17266,24 +17641,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1866</v>
+        <v>1916</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1867</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>1868</v>
+        <v>1918</v>
       </c>
       <c r="B47" t="s">
-        <v>1869</v>
+        <v>1919</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1870</v>
+        <v>1920</v>
       </c>
       <c r="D47" t="s">
-        <v>1871</v>
+        <v>1921</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -17292,33 +17667,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1872</v>
+        <v>1922</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1873</v>
+        <v>1923</v>
       </c>
       <c r="M47" t="s">
-        <v>1874</v>
+        <v>1924</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>1876</v>
+        <v>1926</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>1877</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1878</v>
+        <v>1928</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1879</v>
+        <v>1929</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>1880</v>
+        <v>1930</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -17327,18 +17702,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1881</v>
+        <v>1931</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1882</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>1061</v>
+        <v>1084</v>
       </c>
       <c r="B49" t="s">
-        <v>1883</v>
+        <v>1933</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -17347,28 +17722,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1884</v>
+        <v>1934</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1885</v>
+        <v>1935</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1886</v>
+        <v>1936</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1887</v>
+        <v>1937</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1888</v>
+        <v>1938</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1889</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>1883</v>
+        <v>1933</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -17377,30 +17752,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1890</v>
+        <v>1940</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1885</v>
+        <v>1935</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1891</v>
+        <v>1941</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1887</v>
+        <v>1937</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1892</v>
+        <v>1942</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1889</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>1893</v>
+        <v>1943</v>
       </c>
       <c r="B51" t="s">
-        <v>1894</v>
+        <v>1944</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -17409,34 +17784,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1366</v>
+        <v>1396</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1895</v>
+        <v>1945</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1896</v>
+        <v>1946</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1897</v>
+        <v>1947</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>1898</v>
+        <v>1948</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>1899</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1901</v>
+        <v>1951</v>
       </c>
       <c r="D52" t="s">
-        <v>1902</v>
+        <v>1952</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -17445,24 +17820,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1844</v>
+        <v>1894</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1845</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>1903</v>
+        <v>1953</v>
       </c>
       <c r="B53" t="s">
-        <v>1904</v>
+        <v>1954</v>
       </c>
       <c r="C53" t="s">
-        <v>1905</v>
+        <v>1955</v>
       </c>
       <c r="D53" t="s">
-        <v>1906</v>
+        <v>1956</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -17471,18 +17846,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1907</v>
+        <v>1957</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1908</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>1909</v>
+        <v>1959</v>
       </c>
       <c r="B54" t="s">
-        <v>1910</v>
+        <v>1960</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -17491,36 +17866,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1328</v>
+        <v>1358</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1329</v>
+        <v>1359</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1332</v>
+        <v>1362</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1911</v>
+        <v>1961</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1334</v>
+        <v>1364</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1335</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>1912</v>
+        <v>1962</v>
       </c>
       <c r="B55" t="s">
-        <v>1913</v>
+        <v>1963</v>
       </c>
       <c r="C55" t="s">
-        <v>1914</v>
+        <v>1964</v>
       </c>
       <c r="D55" t="s">
-        <v>1915</v>
+        <v>1965</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -17529,19 +17904,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1916</v>
+        <v>1966</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1917</v>
+        <v>1967</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1561</v>
+        <v>1611</v>
       </c>
       <c r="B56" t="s">
-        <v>1918</v>
+        <v>1968</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -17550,36 +17925,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1919</v>
+        <v>1969</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1920</v>
+        <v>1970</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1921</v>
+        <v>1971</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1922</v>
+        <v>1972</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>1923</v>
+        <v>1973</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>1924</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>1925</v>
+        <v>1975</v>
       </c>
       <c r="B57" t="s">
-        <v>1926</v>
+        <v>1976</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1927</v>
+        <v>1977</v>
       </c>
       <c r="D57" t="s">
-        <v>1928</v>
+        <v>1978</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -17588,36 +17963,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1561</v>
+        <v>1611</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1929</v>
+        <v>1979</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1930</v>
+        <v>1980</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1931</v>
+        <v>1981</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>1932</v>
+        <v>1982</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1933</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1409</v>
+        <v>1439</v>
       </c>
       <c r="B58" t="s">
-        <v>1934</v>
+        <v>1984</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1935</v>
+        <v>1985</v>
       </c>
       <c r="D58" t="s">
-        <v>1936</v>
+        <v>1986</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -17626,36 +18001,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1912</v>
+        <v>1962</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1937</v>
+        <v>1987</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1938</v>
+        <v>1988</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1939</v>
+        <v>1989</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1940</v>
+        <v>1990</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1941</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1387</v>
+        <v>1417</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1942</v>
+        <v>1992</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1943</v>
+        <v>1993</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1944</v>
+        <v>1994</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -17664,10 +18039,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1942</v>
+        <v>1992</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1945</v>
+        <v>1995</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -17676,16 +18051,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>1912</v>
+        <v>1962</v>
       </c>
       <c r="B60" t="s">
-        <v>1946</v>
+        <v>1996</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1947</v>
+        <v>1997</v>
       </c>
       <c r="D60" t="s">
-        <v>1948</v>
+        <v>1998</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -17694,10 +18069,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1949</v>
+        <v>1999</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -17706,16 +18081,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="B61" t="s">
-        <v>1951</v>
+        <v>2001</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1952</v>
+        <v>2002</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>1953</v>
+        <v>2003</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -17724,27 +18099,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1954</v>
+        <v>2004</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>1955</v>
+        <v>2005</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1956</v>
+        <v>2006</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1957</v>
+        <v>2007</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>1958</v>
+        <v>2008</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1959</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>1960</v>
+        <v>2010</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -17753,10 +18128,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1961</v>
+        <v>2011</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>1962</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -17768,24 +18143,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1963</v>
+        <v>2013</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>1962</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>1912</v>
+        <v>1962</v>
       </c>
       <c r="B64" t="s">
-        <v>1964</v>
+        <v>2014</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1965</v>
+        <v>2015</v>
       </c>
       <c r="D64" t="s">
-        <v>1966</v>
+        <v>2016</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -17794,10 +18169,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1967</v>
+        <v>2017</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>1968</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -17808,15 +18183,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1969</v>
+        <v>2019</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>1968</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>1970</v>
+        <v>2020</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -17825,15 +18200,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1971</v>
+        <v>2021</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1972</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>1973</v>
+        <v>2023</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -17842,15 +18217,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1974</v>
+        <v>2024</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>1975</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>1976</v>
+        <v>2026</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -17859,15 +18234,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1977</v>
+        <v>2027</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>1978</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>1976</v>
+        <v>2026</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -17876,15 +18251,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1979</v>
+        <v>2029</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>1978</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>1980</v>
+        <v>2030</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -17893,27 +18268,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1981</v>
+        <v>2031</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>1982</v>
+        <v>2032</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1983</v>
+        <v>2033</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1984</v>
+        <v>2034</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>1985</v>
+        <v>2035</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>1986</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>1987</v>
+        <v>2037</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -17922,27 +18297,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1988</v>
+        <v>2038</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>1989</v>
+        <v>2039</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>1990</v>
+        <v>2040</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>1991</v>
+        <v>2041</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>1992</v>
+        <v>2042</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>1993</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>1994</v>
+        <v>2044</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -17951,7 +18326,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1995</v>
+        <v>2045</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -17959,7 +18334,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>1994</v>
+        <v>2044</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -17968,33 +18343,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1996</v>
+        <v>2046</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>1997</v>
+        <v>2047</v>
       </c>
       <c r="N73" t="s">
-        <v>1998</v>
+        <v>2048</v>
       </c>
       <c r="O73" t="s">
-        <v>1999</v>
+        <v>2049</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2000</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2001</v>
+        <v>2051</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>2002</v>
+        <v>2052</v>
       </c>
       <c r="D74" t="s">
-        <v>2003</v>
+        <v>2053</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -18006,29 +18381,29 @@
         <v>737</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2004</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2005</v>
+        <v>2055</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>2006</v>
+        <v>2056</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>2007</v>
+        <v>2057</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2008</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2009</v>
+        <v>2059</v>
       </c>
       <c r="E76" t="s">
         <v>222</v>
@@ -18037,27 +18412,27 @@
         <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2010</v>
+        <v>2060</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2011</v>
+        <v>2061</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>2012</v>
+        <v>2062</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>2013</v>
+        <v>2063</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>2014</v>
+        <v>2064</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>2015</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2016</v>
+        <v>2066</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -18066,15 +18441,15 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2017</v>
+        <v>2067</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2018</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2019</v>
+        <v>2069</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -18083,27 +18458,27 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2020</v>
+        <v>2070</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2021</v>
+        <v>2071</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>2022</v>
+        <v>2072</v>
       </c>
       <c r="N78" t="s">
-        <v>2023</v>
+        <v>2073</v>
       </c>
       <c r="O78" t="s">
-        <v>2024</v>
+        <v>2074</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>2025</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2026</v>
+        <v>2076</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -18112,33 +18487,33 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2027</v>
+        <v>2077</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2028</v>
+        <v>2078</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2029</v>
+        <v>2079</v>
       </c>
       <c r="N79" t="s">
-        <v>2030</v>
+        <v>2080</v>
       </c>
       <c r="O79" t="s">
-        <v>2031</v>
+        <v>2081</v>
       </c>
       <c r="P79" t="s">
-        <v>2032</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2033</v>
+        <v>2083</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>2034</v>
+        <v>2084</v>
       </c>
       <c r="D80" t="s">
-        <v>2035</v>
+        <v>2085</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -18147,33 +18522,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2036</v>
+        <v>2086</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2037</v>
+        <v>2087</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2038</v>
+        <v>2088</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>2039</v>
+        <v>2089</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>2040</v>
+        <v>2090</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>2041</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2042</v>
+        <v>2092</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2043</v>
+        <v>2093</v>
       </c>
       <c r="D81" t="s">
-        <v>2044</v>
+        <v>2094</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -18182,30 +18557,30 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2045</v>
+        <v>2095</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2046</v>
+        <v>2096</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2047</v>
+        <v>2097</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2048</v>
+        <v>2098</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2049</v>
+        <v>2099</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2050</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="A82" s="2" t="s">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="B82" t="s">
-        <v>2051</v>
+        <v>2101</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -18214,33 +18589,33 @@
         <v>2</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2052</v>
+        <v>2102</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2054</v>
+        <v>2104</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2055</v>
+        <v>2105</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2056</v>
+        <v>2106</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2057</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="B83" t="s">
-        <v>2058</v>
+        <v>2108</v>
       </c>
       <c r="C83" t="s">
-        <v>2059</v>
+        <v>2109</v>
       </c>
       <c r="D83" t="s">
-        <v>2060</v>
+        <v>2110</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -18249,33 +18624,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2061</v>
+        <v>2111</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2062</v>
+        <v>2112</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2063</v>
+        <v>2113</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2064</v>
+        <v>2114</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2065</v>
+        <v>2115</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2066</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2067</v>
+        <v>2117</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1839</v>
+        <v>1889</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>2068</v>
+        <v>2118</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -18284,27 +18659,27 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1840</v>
+        <v>1890</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>1841</v>
+        <v>1891</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2069</v>
+        <v>2119</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2070</v>
+        <v>2120</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2071</v>
+        <v>2121</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2072</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2073</v>
+        <v>2123</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -18313,27 +18688,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2074</v>
+        <v>2124</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2075</v>
+        <v>2125</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2076</v>
+        <v>2126</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2077</v>
+        <v>2127</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2078</v>
+        <v>2128</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2079</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2080</v>
+        <v>2130</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -18342,21 +18717,21 @@
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>2081</v>
+        <v>2131</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2082</v>
+        <v>2132</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2083</v>
+        <v>2133</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2084</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="B87" t="s">
-        <v>2085</v>
+        <v>2135</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -18365,10 +18740,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>2086</v>
+        <v>2136</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2087</v>
+        <v>2137</v>
       </c>
     </row>
   </sheetData>
@@ -18558,16 +18933,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1547</v>
+        <v>1597</v>
       </c>
       <c r="B3" t="s">
-        <v>2088</v>
+        <v>2138</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2089</v>
+        <v>2139</v>
       </c>
       <c r="D3" t="s">
-        <v>2090</v>
+        <v>2140</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -18576,42 +18951,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1543</v>
+        <v>1593</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2091</v>
+        <v>2141</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2092</v>
+        <v>2142</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2093</v>
+        <v>2143</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2094</v>
+        <v>2144</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2095</v>
+        <v>2145</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2096</v>
+        <v>2146</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2097</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2098</v>
+        <v>2148</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2099</v>
+        <v>2149</v>
       </c>
       <c r="D4" t="s">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -18620,21 +18995,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2101</v>
+        <v>2151</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2102</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2103</v>
+        <v>2153</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2104</v>
+        <v>2154</v>
       </c>
       <c r="D5" t="s">
-        <v>2105</v>
+        <v>2155</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -18643,33 +19018,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2106</v>
+        <v>2156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2107</v>
+        <v>2157</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2108</v>
+        <v>2158</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2109</v>
+        <v>2159</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2110</v>
+        <v>2160</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2111</v>
+        <v>2161</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2112</v>
+        <v>2162</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2113</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2114</v>
+        <v>2164</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -18678,62 +19053,62 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2115</v>
+        <v>2165</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2116</v>
+        <v>2166</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2117</v>
+        <v>2167</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2118</v>
+        <v>2168</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2119</v>
+        <v>2169</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2120</v>
+        <v>2170</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2121</v>
+        <v>2171</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2122</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2123</v>
+        <v>2173</v>
       </c>
       <c r="G7" t="s">
-        <v>2124</v>
+        <v>2174</v>
       </c>
       <c r="H7" t="s">
-        <v>2125</v>
+        <v>2175</v>
       </c>
       <c r="L7" t="s">
-        <v>2126</v>
+        <v>2176</v>
       </c>
       <c r="M7" t="s">
-        <v>2127</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2123</v>
+        <v>2173</v>
       </c>
       <c r="G8" t="s">
-        <v>2128</v>
+        <v>2178</v>
       </c>
       <c r="H8" t="s">
-        <v>2125</v>
+        <v>2175</v>
       </c>
       <c r="L8" t="s">
-        <v>2129</v>
+        <v>2179</v>
       </c>
       <c r="M8" t="s">
-        <v>2127</v>
+        <v>2177</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="2180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="2369">
   <si>
     <r>
       <rPr>
@@ -3044,6 +3044,105 @@
     <t>ほうっておいた</t>
   </si>
   <si>
+    <t>使痛苦，欺负</t>
+  </si>
+  <si>
+    <t>苦しめる</t>
+  </si>
+  <si>
+    <t>くるしめる</t>
+  </si>
+  <si>
+    <t>苦しめて</t>
+  </si>
+  <si>
+    <t>くるしめて</t>
+  </si>
+  <si>
+    <t>苦しめた</t>
+  </si>
+  <si>
+    <t>くるしめた</t>
+  </si>
+  <si>
+    <t>离开</t>
+  </si>
+  <si>
+    <t>黙って立ち去る</t>
+  </si>
+  <si>
+    <t>go away in slience</t>
+  </si>
+  <si>
+    <t>立ち去る</t>
+  </si>
+  <si>
+    <t>たちさる</t>
+  </si>
+  <si>
+    <t>重新挺立，恢复</t>
+  </si>
+  <si>
+    <t>敵に立ち直るすきを与えない</t>
+  </si>
+  <si>
+    <t>不给敌人以喘息的机会</t>
+  </si>
+  <si>
+    <t>立ち直る</t>
+  </si>
+  <si>
+    <t>たちなおる</t>
+  </si>
+  <si>
+    <t>划船，蹬自行车</t>
+  </si>
+  <si>
+    <t>じてんしゃをこいて</t>
+  </si>
+  <si>
+    <t>cycling</t>
+  </si>
+  <si>
+    <t>漕ぐ</t>
+  </si>
+  <si>
+    <t>こぐ</t>
+  </si>
+  <si>
+    <t>漕いで</t>
+  </si>
+  <si>
+    <t>こいで</t>
+  </si>
+  <si>
+    <t>相信</t>
+  </si>
+  <si>
+    <t>神の存在を信ずる</t>
+  </si>
+  <si>
+    <t>相信神的存在</t>
+  </si>
+  <si>
+    <t>信じる</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>信じて</t>
+  </si>
+  <si>
+    <t>しんじて</t>
+  </si>
+  <si>
+    <t>信じた</t>
+  </si>
+  <si>
+    <t>しんじた</t>
+  </si>
+  <si>
     <t>着く</t>
   </si>
   <si>
@@ -4021,6 +4120,23 @@
     <t>しはらう</t>
   </si>
   <si>
+    <t>出借，贷款，放款</t>
+  </si>
+  <si>
+    <t>図書館が本を貸し出す
+住宅資金を貸し出す</t>
+  </si>
+  <si>
+    <t>图书馆允许出借书
+贷住房资金</t>
+  </si>
+  <si>
+    <t>貸し出す</t>
+  </si>
+  <si>
+    <t>かしだす</t>
+  </si>
+  <si>
     <t>翻滚，跌倒</t>
   </si>
   <si>
@@ -4300,6 +4416,253 @@
     <t>さびた</t>
   </si>
   <si>
+    <t>发热，变热</t>
+  </si>
+  <si>
+    <t>熱する</t>
+  </si>
+  <si>
+    <t>ねっする</t>
+  </si>
+  <si>
+    <t>熱すない</t>
+  </si>
+  <si>
+    <t>ねっすない</t>
+  </si>
+  <si>
+    <t>熱すって</t>
+  </si>
+  <si>
+    <t>ねっすって</t>
+  </si>
+  <si>
+    <t>熱すった</t>
+  </si>
+  <si>
+    <t>ねっすった</t>
+  </si>
+  <si>
+    <t>覚める
+醒める</t>
+  </si>
+  <si>
+    <t>变冷</t>
+  </si>
+  <si>
+    <t>冷める</t>
+  </si>
+  <si>
+    <t>さめる</t>
+  </si>
+  <si>
+    <t>冷めない</t>
+  </si>
+  <si>
+    <t>さめない</t>
+  </si>
+  <si>
+    <t>冷めて</t>
+  </si>
+  <si>
+    <t>さめて</t>
+  </si>
+  <si>
+    <t>冷めた</t>
+  </si>
+  <si>
+    <t>さめた</t>
+  </si>
+  <si>
+    <t>使物体发声，敲响，广为人知</t>
+  </si>
+  <si>
+    <t>鳴らす</t>
+  </si>
+  <si>
+    <t>ならす</t>
+  </si>
+  <si>
+    <t>鳴らさない</t>
+  </si>
+  <si>
+    <t>ならさない</t>
+  </si>
+  <si>
+    <t>鳴らして</t>
+  </si>
+  <si>
+    <t>ならして</t>
+  </si>
+  <si>
+    <t>鳴らした</t>
+  </si>
+  <si>
+    <t>ならした</t>
+  </si>
+  <si>
+    <t>満たす</t>
+  </si>
+  <si>
+    <t>混乱，不太平</t>
+  </si>
+  <si>
+    <t>乱れる</t>
+  </si>
+  <si>
+    <t>みだれる</t>
+  </si>
+  <si>
+    <t>乱れない</t>
+  </si>
+  <si>
+    <t>みだれない</t>
+  </si>
+  <si>
+    <t>乱れて</t>
+  </si>
+  <si>
+    <t>みだれて</t>
+  </si>
+  <si>
+    <t>乱れた</t>
+  </si>
+  <si>
+    <t>みだれた</t>
+  </si>
+  <si>
+    <t>充满，填满</t>
+  </si>
+  <si>
+    <t>みたす</t>
+  </si>
+  <si>
+    <t>満たさない</t>
+  </si>
+  <si>
+    <t>みたさない</t>
+  </si>
+  <si>
+    <t>満たして</t>
+  </si>
+  <si>
+    <t>みたして</t>
+  </si>
+  <si>
+    <t>満たした</t>
+  </si>
+  <si>
+    <t>みたした</t>
+  </si>
+  <si>
+    <t>膨胀</t>
+  </si>
+  <si>
+    <t>膨らむ</t>
+  </si>
+  <si>
+    <t>ふくらむ</t>
+  </si>
+  <si>
+    <t>膨らまない</t>
+  </si>
+  <si>
+    <t>ふくらまない</t>
+  </si>
+  <si>
+    <t>膨らんて</t>
+  </si>
+  <si>
+    <t>ふくらんて</t>
+  </si>
+  <si>
+    <t>增加，增多</t>
+  </si>
+  <si>
+    <t>加わる</t>
+  </si>
+  <si>
+    <t>くわわる</t>
+  </si>
+  <si>
+    <t>加わらない</t>
+  </si>
+  <si>
+    <t>くわわらない</t>
+  </si>
+  <si>
+    <t>加わって</t>
+  </si>
+  <si>
+    <t>くわわって</t>
+  </si>
+  <si>
+    <t>加わった</t>
+  </si>
+  <si>
+    <t>くわわった</t>
+  </si>
+  <si>
+    <t>飞越</t>
+  </si>
+  <si>
+    <t>飛行機で太平洋を飛び越える</t>
+  </si>
+  <si>
+    <t>坐飞机飞过太平洋</t>
+  </si>
+  <si>
+    <t>飛び越える</t>
+  </si>
+  <si>
+    <t>とびこえる</t>
+  </si>
+  <si>
+    <t>飛び越えて</t>
+  </si>
+  <si>
+    <t>とびこえて</t>
+  </si>
+  <si>
+    <t>飛び越えた</t>
+  </si>
+  <si>
+    <t>とびこえた</t>
+  </si>
+  <si>
+    <t>迫近</t>
+  </si>
+  <si>
+    <t>間近に迫る「まぢかに」</t>
+  </si>
+  <si>
+    <t>迫在眉睫</t>
+  </si>
+  <si>
+    <t>迫る</t>
+  </si>
+  <si>
+    <t>せまる</t>
+  </si>
+  <si>
+    <t>迫らない</t>
+  </si>
+  <si>
+    <t>せまらない</t>
+  </si>
+  <si>
+    <t>迫って</t>
+  </si>
+  <si>
+    <t>せまって</t>
+  </si>
+  <si>
+    <t>迫った</t>
+  </si>
+  <si>
+    <t>せまった</t>
+  </si>
+  <si>
     <t>誓う</t>
   </si>
   <si>
@@ -5116,6 +5479,99 @@
     <t>かりた</t>
   </si>
   <si>
+    <t>击败</t>
+  </si>
+  <si>
+    <t>議論で相手を負かす</t>
+  </si>
+  <si>
+    <t>拼接辩论打败对方</t>
+  </si>
+  <si>
+    <t>負かす</t>
+  </si>
+  <si>
+    <t>まかす</t>
+  </si>
+  <si>
+    <t>给予</t>
+  </si>
+  <si>
+    <t>敵に立ち直るスキを与えない</t>
+  </si>
+  <si>
+    <t>与えない</t>
+  </si>
+  <si>
+    <t>あたえない</t>
+  </si>
+  <si>
+    <t>炫耀</t>
+  </si>
+  <si>
+    <t>誇る</t>
+  </si>
+  <si>
+    <t>ほこる</t>
+  </si>
+  <si>
+    <t>誇らない</t>
+  </si>
+  <si>
+    <t>ほこらない</t>
+  </si>
+  <si>
+    <t>誇って</t>
+  </si>
+  <si>
+    <t>ほこって</t>
+  </si>
+  <si>
+    <t>誇った</t>
+  </si>
+  <si>
+    <t>ほこった</t>
+  </si>
+  <si>
+    <t>禁止</t>
+  </si>
+  <si>
+    <t>ここで喫煙を禁ずる</t>
+  </si>
+  <si>
+    <t>这里禁止吸烟</t>
+  </si>
+  <si>
+    <t>禁ずる</t>
+  </si>
+  <si>
+    <t>きんずる</t>
+  </si>
+  <si>
+    <t>禁じます</t>
+  </si>
+  <si>
+    <t>きんじます</t>
+  </si>
+  <si>
+    <t>禁じない</t>
+  </si>
+  <si>
+    <t>きんじない</t>
+  </si>
+  <si>
+    <t>禁ずして</t>
+  </si>
+  <si>
+    <t>きんずして</t>
+  </si>
+  <si>
+    <t>禁ずした</t>
+  </si>
+  <si>
+    <t>きんずした</t>
+  </si>
+  <si>
     <t>支える</t>
   </si>
   <si>
@@ -5249,6 +5705,39 @@
   </si>
   <si>
     <t>さけた</t>
+  </si>
+  <si>
+    <t>袭击，侵袭</t>
+  </si>
+  <si>
+    <t>嵐に襲われる</t>
+  </si>
+  <si>
+    <t>遭受暴风雨的侵袭</t>
+  </si>
+  <si>
+    <t>襲う</t>
+  </si>
+  <si>
+    <t>おそう</t>
+  </si>
+  <si>
+    <t>襲わない</t>
+  </si>
+  <si>
+    <t>おそわない</t>
+  </si>
+  <si>
+    <t>襲って</t>
+  </si>
+  <si>
+    <t>おそって</t>
+  </si>
+  <si>
+    <t>襲った</t>
+  </si>
+  <si>
+    <t>おそった</t>
   </si>
   <si>
     <t>見る</t>
@@ -6543,6 +7032,27 @@
     <t>はなした</t>
   </si>
   <si>
+    <t>抑制，压制</t>
+  </si>
+  <si>
+    <t>病気の広がるを抑える</t>
+  </si>
+  <si>
+    <t>控制病情蔓延</t>
+  </si>
+  <si>
+    <t>抑えて</t>
+  </si>
+  <si>
+    <t>おさえて</t>
+  </si>
+  <si>
+    <t>抑えた</t>
+  </si>
+  <si>
+    <t>おさえた</t>
+  </si>
+  <si>
     <t>集中，解决，做完</t>
   </si>
   <si>
@@ -6804,6 +7314,33 @@
     <t>はがす</t>
   </si>
   <si>
+    <t>剝がして</t>
+  </si>
+  <si>
+    <t>はがして</t>
+  </si>
+  <si>
+    <t>拉拽</t>
+  </si>
+  <si>
+    <t>引っ張る</t>
+  </si>
+  <si>
+    <t>ひっぱる</t>
+  </si>
+  <si>
+    <t>引っ張って</t>
+  </si>
+  <si>
+    <t>ひっぱって</t>
+  </si>
+  <si>
+    <t>引っ張った</t>
+  </si>
+  <si>
+    <t>ひっぱった</t>
+  </si>
+  <si>
     <t>支撑</t>
   </si>
   <si>
@@ -6928,6 +7465,39 @@
   </si>
   <si>
     <t>混じらない</t>
+  </si>
+  <si>
+    <t>不同，有差异</t>
+  </si>
+  <si>
+    <t>その点が他の人と異なるところだ</t>
+  </si>
+  <si>
+    <t>那一点是和别人不同的地方</t>
+  </si>
+  <si>
+    <t>異なる</t>
+  </si>
+  <si>
+    <t>ことなる</t>
+  </si>
+  <si>
+    <t>異ならない</t>
+  </si>
+  <si>
+    <t>ことならない</t>
+  </si>
+  <si>
+    <t>異なって</t>
+  </si>
+  <si>
+    <t>ことなって</t>
+  </si>
+  <si>
+    <t>異なった</t>
+  </si>
+  <si>
+    <t>ことなった</t>
   </si>
 </sst>
 </file>
@@ -6940,7 +7510,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7022,6 +7592,12 @@
       <sz val="10"/>
       <color rgb="FF3D454C"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -7525,16 +8101,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7543,119 +8116,122 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7686,13 +8262,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8065,14 +8645,14 @@
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="20"/>
+      <c r="K1" s="22"/>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
@@ -9617,9 +10197,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AE93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
+    <col min="2" max="2" width="29.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="67.7777777777778" customWidth="1"/>
     <col min="4" max="4" width="40.2222222222222" customWidth="1"/>
     <col min="5" max="7" width="11.6666666666667" customWidth="1"/>
@@ -10603,11 +11184,11 @@
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
       <c r="H33" s="2" t="s">
         <v>575</v>
       </c>
@@ -10625,11 +11206,11 @@
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="20" t="s">
         <v>580</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
       <c r="E34" s="2" t="s">
         <v>571</v>
       </c>
@@ -10644,11 +11225,11 @@
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="20" t="s">
         <v>583</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
       <c r="E35" s="2" t="s">
         <v>571</v>
       </c>
@@ -10675,11 +11256,11 @@
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="20" t="s">
         <v>590</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
       <c r="E36" s="2" t="s">
         <v>571</v>
       </c>
@@ -10706,11 +11287,11 @@
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="20" t="s">
         <v>597</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
       <c r="E37" s="2" t="s">
         <v>571</v>
       </c>
@@ -10740,11 +11321,11 @@
       <c r="A38" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="20" t="s">
         <v>605</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
       <c r="E38" s="2" t="s">
         <v>571</v>
       </c>
@@ -10759,11 +11340,11 @@
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="20" t="s">
         <v>605</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
       <c r="E39" s="2" t="s">
         <v>571</v>
       </c>
@@ -10781,7 +11362,7 @@
       <c r="A40" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="20" t="s">
         <v>605</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -10799,7 +11380,7 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2"/>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="20" t="s">
         <v>610</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -10829,7 +11410,7 @@
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2"/>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="20" t="s">
         <v>617</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -10865,7 +11446,7 @@
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="A43" s="2"/>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="20" t="s">
         <v>626</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -10903,11 +11484,11 @@
       <c r="A44" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="20" t="s">
         <v>636</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
       <c r="E44" s="2" t="s">
         <v>571</v>
       </c>
@@ -10937,11 +11518,11 @@
       <c r="A45" t="s">
         <v>637</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="20" t="s">
         <v>636</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
       <c r="E45" s="2" t="s">
         <v>571</v>
       </c>
@@ -10968,11 +11549,11 @@
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="20" t="s">
         <v>648</v>
       </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
       <c r="E46" s="2" t="s">
         <v>571</v>
       </c>
@@ -11002,11 +11583,11 @@
       <c r="A47" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="20" t="s">
         <v>655</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
       <c r="E47" s="2" t="s">
         <v>571</v>
       </c>
@@ -11039,13 +11620,13 @@
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="20" t="s">
         <v>664</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="20" t="s">
         <v>666</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -11074,11 +11655,11 @@
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="20" t="s">
         <v>673</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="18"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="2" t="s">
         <v>564</v>
       </c>
@@ -11097,13 +11678,13 @@
       <c r="P49" s="2"/>
     </row>
     <row r="50" ht="18" spans="1:16">
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="20" t="s">
         <v>676</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>678</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -11135,11 +11716,11 @@
       <c r="A51" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="20" t="s">
         <v>686</v>
       </c>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
       <c r="E51" s="2" t="s">
         <v>571</v>
       </c>
@@ -11207,7 +11788,7 @@
       <c r="A53" t="s">
         <v>701</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="20" t="s">
         <v>702</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -11227,7 +11808,7 @@
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="20" t="s">
         <v>706</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -11262,7 +11843,7 @@
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="20" t="s">
         <v>715</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -11288,7 +11869,7 @@
       <c r="A56" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="20" t="s">
         <v>720</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -11465,7 +12046,7 @@
       <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G62" s="21" t="s">
         <v>757</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -11691,7 +12272,7 @@
       <c r="B70" t="s">
         <v>808</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="21" t="s">
         <v>809</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -12195,6 +12776,145 @@
       </c>
       <c r="P88" t="s">
         <v>908</v>
+      </c>
+    </row>
+    <row r="89" ht="18" spans="1:16">
+      <c r="B89" t="s">
+        <v>909</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>910</v>
+      </c>
+      <c r="H89" t="s">
+        <v>911</v>
+      </c>
+      <c r="M89" t="s">
+        <v>912</v>
+      </c>
+      <c r="N89" t="s">
+        <v>913</v>
+      </c>
+      <c r="O89" t="s">
+        <v>914</v>
+      </c>
+      <c r="P89" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="90" ht="18" spans="1:16">
+      <c r="B90" t="s">
+        <v>916</v>
+      </c>
+      <c r="C90" t="s">
+        <v>917</v>
+      </c>
+      <c r="D90" t="s">
+        <v>918</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>919</v>
+      </c>
+      <c r="H90" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="91" ht="18" spans="1:16">
+      <c r="B91" t="s">
+        <v>921</v>
+      </c>
+      <c r="C91" t="s">
+        <v>922</v>
+      </c>
+      <c r="D91" t="s">
+        <v>923</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>924</v>
+      </c>
+      <c r="H91" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="92" ht="18" spans="1:16">
+      <c r="B92" t="s">
+        <v>926</v>
+      </c>
+      <c r="C92" t="s">
+        <v>927</v>
+      </c>
+      <c r="D92" t="s">
+        <v>928</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>929</v>
+      </c>
+      <c r="H92" t="s">
+        <v>930</v>
+      </c>
+      <c r="M92" t="s">
+        <v>931</v>
+      </c>
+      <c r="N92" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="93" ht="18" spans="1:16">
+      <c r="B93" t="s">
+        <v>933</v>
+      </c>
+      <c r="C93" t="s">
+        <v>934</v>
+      </c>
+      <c r="D93" t="s">
+        <v>935</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>936</v>
+      </c>
+      <c r="H93" t="s">
+        <v>937</v>
+      </c>
+      <c r="M93" t="s">
+        <v>938</v>
+      </c>
+      <c r="N93" t="s">
+        <v>939</v>
+      </c>
+      <c r="O93" t="s">
+        <v>940</v>
+      </c>
+      <c r="P93" t="s">
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -12220,7 +12940,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE64"/>
+  <dimension ref="A1:AE74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -12376,28 +13096,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>909</v>
+        <v>942</v>
       </c>
       <c r="H3" t="s">
-        <v>910</v>
+        <v>943</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>911</v>
+        <v>944</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>912</v>
+        <v>945</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>913</v>
+        <v>946</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>914</v>
+        <v>947</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>915</v>
+        <v>948</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>916</v>
+        <v>949</v>
       </c>
     </row>
     <row r="4" ht="31.2" customHeight="1" spans="2:31">
@@ -12407,10 +13127,10 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>917</v>
-      </c>
-      <c r="F4" s="16"/>
+      <c r="E4" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="F4" s="17"/>
       <c r="G4" s="2" t="s">
         <v>443</v>
       </c>
@@ -12426,73 +13146,73 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>918</v>
+        <v>951</v>
       </c>
       <c r="F5" t="s">
-        <v>919</v>
+        <v>952</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="H5" t="s">
-        <v>921</v>
+        <v>954</v>
       </c>
       <c r="I5" t="s">
-        <v>922</v>
+        <v>955</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>923</v>
+        <v>956</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>924</v>
+        <v>957</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>925</v>
+        <v>958</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>926</v>
+        <v>959</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>927</v>
+        <v>960</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>928</v>
+        <v>961</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>929</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" ht="18" spans="2:31">
       <c r="C6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>930</v>
+        <v>963</v>
       </c>
       <c r="H6" t="s">
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>932</v>
+        <v>965</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>933</v>
+        <v>966</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>934</v>
+        <v>967</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>935</v>
+        <v>968</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>926</v>
+        <v>959</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>936</v>
+        <v>969</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>928</v>
+        <v>961</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>937</v>
+        <v>970</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>550</v>
@@ -12501,16 +13221,16 @@
         <v>551</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>938</v>
+        <v>971</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>939</v>
+        <v>972</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>940</v>
+        <v>973</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>941</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" ht="18" spans="2:31">
@@ -12521,7 +13241,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>942</v>
+        <v>975</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>728</v>
@@ -12530,16 +13250,16 @@
         <v>729</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>943</v>
+        <v>976</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>944</v>
+        <v>977</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>945</v>
+        <v>978</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>730</v>
@@ -12568,16 +13288,16 @@
         <v>729</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>947</v>
+        <v>980</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>944</v>
+        <v>977</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>948</v>
+        <v>981</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>735</v>
@@ -12600,37 +13320,37 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>949</v>
+        <v>982</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>950</v>
+        <v>983</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>951</v>
+        <v>984</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>952</v>
+        <v>985</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>953</v>
+        <v>986</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>954</v>
+        <v>987</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>956</v>
+        <v>989</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>957</v>
+        <v>990</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>958</v>
+        <v>991</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>959</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:31">
@@ -12641,38 +13361,38 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>960</v>
+        <v>993</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>962</v>
+        <v>995</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>963</v>
+        <v>996</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>965</v>
+        <v>998</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>966</v>
+        <v>999</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>967</v>
+        <v>1000</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>968</v>
+        <v>1001</v>
       </c>
       <c r="O10" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="P10" t="s">
-        <v>970</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="11" ht="18" spans="2:31">
@@ -12683,16 +13403,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>971</v>
+        <v>1004</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -12703,7 +13423,7 @@
     </row>
     <row r="12" ht="18" spans="2:31">
       <c r="B12" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>49</v>
@@ -12714,25 +13434,25 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>979</v>
+        <v>1012</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" spans="2:31">
       <c r="B13" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>49</v>
@@ -12741,39 +13461,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>982</v>
+        <v>1015</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>983</v>
+        <v>1016</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>984</v>
+        <v>1017</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>985</v>
+        <v>1018</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>986</v>
+        <v>1019</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>988</v>
+        <v>1021</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>989</v>
+        <v>1022</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>990</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="18" spans="2:31">
       <c r="B14" t="s">
-        <v>991</v>
+        <v>1024</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>222</v>
@@ -12782,21 +13502,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>992</v>
+        <v>1025</v>
       </c>
       <c r="F14" t="s">
-        <v>993</v>
+        <v>1026</v>
       </c>
       <c r="G14" t="s">
-        <v>994</v>
+        <v>1027</v>
       </c>
       <c r="H14" t="s">
-        <v>995</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="15" ht="18" spans="2:31">
       <c r="B15" t="s">
-        <v>996</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>49</v>
@@ -12805,18 +13525,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>997</v>
+        <v>1030</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>998</v>
+        <v>1031</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>999</v>
+        <v>1032</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1000</v>
+        <v>1033</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -12825,7 +13545,7 @@
     </row>
     <row r="16" ht="18" spans="2:31">
       <c r="B16" t="s">
-        <v>1001</v>
+        <v>1034</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>49</v>
@@ -12834,10 +13554,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1002</v>
+        <v>1035</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1003</v>
+        <v>1036</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>374</v>
@@ -12848,7 +13568,7 @@
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="B17" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>49</v>
@@ -12857,19 +13577,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1005</v>
+        <v>1038</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>1006</v>
+        <v>1039</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1007</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="B18" t="s">
-        <v>1008</v>
+        <v>1041</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>49</v>
@@ -12880,15 +13600,15 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>1009</v>
+        <v>1042</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1010</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1011</v>
+        <v>1044</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>49</v>
@@ -12899,15 +13619,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>1012</v>
+        <v>1045</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1013</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>49</v>
@@ -12916,10 +13636,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1016</v>
+        <v>1049</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>347</v>
@@ -12936,21 +13656,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="B22" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -12959,24 +13679,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1022</v>
+        <v>1055</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1023</v>
+        <v>1056</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1024</v>
+        <v>1057</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1025</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="B23" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -12987,30 +13707,30 @@
       <c r="E23" s="2"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1029</v>
+        <v>1062</v>
       </c>
       <c r="M23" t="s">
-        <v>1030</v>
+        <v>1063</v>
       </c>
       <c r="N23" t="s">
-        <v>1031</v>
+        <v>1064</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="B24" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>49</v>
@@ -13021,30 +13741,30 @@
       <c r="E24" s="2"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1034</v>
+        <v>1067</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1035</v>
+        <v>1068</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1036</v>
+        <v>1069</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1037</v>
+        <v>1070</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1038</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="B25" t="s">
-        <v>1039</v>
+        <v>1072</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>49</v>
@@ -13053,28 +13773,28 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1040</v>
+        <v>1073</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1041</v>
+        <v>1074</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1042</v>
+        <v>1075</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1043</v>
+        <v>1076</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1044</v>
+        <v>1077</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1045</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>1046</v>
+        <v>1079</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>49</v>
@@ -13083,27 +13803,27 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1047</v>
+        <v>1080</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1048</v>
+        <v>1081</v>
       </c>
       <c r="M26" t="s">
-        <v>1049</v>
+        <v>1082</v>
       </c>
       <c r="N26" t="s">
-        <v>1050</v>
+        <v>1083</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1051</v>
+        <v>1084</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1052</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1053</v>
+        <v>1086</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -13112,21 +13832,21 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1054</v>
+        <v>1087</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1055</v>
+        <v>1088</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1056</v>
+        <v>1089</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1057</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1058</v>
+        <v>1091</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>49</v>
@@ -13135,33 +13855,33 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1059</v>
+        <v>1092</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1060</v>
+        <v>1093</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1061</v>
+        <v>1094</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1062</v>
+        <v>1095</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1063</v>
+        <v>1096</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1064</v>
+        <v>1097</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1066</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1067</v>
+        <v>1100</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>49</v>
@@ -13170,39 +13890,39 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1068</v>
+        <v>1101</v>
       </c>
       <c r="F29" t="s">
-        <v>1069</v>
+        <v>1102</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1070</v>
+        <v>1103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1071</v>
+        <v>1104</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1072</v>
+        <v>1105</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1073</v>
+        <v>1106</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1074</v>
+        <v>1107</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1075</v>
+        <v>1108</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1077</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1078</v>
+        <v>1111</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>222</v>
@@ -13211,21 +13931,21 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1079</v>
+        <v>1112</v>
       </c>
       <c r="F30" t="s">
-        <v>1080</v>
+        <v>1113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1081</v>
+        <v>1114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1082</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>49</v>
@@ -13234,15 +13954,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>49</v>
@@ -13251,33 +13971,33 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1088</v>
+        <v>1121</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1090</v>
+        <v>1123</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1091</v>
+        <v>1124</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1093</v>
+        <v>1126</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1094</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1095</v>
+        <v>1128</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -13286,39 +14006,39 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1096</v>
+        <v>1129</v>
       </c>
       <c r="F33" t="s">
-        <v>1097</v>
+        <v>1130</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1098</v>
+        <v>1131</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1099</v>
+        <v>1132</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1100</v>
+        <v>1133</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1101</v>
+        <v>1134</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1102</v>
+        <v>1135</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1103</v>
+        <v>1136</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1104</v>
+        <v>1137</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1105</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1106</v>
+        <v>1139</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>49</v>
@@ -13327,33 +14047,33 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1107</v>
+        <v>1140</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1108</v>
+        <v>1141</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1109</v>
+        <v>1142</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1110</v>
+        <v>1143</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1111</v>
+        <v>1144</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1112</v>
+        <v>1145</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1113</v>
+        <v>1146</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1114</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1115</v>
+        <v>1148</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>49</v>
@@ -13361,34 +14081,34 @@
       <c r="D35">
         <v>1</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>1117</v>
+      <c r="G35" s="18" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>1150</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>1118</v>
+        <v>1151</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1119</v>
+        <v>1152</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1120</v>
+        <v>1153</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1121</v>
+        <v>1154</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1122</v>
+        <v>1155</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1123</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1124</v>
+        <v>1157</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>49</v>
@@ -13397,39 +14117,39 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F36" t="s">
-        <v>1126</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>1128</v>
+        <v>1159</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>1161</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1129</v>
+        <v>1162</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1130</v>
+        <v>1163</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1131</v>
+        <v>1164</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1133</v>
+        <v>1166</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1134</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1115</v>
+        <v>1148</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
@@ -13437,34 +14157,34 @@
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>1135</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>1136</v>
+      <c r="G37" s="18" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>1169</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1137</v>
+        <v>1170</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1138</v>
+        <v>1171</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1139</v>
+        <v>1172</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1140</v>
+        <v>1173</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1141</v>
+        <v>1174</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1142</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1143</v>
+        <v>1176</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>815</v>
@@ -13473,16 +14193,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>1144</v>
+        <v>1177</v>
       </c>
       <c r="F38" t="s">
-        <v>1145</v>
+        <v>1178</v>
       </c>
       <c r="G38" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>1147</v>
+        <v>1179</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>1180</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -13493,10 +14213,10 @@
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="A39" t="s">
-        <v>1148</v>
+        <v>1181</v>
       </c>
       <c r="B39" t="s">
-        <v>1149</v>
+        <v>1182</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>49</v>
@@ -13504,34 +14224,34 @@
       <c r="D39">
         <v>1</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="18" t="s">
         <v>701</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>1150</v>
+      <c r="H39" s="18" t="s">
+        <v>1183</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>1151</v>
+        <v>1184</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1152</v>
+        <v>1185</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1153</v>
+        <v>1186</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1154</v>
+        <v>1187</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1155</v>
+        <v>1188</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1156</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1157</v>
+        <v>1190</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>49</v>
@@ -13539,11 +14259,11 @@
       <c r="D40">
         <v>2</v>
       </c>
-      <c r="G40" s="17" t="s">
-        <v>1158</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>1159</v>
+      <c r="G40" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>1192</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -13554,10 +14274,10 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1160</v>
+        <v>1193</v>
       </c>
       <c r="B41" t="s">
-        <v>1161</v>
+        <v>1194</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>49</v>
@@ -13566,18 +14286,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1163</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="B42" t="s">
-        <v>1164</v>
+        <v>1197</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -13586,10 +14306,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1160</v>
+        <v>1193</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1165</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
@@ -13600,10 +14320,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1166</v>
+        <v>1199</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1165</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
@@ -13614,33 +14334,33 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1167</v>
+        <v>1200</v>
       </c>
       <c r="F44" t="s">
-        <v>1168</v>
+        <v>1201</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1169</v>
+        <v>1202</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1170</v>
+        <v>1203</v>
       </c>
       <c r="I44" t="s">
-        <v>1170</v>
+        <v>1203</v>
       </c>
       <c r="K44" t="s">
-        <v>1171</v>
+        <v>1204</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1172</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="B45" t="s">
-        <v>1174</v>
+        <v>1207</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>49</v>
@@ -13649,34 +14369,34 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1175</v>
+        <v>1208</v>
       </c>
       <c r="F45" t="s">
-        <v>1176</v>
+        <v>1209</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1177</v>
+        <v>1210</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1178</v>
+        <v>1211</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1179</v>
+        <v>1212</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1180</v>
+        <v>1213</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1181</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" t="s">
-        <v>1182</v>
+        <v>1215</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -13685,33 +14405,33 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1183</v>
+        <v>1216</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1184</v>
+        <v>1217</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1185</v>
+        <v>1218</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>1186</v>
+        <v>1219</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1187</v>
+        <v>1220</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1188</v>
+        <v>1221</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1189</v>
+        <v>1222</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1190</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="B47" t="s">
-        <v>1191</v>
+        <v>1224</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>49</v>
@@ -13720,15 +14440,15 @@
         <v>2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1192</v>
+        <v>1225</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1193</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1194</v>
+        <v>1227</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>49</v>
@@ -13737,30 +14457,30 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1195</v>
+        <v>1228</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1196</v>
+        <v>1229</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1197</v>
+        <v>1230</v>
       </c>
       <c r="N48" t="s">
-        <v>1198</v>
+        <v>1231</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1199</v>
+        <v>1232</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1200</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" t="s">
-        <v>1201</v>
+        <v>1234</v>
       </c>
       <c r="B49" t="s">
-        <v>1202</v>
+        <v>1235</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>815</v>
@@ -13769,33 +14489,33 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1203</v>
+        <v>1236</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1204</v>
+        <v>1237</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1205</v>
+        <v>1238</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1205</v>
+        <v>1238</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1206</v>
+        <v>1239</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1207</v>
+        <v>1240</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1208</v>
+        <v>1241</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1208</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="B50" t="s">
-        <v>1209</v>
+        <v>1242</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>49</v>
@@ -13804,36 +14524,36 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>1210</v>
+        <v>1243</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1211</v>
+        <v>1244</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1212</v>
+        <v>1245</v>
       </c>
       <c r="K50" t="s">
-        <v>1213</v>
+        <v>1246</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1214</v>
+        <v>1247</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1215</v>
+        <v>1248</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1216</v>
+        <v>1249</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1217</v>
+        <v>1250</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1218</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="B51" t="s">
-        <v>1219</v>
+        <v>1252</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>222</v>
@@ -13842,21 +14562,21 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1220</v>
+        <v>1253</v>
       </c>
       <c r="F51" t="s">
-        <v>1221</v>
+        <v>1254</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1222</v>
+        <v>1255</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1223</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="B52" t="s">
-        <v>1219</v>
+        <v>1252</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -13865,178 +14585,160 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>1224</v>
+        <v>1257</v>
       </c>
       <c r="F52" t="s">
-        <v>1225</v>
+        <v>1258</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1226</v>
+        <v>1259</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="53" ht="18" spans="1:16">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="53" ht="27.6" spans="1:16">
       <c r="B53" t="s">
-        <v>1228</v>
+        <v>1261</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
+      <c r="E53" s="19" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>1263</v>
+      </c>
       <c r="G53" s="2" t="s">
-        <v>1229</v>
+        <v>1264</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="M53" t="s">
-        <v>1233</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>1236</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="B54" t="s">
-        <v>1237</v>
+        <v>1266</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>815</v>
+        <v>49</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1239</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>1240</v>
+        <v>1267</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1241</v>
+        <v>1268</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>1270</v>
       </c>
       <c r="M54" t="s">
-        <v>1242</v>
+        <v>1271</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1243</v>
+        <v>1272</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1244</v>
+        <v>1273</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1245</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="B55" t="s">
-        <v>1246</v>
+        <v>1275</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>49</v>
+        <v>815</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
-      <c r="G55" t="s">
-        <v>1247</v>
+      <c r="E55" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>1278</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1248</v>
+        <v>1279</v>
+      </c>
+      <c r="M55" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>1283</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:16">
+      <c r="B56" t="s">
+        <v>1284</v>
+      </c>
       <c r="C56" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="F56" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>1251</v>
+      <c r="G56" t="s">
+        <v>1285</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1252</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>1254</v>
-      </c>
-      <c r="O56" t="s">
-        <v>1255</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
-      <c r="B57" t="s">
-        <v>1256</v>
-      </c>
       <c r="C57" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
+      <c r="E57" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1288</v>
+      </c>
       <c r="G57" s="2" t="s">
-        <v>1257</v>
+        <v>1289</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1263</v>
+        <v>1291</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>1266</v>
+        <v>1292</v>
+      </c>
+      <c r="O57" t="s">
+        <v>1293</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="B58" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>
@@ -14045,228 +14747,591 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1268</v>
+        <v>1295</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1258</v>
+        <v>1296</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1269</v>
+        <v>1297</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1260</v>
+        <v>1298</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1270</v>
+        <v>1299</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1262</v>
+        <v>1300</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1271</v>
+        <v>1301</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1264</v>
+        <v>1302</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1272</v>
+        <v>1303</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1266</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="B59" t="s">
-        <v>1273</v>
+        <v>1305</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>815</v>
+        <v>49</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1274</v>
+        <v>1306</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1275</v>
+        <v>1296</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1276</v>
+        <v>1307</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>1278</v>
+        <v>1308</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>1279</v>
+        <v>1300</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1280</v>
+        <v>1309</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1282</v>
+        <v>1310</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="B60" t="s">
-        <v>1284</v>
+        <v>1311</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>815</v>
       </c>
       <c r="D60">
-        <v>2</v>
-      </c>
-      <c r="G60" t="s">
-        <v>1285</v>
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>1312</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1286</v>
+        <v>1313</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1287</v>
+        <v>1314</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1288</v>
+        <v>1315</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>1289</v>
+        <v>1316</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1290</v>
+        <v>1317</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1291</v>
+        <v>1318</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1292</v>
+        <v>1319</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1293</v>
+        <v>1320</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1294</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="B61" t="s">
-        <v>1295</v>
+        <v>1322</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1296</v>
-      </c>
-      <c r="F61" t="s">
-        <v>1297</v>
+        <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>1298</v>
-      </c>
-      <c r="H61" t="s">
-        <v>1299</v>
+        <v>1323</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>1332</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" t="s">
-        <v>1300</v>
+        <v>1333</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>815</v>
+        <v>49</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1335</v>
       </c>
       <c r="G62" t="s">
-        <v>1301</v>
+        <v>1336</v>
       </c>
       <c r="H62" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62" t="s">
-        <v>1303</v>
-      </c>
-      <c r="L62" t="s">
-        <v>1304</v>
-      </c>
-      <c r="M62" t="s">
-        <v>1305</v>
-      </c>
-      <c r="N62" t="s">
-        <v>1306</v>
-      </c>
-      <c r="O62" t="s">
-        <v>1307</v>
-      </c>
-      <c r="P62" t="s">
-        <v>1308</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
       <c r="B63" t="s">
-        <v>1309</v>
+        <v>1338</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>49</v>
+        <v>815</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>1310</v>
+        <v>1339</v>
       </c>
       <c r="H63" t="s">
-        <v>1311</v>
+        <v>1340</v>
+      </c>
+      <c r="K63" t="s">
+        <v>1341</v>
+      </c>
+      <c r="L63" t="s">
+        <v>1342</v>
+      </c>
+      <c r="M63" t="s">
+        <v>1343</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1344</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1345</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="B64" t="s">
-        <v>1312</v>
+        <v>1347</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="65" ht="18" spans="1:16">
+      <c r="B65" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D65">
         <v>2</v>
       </c>
-      <c r="G64" t="s">
-        <v>1313</v>
-      </c>
-      <c r="H64" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K64" t="s">
-        <v>1315</v>
-      </c>
-      <c r="L64" t="s">
-        <v>1316</v>
-      </c>
-      <c r="M64" t="s">
-        <v>1317</v>
-      </c>
-      <c r="N64" t="s">
-        <v>1318</v>
-      </c>
-      <c r="O64" t="s">
-        <v>1319</v>
-      </c>
-      <c r="P64" t="s">
-        <v>1320</v>
+      <c r="G65" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1352</v>
+      </c>
+      <c r="K65" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M65" t="s">
+        <v>1355</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1356</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1357</v>
+      </c>
+      <c r="P65" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="66" ht="18" spans="1:16">
+      <c r="B66" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K66" t="s">
+        <v>1362</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M66" t="s">
+        <v>1364</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1365</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1366</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="67" ht="27.6" spans="1:16">
+      <c r="A67" s="17" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K67" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L67" t="s">
+        <v>1373</v>
+      </c>
+      <c r="M67" t="s">
+        <v>1374</v>
+      </c>
+      <c r="N67" t="s">
+        <v>1375</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="B68" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C68" t="s">
+        <v>222</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K68" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L68" t="s">
+        <v>1382</v>
+      </c>
+      <c r="M68" t="s">
+        <v>1383</v>
+      </c>
+      <c r="N68" t="s">
+        <v>1384</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="69" ht="18" spans="1:16">
+      <c r="A69" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1390</v>
+      </c>
+      <c r="K69" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1392</v>
+      </c>
+      <c r="M69" t="s">
+        <v>1393</v>
+      </c>
+      <c r="N69" t="s">
+        <v>1394</v>
+      </c>
+      <c r="O69" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C70" t="s">
+        <v>222</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1398</v>
+      </c>
+      <c r="K70" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L70" t="s">
+        <v>1400</v>
+      </c>
+      <c r="M70" t="s">
+        <v>1401</v>
+      </c>
+      <c r="N70" t="s">
+        <v>1402</v>
+      </c>
+      <c r="O70" t="s">
+        <v>1403</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="71" ht="18" spans="1:16">
+      <c r="B71" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1409</v>
+      </c>
+      <c r="M71" t="s">
+        <v>1410</v>
+      </c>
+      <c r="N71" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="72" ht="18" spans="1:16">
+      <c r="B72" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K72" t="s">
+        <v>1415</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M72" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N72" t="s">
+        <v>1418</v>
+      </c>
+      <c r="O72" t="s">
+        <v>1419</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="B73" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C73" t="s">
+        <v>222</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1425</v>
+      </c>
+      <c r="M73" t="s">
+        <v>1426</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1427</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1428</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="74" ht="18" spans="1:16">
+      <c r="B74" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K74" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1436</v>
+      </c>
+      <c r="M74" t="s">
+        <v>1437</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1438</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1439</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -14292,7 +15357,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" ht="18" spans="1:31">
@@ -14439,28 +15504,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1321</v>
+        <v>1441</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1322</v>
+        <v>1442</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1323</v>
+        <v>1443</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1324</v>
+        <v>1444</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1325</v>
+        <v>1445</v>
       </c>
       <c r="N3" t="s">
-        <v>1326</v>
+        <v>1446</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1327</v>
+        <v>1447</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1328</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -14471,28 +15536,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1329</v>
+        <v>1449</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1330</v>
+        <v>1450</v>
       </c>
       <c r="I4" t="s">
-        <v>1331</v>
+        <v>1451</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1332</v>
+        <v>1452</v>
       </c>
       <c r="M4" t="s">
-        <v>1333</v>
+        <v>1453</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1334</v>
+        <v>1454</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1335</v>
+        <v>1455</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1336</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -14503,60 +15568,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1337</v>
+        <v>1457</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1338</v>
+        <v>1458</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1339</v>
+        <v>1459</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1340</v>
+        <v>1460</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1341</v>
+        <v>1461</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1342</v>
+        <v>1462</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1343</v>
+        <v>1463</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1344</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1345</v>
+        <v>1465</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1346</v>
+        <v>1466</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1338</v>
+        <v>1458</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1347</v>
+        <v>1467</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1340</v>
+        <v>1460</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1348</v>
+        <v>1468</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1342</v>
+        <v>1462</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1349</v>
+        <v>1469</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1344</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -14564,21 +15629,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1350</v>
+        <v>1470</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1351</v>
+        <v>1471</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1352</v>
+        <v>1472</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1353</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1354</v>
+        <v>1474</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -14587,15 +15652,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1355</v>
+        <v>1475</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1356</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1354</v>
+        <v>1474</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -14612,7 +15677,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1357</v>
+        <v>1477</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -14621,36 +15686,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1358</v>
+        <v>1478</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1359</v>
+        <v>1479</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1360</v>
+        <v>1480</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1361</v>
+        <v>1481</v>
       </c>
       <c r="M10" t="s">
-        <v>1362</v>
+        <v>1482</v>
       </c>
       <c r="N10" t="s">
-        <v>1363</v>
+        <v>1483</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1364</v>
+        <v>1484</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1365</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1366</v>
+        <v>1486</v>
       </c>
       <c r="B11" t="s">
-        <v>1367</v>
+        <v>1487</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -14659,42 +15724,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1368</v>
+        <v>1488</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1369</v>
+        <v>1489</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1370</v>
+        <v>1490</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1371</v>
+        <v>1491</v>
       </c>
       <c r="M11" t="s">
-        <v>1372</v>
+        <v>1492</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1373</v>
+        <v>1493</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1374</v>
+        <v>1494</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1375</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1368</v>
+        <v>1488</v>
       </c>
       <c r="B12" t="s">
-        <v>1376</v>
+        <v>1496</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1377</v>
+        <v>1497</v>
       </c>
       <c r="D12" t="s">
-        <v>1378</v>
+        <v>1498</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -14703,33 +15768,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1366</v>
+        <v>1486</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1379</v>
+        <v>1499</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1380</v>
+        <v>1500</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1381</v>
+        <v>1501</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1382</v>
+        <v>1502</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1383</v>
+        <v>1503</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1384</v>
+        <v>1504</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1385</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1386</v>
+        <v>1506</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -14738,39 +15803,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1387</v>
+        <v>1507</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1388</v>
+        <v>1508</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1389</v>
+        <v>1509</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1390</v>
+        <v>1510</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1391</v>
+        <v>1511</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1392</v>
+        <v>1512</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1393</v>
+        <v>1513</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1394</v>
+        <v>1514</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1395</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1396</v>
+        <v>1516</v>
       </c>
       <c r="B14" t="s">
-        <v>1397</v>
+        <v>1517</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -14779,22 +15844,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1398</v>
+        <v>1518</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1401</v>
+        <v>1521</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1402</v>
+        <v>1522</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1403</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -14806,33 +15871,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1404</v>
+        <v>1524</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1405</v>
+        <v>1525</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1406</v>
+        <v>1526</v>
       </c>
       <c r="N15" t="s">
-        <v>1407</v>
+        <v>1527</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1408</v>
+        <v>1528</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1409</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1410</v>
+        <v>1530</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1411</v>
+        <v>1531</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1412</v>
+        <v>1532</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -14841,18 +15906,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1413</v>
+        <v>1533</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1414</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1415</v>
+        <v>1535</v>
       </c>
       <c r="B17" t="s">
-        <v>1416</v>
+        <v>1536</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -14861,30 +15926,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1417</v>
+        <v>1537</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1418</v>
+        <v>1538</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1419</v>
+        <v>1539</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1420</v>
+        <v>1540</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1421</v>
+        <v>1541</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1422</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1423</v>
+        <v>1543</v>
       </c>
       <c r="B18" t="s">
-        <v>1424</v>
+        <v>1544</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -14893,27 +15958,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1425</v>
+        <v>1545</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1426</v>
+        <v>1546</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1427</v>
+        <v>1547</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1428</v>
+        <v>1548</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1429</v>
+        <v>1549</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1430</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1431</v>
+        <v>1551</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -14922,30 +15987,30 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1423</v>
+        <v>1543</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1432</v>
+        <v>1552</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1433</v>
+        <v>1553</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1434</v>
+        <v>1554</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1435</v>
+        <v>1555</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1436</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>1437</v>
+        <v>1557</v>
       </c>
       <c r="B20" t="s">
-        <v>1438</v>
+        <v>1558</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -14954,40 +16019,40 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1439</v>
+        <v>1559</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1440</v>
+        <v>1560</v>
       </c>
       <c r="K20" t="s">
-        <v>1441</v>
+        <v>1561</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1442</v>
+        <v>1562</v>
       </c>
       <c r="M20" t="s">
-        <v>1443</v>
+        <v>1563</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1444</v>
+        <v>1564</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1445</v>
+        <v>1565</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1446</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
-        <v>1447</v>
+        <v>1567</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1448</v>
+        <v>1568</v>
       </c>
       <c r="D21" t="s">
-        <v>1449</v>
+        <v>1569</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -14996,34 +16061,34 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1450</v>
+        <v>1570</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1451</v>
+        <v>1571</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1452</v>
+        <v>1572</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1453</v>
+        <v>1573</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1454</v>
+        <v>1574</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1455</v>
+        <v>1575</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1456</v>
+        <v>1576</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1457</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1458</v>
+        <v>1578</v>
       </c>
       <c r="C22" s="2"/>
       <c r="E22" t="s">
@@ -15033,33 +16098,33 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1459</v>
+        <v>1579</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1460</v>
+        <v>1580</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1461</v>
+        <v>1581</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1462</v>
+        <v>1582</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1463</v>
+        <v>1583</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1464</v>
+        <v>1584</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1465</v>
+        <v>1585</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1466</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="B23" t="s">
-        <v>1467</v>
+        <v>1587</v>
       </c>
       <c r="E23" t="s">
         <v>222</v>
@@ -15068,27 +16133,27 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1468</v>
+        <v>1588</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1469</v>
+        <v>1589</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1470</v>
+        <v>1590</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1471</v>
+        <v>1591</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1472</v>
+        <v>1592</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1473</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1439</v>
+        <v>1559</v>
       </c>
       <c r="E24" t="s">
         <v>49</v>
@@ -15097,33 +16162,33 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1437</v>
+        <v>1557</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1474</v>
+        <v>1594</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1475</v>
+        <v>1595</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1476</v>
+        <v>1596</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1477</v>
+        <v>1597</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1478</v>
+        <v>1598</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1479</v>
+        <v>1599</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1480</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="B25" t="s">
-        <v>1481</v>
+        <v>1601</v>
       </c>
       <c r="E25" t="s">
         <v>222</v>
@@ -15132,27 +16197,27 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1482</v>
+        <v>1602</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1483</v>
+        <v>1603</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1484</v>
+        <v>1604</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1485</v>
+        <v>1605</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1486</v>
+        <v>1606</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1487</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1488</v>
+        <v>1608</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -15161,36 +16226,36 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1489</v>
+        <v>1609</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1490</v>
+        <v>1610</v>
       </c>
       <c r="I26" t="s">
-        <v>1491</v>
+        <v>1611</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1492</v>
+        <v>1612</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1493</v>
+        <v>1613</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1494</v>
+        <v>1614</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1495</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1496</v>
+        <v>1616</v>
       </c>
       <c r="C27" t="s">
-        <v>1497</v>
+        <v>1617</v>
       </c>
       <c r="D27" t="s">
-        <v>1498</v>
+        <v>1618</v>
       </c>
       <c r="E27" t="s">
         <v>49</v>
@@ -15199,27 +16264,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1499</v>
+        <v>1619</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1500</v>
+        <v>1620</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1501</v>
+        <v>1621</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1502</v>
+        <v>1622</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1503</v>
+        <v>1623</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1504</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1505</v>
+        <v>1625</v>
       </c>
       <c r="E28" t="s">
         <v>222</v>
@@ -15228,27 +16293,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1506</v>
+        <v>1626</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1507</v>
+        <v>1627</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1508</v>
+        <v>1628</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1509</v>
+        <v>1629</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1510</v>
+        <v>1630</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1511</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1512</v>
+        <v>1632</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -15257,10 +16322,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1513</v>
+        <v>1633</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1514</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
@@ -15271,33 +16336,33 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1515</v>
+        <v>1635</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1516</v>
+        <v>1636</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1517</v>
+        <v>1637</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1518</v>
+        <v>1638</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>1519</v>
+        <v>1639</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1520</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1521</v>
+        <v>1641</v>
       </c>
       <c r="C31" t="s">
-        <v>1522</v>
+        <v>1642</v>
       </c>
       <c r="D31" t="s">
-        <v>1523</v>
+        <v>1643</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
@@ -15306,21 +16371,21 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1524</v>
+        <v>1644</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1525</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1526</v>
+        <v>1646</v>
       </c>
       <c r="C32" t="s">
-        <v>1527</v>
+        <v>1647</v>
       </c>
       <c r="D32" t="s">
-        <v>1528</v>
+        <v>1648</v>
       </c>
       <c r="E32" t="s">
         <v>222</v>
@@ -15329,33 +16394,33 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1529</v>
+        <v>1649</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1530</v>
+        <v>1650</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1531</v>
+        <v>1651</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1532</v>
+        <v>1652</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1533</v>
+        <v>1653</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1534</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1535</v>
+        <v>1655</v>
       </c>
       <c r="C33" t="s">
-        <v>1536</v>
+        <v>1656</v>
       </c>
       <c r="D33" t="s">
-        <v>1537</v>
+        <v>1657</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>815</v>
@@ -15364,30 +16429,30 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1538</v>
+        <v>1658</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1539</v>
+        <v>1659</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1540</v>
+        <v>1660</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1541</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>1542</v>
+        <v>1662</v>
       </c>
       <c r="B34" t="s">
-        <v>1543</v>
+        <v>1663</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1544</v>
+        <v>1664</v>
       </c>
       <c r="D34" t="s">
-        <v>1545</v>
+        <v>1665</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>222</v>
@@ -15396,33 +16461,33 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1546</v>
+        <v>1666</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1547</v>
+        <v>1667</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1548</v>
+        <v>1668</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1549</v>
+        <v>1669</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1550</v>
+        <v>1670</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1551</v>
+        <v>1671</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1552</v>
+        <v>1672</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1553</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1554</v>
+        <v>1674</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -15431,27 +16496,27 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1555</v>
+        <v>1675</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1556</v>
+        <v>1676</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1557</v>
+        <v>1677</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1558</v>
+        <v>1678</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1559</v>
+        <v>1679</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1560</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1561</v>
+        <v>1681</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -15460,33 +16525,33 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1562</v>
+        <v>1682</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1563</v>
+        <v>1683</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1564</v>
+        <v>1684</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1565</v>
+        <v>1685</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1566</v>
+        <v>1686</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1567</v>
+        <v>1687</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1568</v>
+        <v>1688</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1569</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1570</v>
+        <v>1690</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>815</v>
@@ -15495,15 +16560,15 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>1571</v>
+        <v>1691</v>
       </c>
       <c r="H37" t="s">
-        <v>1572</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1573</v>
+        <v>1693</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -15512,39 +16577,39 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1574</v>
+        <v>1694</v>
       </c>
       <c r="H38" t="s">
-        <v>1575</v>
+        <v>1695</v>
       </c>
       <c r="K38" t="s">
-        <v>1576</v>
+        <v>1696</v>
       </c>
       <c r="L38" t="s">
-        <v>1577</v>
+        <v>1697</v>
       </c>
       <c r="M38" t="s">
-        <v>1578</v>
+        <v>1698</v>
       </c>
       <c r="N38" t="s">
-        <v>1579</v>
+        <v>1699</v>
       </c>
       <c r="O38" t="s">
-        <v>1580</v>
+        <v>1700</v>
       </c>
       <c r="P38" t="s">
-        <v>1581</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1582</v>
+        <v>1702</v>
       </c>
       <c r="C39" t="s">
-        <v>1583</v>
+        <v>1703</v>
       </c>
       <c r="D39" t="s">
-        <v>1584</v>
+        <v>1704</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
@@ -15553,29 +16618,166 @@
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>1585</v>
+        <v>1705</v>
       </c>
       <c r="H39" t="s">
-        <v>1586</v>
+        <v>1706</v>
       </c>
       <c r="K39" t="s">
-        <v>1587</v>
+        <v>1707</v>
       </c>
       <c r="L39" t="s">
-        <v>1588</v>
+        <v>1708</v>
       </c>
       <c r="M39" t="s">
-        <v>1589</v>
+        <v>1709</v>
       </c>
       <c r="N39" t="s">
-        <v>1590</v>
+        <v>1710</v>
       </c>
       <c r="O39" t="s">
-        <v>1591</v>
+        <v>1711</v>
       </c>
       <c r="P39" t="s">
-        <v>1592</v>
-      </c>
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="40" ht="18" spans="1:16">
+      <c r="B40" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="B41" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D41" t="s">
+        <v>923</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K41" t="s">
+        <v>1720</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="42" ht="18" spans="1:16">
+      <c r="B42" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1723</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1724</v>
+      </c>
+      <c r="K42" t="s">
+        <v>1725</v>
+      </c>
+      <c r="L42" t="s">
+        <v>1726</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N42" t="s">
+        <v>1728</v>
+      </c>
+      <c r="O42" t="s">
+        <v>1729</v>
+      </c>
+      <c r="P42" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="43" ht="18" spans="1:16">
+      <c r="B43" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1734</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1735</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1736</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1737</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1738</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1739</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1740</v>
+      </c>
+      <c r="N43" t="s">
+        <v>1741</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1742</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="45" ht="16.8" spans="1:16">
+      <c r="I45" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -15600,8 +16802,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5"/>
+  <dimension ref="A1:AF7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
     <col min="3" max="4" width="22.6666666666667" customWidth="1"/>
@@ -15749,16 +16951,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1593</v>
+        <v>1744</v>
       </c>
       <c r="B3" t="s">
-        <v>1594</v>
+        <v>1745</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1595</v>
+        <v>1746</v>
       </c>
       <c r="D3" t="s">
-        <v>1596</v>
+        <v>1747</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -15767,31 +16969,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1597</v>
+        <v>1748</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1598</v>
+        <v>1749</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1599</v>
+        <v>1750</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1600</v>
+        <v>1751</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1601</v>
+        <v>1752</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1602</v>
+        <v>1753</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1603</v>
+        <v>1754</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1604</v>
+        <v>1755</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -15801,42 +17003,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1605</v>
+        <v>1756</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1606</v>
+        <v>1757</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1605</v>
+        <v>1756</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1606</v>
+        <v>1757</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1607</v>
+        <v>1758</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1608</v>
+        <v>1759</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1609</v>
+        <v>1760</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1610</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1611</v>
+        <v>1762</v>
       </c>
       <c r="B4" t="s">
-        <v>1612</v>
+        <v>1763</v>
       </c>
       <c r="C4" t="s">
-        <v>1613</v>
+        <v>1764</v>
       </c>
       <c r="D4" t="s">
-        <v>1614</v>
+        <v>1765</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -15845,37 +17047,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1615</v>
+        <v>1766</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1616</v>
+        <v>1767</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1617</v>
+        <v>1768</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1618</v>
+        <v>1769</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1619</v>
+        <v>1770</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1620</v>
+        <v>1771</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1621</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1612</v>
+        <v>1763</v>
       </c>
       <c r="C5" t="s">
-        <v>1622</v>
+        <v>1773</v>
       </c>
       <c r="D5" t="s">
-        <v>1614</v>
+        <v>1765</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -15884,54 +17086,95 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1623</v>
+        <v>1774</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1624</v>
+        <v>1775</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1625</v>
+        <v>1776</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1626</v>
+        <v>1777</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1627</v>
+        <v>1778</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1628</v>
+        <v>1779</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1629</v>
+        <v>1780</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1630</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1631</v>
+        <v>1782</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1632</v>
+        <v>1783</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1633</v>
+        <v>1784</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1634</v>
+        <v>1785</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1635</v>
+        <v>1786</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1636</v>
+        <v>1787</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1637</v>
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="B7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1799</v>
       </c>
     </row>
   </sheetData>
@@ -15957,7 +17200,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE87"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" customWidth="1"/>
@@ -16113,30 +17356,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1638</v>
+        <v>1800</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1639</v>
+        <v>1801</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1640</v>
+        <v>1802</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1641</v>
+        <v>1803</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1642</v>
+        <v>1804</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1643</v>
+        <v>1805</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1644</v>
+        <v>1806</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1645</v>
+        <v>1807</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -16146,16 +17389,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1646</v>
+        <v>1808</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1647</v>
+        <v>1809</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1648</v>
+        <v>1810</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1649</v>
+        <v>1811</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -16170,34 +17413,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1650</v>
+        <v>1812</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1651</v>
+        <v>1813</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1652</v>
+        <v>1814</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1653</v>
+        <v>1815</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1654</v>
+        <v>1816</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1655</v>
+        <v>1817</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1656</v>
+        <v>1818</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1657</v>
+        <v>1819</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1658</v>
+        <v>1820</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1659</v>
+        <v>1821</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -16217,7 +17460,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1660</v>
+        <v>1822</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -16226,34 +17469,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1661</v>
+        <v>1823</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1662</v>
+        <v>1824</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1663</v>
+        <v>1825</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1664</v>
+        <v>1826</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1665</v>
+        <v>1827</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1666</v>
+        <v>1828</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1667</v>
+        <v>1829</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1668</v>
+        <v>1830</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1669</v>
+        <v>1831</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1670</v>
+        <v>1832</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -16263,16 +17506,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1671</v>
+        <v>1833</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1672</v>
+        <v>1834</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1673</v>
+        <v>1835</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1674</v>
+        <v>1836</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -16281,13 +17524,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1675</v>
+        <v>1837</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1676</v>
+        <v>1838</v>
       </c>
       <c r="D6" t="s">
-        <v>1677</v>
+        <v>1839</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -16296,30 +17539,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1678</v>
+        <v>1840</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1679</v>
+        <v>1841</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1680</v>
+        <v>1842</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1681</v>
+        <v>1843</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1682</v>
+        <v>1844</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1683</v>
+        <v>1845</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1684</v>
+        <v>1846</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1685</v>
+        <v>1847</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -16331,10 +17574,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1686</v>
+        <v>1848</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1687</v>
+        <v>1849</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -16343,13 +17586,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1675</v>
+        <v>1837</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1688</v>
+        <v>1850</v>
       </c>
       <c r="D7" t="s">
-        <v>1677</v>
+        <v>1839</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -16358,34 +17601,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1686</v>
+        <v>1848</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1687</v>
+        <v>1849</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1689</v>
+        <v>1851</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1690</v>
+        <v>1852</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1691</v>
+        <v>1853</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1692</v>
+        <v>1854</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1693</v>
+        <v>1855</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1694</v>
+        <v>1856</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1695</v>
+        <v>1857</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1696</v>
+        <v>1858</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -16405,7 +17648,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1697</v>
+        <v>1859</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -16414,75 +17657,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1698</v>
+        <v>1860</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1699</v>
+        <v>1861</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1700</v>
+        <v>1862</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1701</v>
+        <v>1863</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1702</v>
+        <v>1864</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1703</v>
+        <v>1865</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1704</v>
+        <v>1866</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1705</v>
+        <v>1867</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1706</v>
+        <v>1868</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1707</v>
+        <v>1869</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1708</v>
+        <v>1870</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1709</v>
+        <v>1871</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1710</v>
+        <v>1872</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1711</v>
+        <v>1873</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1712</v>
+        <v>1874</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1607</v>
+        <v>1758</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1608</v>
+        <v>1759</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1605</v>
+        <v>1756</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1606</v>
+        <v>1757</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1607</v>
+        <v>1758</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1608</v>
+        <v>1759</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1609</v>
+        <v>1760</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1610</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -16490,7 +17733,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1713</v>
+        <v>1875</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -16499,10 +17742,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1714</v>
+        <v>1876</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1715</v>
+        <v>1877</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -16535,7 +17778,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1716</v>
+        <v>1878</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -16544,10 +17787,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1717</v>
+        <v>1879</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1718</v>
+        <v>1880</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -16576,7 +17819,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1719</v>
+        <v>1881</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -16585,37 +17828,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1720</v>
+        <v>1882</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1721</v>
+        <v>1883</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1722</v>
+        <v>1884</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1723</v>
+        <v>1885</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1724</v>
+        <v>1886</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1725</v>
+        <v>1887</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1726</v>
+        <v>1888</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1727</v>
+        <v>1889</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1728</v>
+        <v>1890</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1729</v>
+        <v>1891</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1730</v>
+        <v>1892</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -16628,10 +17871,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1731</v>
+        <v>1893</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1732</v>
+        <v>1894</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -16639,7 +17882,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1733</v>
+        <v>1895</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -16648,20 +17891,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1734</v>
+        <v>1896</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1735</v>
+        <v>1897</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1736</v>
+        <v>1898</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1737</v>
+        <v>1899</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -16683,10 +17926,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1738</v>
+        <v>1900</v>
       </c>
       <c r="B13" t="s">
-        <v>1739</v>
+        <v>1901</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -16695,20 +17938,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1740</v>
+        <v>1902</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1741</v>
+        <v>1903</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1742</v>
+        <v>1904</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1743</v>
+        <v>1905</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -16730,10 +17973,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1740</v>
+        <v>1902</v>
       </c>
       <c r="B14" t="s">
-        <v>1744</v>
+        <v>1906</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16742,20 +17985,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1738</v>
+        <v>1900</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1745</v>
+        <v>1907</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1746</v>
+        <v>1908</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1737</v>
+        <v>1899</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -16777,10 +18020,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1747</v>
+        <v>1909</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1748</v>
+        <v>1910</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -16790,39 +18033,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1749</v>
+        <v>1911</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1750</v>
+        <v>1912</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1751</v>
+        <v>1913</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1752</v>
+        <v>1914</v>
       </c>
       <c r="K15" t="s">
-        <v>1753</v>
+        <v>1915</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1754</v>
+        <v>1916</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1755</v>
+        <v>1917</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1756</v>
+        <v>1918</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1757</v>
+        <v>1919</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1758</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1759</v>
+        <v>1921</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16831,34 +18074,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1760</v>
+        <v>1922</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1761</v>
+        <v>1923</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1762</v>
+        <v>1924</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1763</v>
+        <v>1925</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1764</v>
+        <v>1926</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1765</v>
+        <v>1927</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1766</v>
+        <v>1928</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1767</v>
+        <v>1929</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1768</v>
+        <v>1930</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1769</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -16869,7 +18112,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1770</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -16880,7 +18123,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1771</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -16891,10 +18134,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1772</v>
+        <v>1934</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1773</v>
+        <v>1935</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -16906,18 +18149,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1774</v>
+        <v>1936</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1773</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1775</v>
+        <v>1937</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1776</v>
+        <v>1938</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -16927,42 +18170,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1777</v>
+        <v>1939</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1778</v>
+        <v>1940</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1779</v>
+        <v>1941</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1780</v>
+        <v>1942</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1781</v>
+        <v>1943</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1782</v>
+        <v>1944</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1783</v>
+        <v>1945</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1784</v>
+        <v>1946</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1785</v>
+        <v>1947</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1786</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1787</v>
+        <v>1949</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1788</v>
+        <v>1950</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -16972,39 +18215,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1789</v>
+        <v>1951</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1778</v>
+        <v>1940</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1780</v>
+        <v>1942</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1790</v>
+        <v>1952</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1782</v>
+        <v>1944</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1791</v>
+        <v>1953</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1784</v>
+        <v>1946</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1792</v>
+        <v>1954</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1786</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>1793</v>
+        <v>1955</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1794</v>
+        <v>1956</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -17014,27 +18257,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1795</v>
+        <v>1957</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1796</v>
+        <v>1958</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1797</v>
+        <v>1959</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1798</v>
+        <v>1960</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1799</v>
+        <v>1961</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1800</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>1801</v>
+        <v>1963</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -17043,39 +18286,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1802</v>
+        <v>1964</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1803</v>
+        <v>1965</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1804</v>
+        <v>1966</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1805</v>
+        <v>1967</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1806</v>
+        <v>1968</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1807</v>
+        <v>1969</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1808</v>
+        <v>1970</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1809</v>
+        <v>1971</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1810</v>
+        <v>1972</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1811</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>1801</v>
+        <v>1963</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -17084,10 +18327,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1812</v>
+        <v>1974</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1813</v>
+        <v>1975</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -17100,7 +18343,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>1814</v>
+        <v>1976</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -17109,26 +18352,26 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1815</v>
+        <v>1977</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>1816</v>
+        <v>1978</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1817</v>
+        <v>1979</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1818</v>
+        <v>1980</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1819</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -17139,32 +18382,32 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>1820</v>
+        <v>1982</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1817</v>
+        <v>1979</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1821</v>
+        <v>1983</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1819</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
       <c r="B28" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1822</v>
+        <v>1984</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -17174,39 +18417,39 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1823</v>
+        <v>1985</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1824</v>
+        <v>1986</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1825</v>
+        <v>1987</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1826</v>
+        <v>1988</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1827</v>
+        <v>1989</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1828</v>
+        <v>1990</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1829</v>
+        <v>1991</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1830</v>
+        <v>1992</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1831</v>
+        <v>1993</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1832</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
       <c r="B29" t="s">
-        <v>1058</v>
+        <v>1091</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>222</v>
@@ -17215,27 +18458,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1833</v>
+        <v>1995</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1834</v>
+        <v>1996</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1835</v>
+        <v>1997</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1836</v>
+        <v>1998</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1837</v>
+        <v>1999</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1838</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>1839</v>
+        <v>2001</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -17244,27 +18487,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1840</v>
+        <v>2002</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1841</v>
+        <v>2003</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1842</v>
+        <v>2004</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1843</v>
+        <v>2005</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>1844</v>
+        <v>2006</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1845</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>1846</v>
+        <v>2008</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -17273,27 +18516,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1847</v>
+        <v>2009</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1848</v>
+        <v>2010</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1849</v>
+        <v>2011</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1850</v>
+        <v>2012</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1851</v>
+        <v>2013</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1852</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>1853</v>
+        <v>2015</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -17308,21 +18551,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1854</v>
+        <v>2016</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1855</v>
+        <v>2017</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1856</v>
+        <v>2018</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1857</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1858</v>
+        <v>2020</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -17331,22 +18574,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1859</v>
+        <v>2021</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1860</v>
+        <v>2022</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1861</v>
+        <v>2023</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1862</v>
+        <v>2024</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1863</v>
+        <v>2025</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1864</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -17356,30 +18599,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1865</v>
+        <v>2027</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1866</v>
+        <v>2028</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1867</v>
+        <v>2029</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1868</v>
+        <v>2030</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1869</v>
+        <v>2031</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1870</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1871</v>
+        <v>2033</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -17388,10 +18631,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1872</v>
+        <v>2034</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1873</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -17402,30 +18645,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1874</v>
+        <v>2036</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1875</v>
+        <v>2037</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1876</v>
+        <v>2038</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1877</v>
+        <v>2039</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1878</v>
+        <v>2040</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1879</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1880</v>
+        <v>2042</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1881</v>
+        <v>2043</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -17434,30 +18677,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1882</v>
+        <v>2044</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1883</v>
+        <v>2045</v>
       </c>
       <c r="M38" t="s">
-        <v>1884</v>
+        <v>2046</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1885</v>
+        <v>2047</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>1886</v>
+        <v>2048</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1887</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1888</v>
+        <v>2050</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1889</v>
+        <v>2051</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -17467,18 +18710,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1890</v>
+        <v>2052</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1891</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1892</v>
+        <v>2054</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1893</v>
+        <v>2055</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -17488,22 +18731,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1678</v>
+        <v>1840</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1679</v>
+        <v>1841</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1682</v>
+        <v>1844</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1683</v>
+        <v>1845</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1684</v>
+        <v>1846</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1685</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -17516,15 +18759,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1894</v>
+        <v>2056</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1895</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>1896</v>
+        <v>2058</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -17533,54 +18776,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1897</v>
+        <v>2059</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1898</v>
+        <v>2060</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1899</v>
+        <v>2061</v>
       </c>
       <c r="N42" t="s">
-        <v>1900</v>
+        <v>2062</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>1901</v>
+        <v>2063</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>1902</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1903</v>
+        <v>2065</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1904</v>
+        <v>2066</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1898</v>
+        <v>2060</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1905</v>
+        <v>2067</v>
       </c>
       <c r="N43" t="s">
-        <v>1900</v>
+        <v>2062</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>1906</v>
+        <v>2068</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>1902</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1907</v>
+        <v>2069</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -17589,30 +18832,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1908</v>
+        <v>2070</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1898</v>
+        <v>2060</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1909</v>
+        <v>2071</v>
       </c>
       <c r="N44" t="s">
-        <v>1900</v>
+        <v>2062</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>1910</v>
+        <v>2072</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>1902</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>1911</v>
+        <v>2073</v>
       </c>
       <c r="C45" t="s">
-        <v>1912</v>
+        <v>2074</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -17621,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1913</v>
+        <v>2075</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -17629,10 +18872,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>1914</v>
+        <v>2076</v>
       </c>
       <c r="B46" t="s">
-        <v>1915</v>
+        <v>2077</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -17641,24 +18884,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1916</v>
+        <v>2078</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1917</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>1918</v>
+        <v>2080</v>
       </c>
       <c r="B47" t="s">
-        <v>1919</v>
+        <v>2081</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1920</v>
+        <v>2082</v>
       </c>
       <c r="D47" t="s">
-        <v>1921</v>
+        <v>2083</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -17667,33 +18910,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1922</v>
+        <v>2084</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1923</v>
+        <v>2085</v>
       </c>
       <c r="M47" t="s">
-        <v>1924</v>
+        <v>2086</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1925</v>
+        <v>2087</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>1926</v>
+        <v>2088</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>1927</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1928</v>
+        <v>2090</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1929</v>
+        <v>2091</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>1930</v>
+        <v>2092</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -17702,18 +18945,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1931</v>
+        <v>2093</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1932</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="B49" t="s">
-        <v>1933</v>
+        <v>2095</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -17722,28 +18965,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1934</v>
+        <v>2096</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1935</v>
+        <v>2097</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1936</v>
+        <v>2098</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1937</v>
+        <v>2099</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1938</v>
+        <v>2100</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1939</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>1933</v>
+        <v>2095</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -17752,30 +18995,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1940</v>
+        <v>2102</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1935</v>
+        <v>2097</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1941</v>
+        <v>2103</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1937</v>
+        <v>2099</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1942</v>
+        <v>2104</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1939</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>1943</v>
+        <v>2105</v>
       </c>
       <c r="B51" t="s">
-        <v>1944</v>
+        <v>2106</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -17784,34 +19027,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1396</v>
+        <v>1516</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1945</v>
+        <v>2107</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1946</v>
+        <v>2108</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1947</v>
+        <v>2109</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>1948</v>
+        <v>2110</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>1949</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>1950</v>
+        <v>2112</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1951</v>
+        <v>2113</v>
       </c>
       <c r="D52" t="s">
-        <v>1952</v>
+        <v>2114</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -17820,24 +19063,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1894</v>
+        <v>2056</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1895</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>1953</v>
+        <v>2115</v>
       </c>
       <c r="B53" t="s">
-        <v>1954</v>
+        <v>2116</v>
       </c>
       <c r="C53" t="s">
-        <v>1955</v>
+        <v>2117</v>
       </c>
       <c r="D53" t="s">
-        <v>1956</v>
+        <v>2118</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -17846,18 +19089,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1957</v>
+        <v>2119</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1958</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>1959</v>
+        <v>2121</v>
       </c>
       <c r="B54" t="s">
-        <v>1960</v>
+        <v>2122</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -17866,36 +19109,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1358</v>
+        <v>1478</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1359</v>
+        <v>1479</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1362</v>
+        <v>1482</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1961</v>
+        <v>2123</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1364</v>
+        <v>1484</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1365</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>1962</v>
+        <v>2124</v>
       </c>
       <c r="B55" t="s">
-        <v>1963</v>
+        <v>2125</v>
       </c>
       <c r="C55" t="s">
-        <v>1964</v>
+        <v>2126</v>
       </c>
       <c r="D55" t="s">
-        <v>1965</v>
+        <v>2127</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -17904,19 +19147,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1966</v>
+        <v>2128</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1967</v>
+        <v>2129</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1611</v>
+        <v>1762</v>
       </c>
       <c r="B56" t="s">
-        <v>1968</v>
+        <v>2130</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -17925,36 +19168,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1969</v>
+        <v>2131</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1970</v>
+        <v>2132</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1971</v>
+        <v>2133</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1972</v>
+        <v>2134</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>1973</v>
+        <v>2135</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>1974</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>1975</v>
+        <v>2137</v>
       </c>
       <c r="B57" t="s">
-        <v>1976</v>
+        <v>2138</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1977</v>
+        <v>2139</v>
       </c>
       <c r="D57" t="s">
-        <v>1978</v>
+        <v>2140</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -17963,36 +19206,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1611</v>
+        <v>1762</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1979</v>
+        <v>2141</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1980</v>
+        <v>2142</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1981</v>
+        <v>2143</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>1982</v>
+        <v>2144</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1983</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1439</v>
+        <v>1559</v>
       </c>
       <c r="B58" t="s">
-        <v>1984</v>
+        <v>2146</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1985</v>
+        <v>2147</v>
       </c>
       <c r="D58" t="s">
-        <v>1986</v>
+        <v>2148</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -18001,36 +19244,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1962</v>
+        <v>2124</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1987</v>
+        <v>2149</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1988</v>
+        <v>2150</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1989</v>
+        <v>2151</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1990</v>
+        <v>2152</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1991</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1417</v>
+        <v>1537</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1992</v>
+        <v>2154</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1993</v>
+        <v>2155</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1994</v>
+        <v>2156</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -18039,10 +19282,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1992</v>
+        <v>2154</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1995</v>
+        <v>2157</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -18051,16 +19294,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>1962</v>
+        <v>2124</v>
       </c>
       <c r="B60" t="s">
-        <v>1996</v>
+        <v>2158</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1997</v>
+        <v>2159</v>
       </c>
       <c r="D60" t="s">
-        <v>1998</v>
+        <v>2160</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -18069,10 +19312,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1999</v>
+        <v>2161</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2000</v>
+        <v>2162</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -18081,16 +19324,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1425</v>
+        <v>1545</v>
       </c>
       <c r="B61" t="s">
-        <v>2001</v>
+        <v>2163</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2002</v>
+        <v>2164</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2003</v>
+        <v>2165</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -18099,27 +19342,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2004</v>
+        <v>2166</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2005</v>
+        <v>2167</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2006</v>
+        <v>2168</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2007</v>
+        <v>2169</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2008</v>
+        <v>2170</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2009</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2010</v>
+        <v>2172</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -18128,10 +19371,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2011</v>
+        <v>2173</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2012</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -18143,24 +19386,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2013</v>
+        <v>2175</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2012</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>1962</v>
+        <v>2124</v>
       </c>
       <c r="B64" t="s">
-        <v>2014</v>
+        <v>2176</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2015</v>
+        <v>2177</v>
       </c>
       <c r="D64" t="s">
-        <v>2016</v>
+        <v>2178</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -18169,10 +19412,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2017</v>
+        <v>2179</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2018</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -18183,15 +19426,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2019</v>
+        <v>2181</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2018</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2020</v>
+        <v>2182</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -18200,15 +19443,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2021</v>
+        <v>2183</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2022</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2023</v>
+        <v>2185</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -18217,15 +19460,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2024</v>
+        <v>2186</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2025</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2026</v>
+        <v>2188</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -18234,15 +19477,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2027</v>
+        <v>2189</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2028</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2026</v>
+        <v>2188</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -18251,15 +19494,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2029</v>
+        <v>2191</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2028</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2030</v>
+        <v>2192</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -18268,27 +19511,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2031</v>
+        <v>2193</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2032</v>
+        <v>2194</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2033</v>
+        <v>2195</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2034</v>
+        <v>2196</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2035</v>
+        <v>2197</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2036</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2037</v>
+        <v>2199</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -18297,27 +19540,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2038</v>
+        <v>2200</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2039</v>
+        <v>2201</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2040</v>
+        <v>2202</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2041</v>
+        <v>2203</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2042</v>
+        <v>2204</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2043</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2044</v>
+        <v>2206</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -18326,7 +19569,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2045</v>
+        <v>2207</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -18334,7 +19577,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2044</v>
+        <v>2206</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -18343,33 +19586,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2046</v>
+        <v>2208</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2047</v>
+        <v>2209</v>
       </c>
       <c r="N73" t="s">
-        <v>2048</v>
+        <v>2210</v>
       </c>
       <c r="O73" t="s">
-        <v>2049</v>
+        <v>2211</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2050</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>2052</v>
+        <v>2213</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2214</v>
       </c>
       <c r="D74" t="s">
-        <v>2053</v>
+        <v>2215</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -18378,61 +19621,67 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>737</v>
+        <v>2175</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2054</v>
+        <v>2174</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="N74" t="s">
+        <v>2217</v>
+      </c>
+      <c r="O74" t="s">
+        <v>2218</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>2219</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>2056</v>
+        <v>2220</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E75" t="s">
+        <v>222</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>2057</v>
+        <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2058</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E76" t="s">
-        <v>222</v>
+        <v>2224</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>2225</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2060</v>
+        <v>2226</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2061</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>2062</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>2063</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>2064</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>2065</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2066</v>
+        <v>2228</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -18441,15 +19690,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2067</v>
+        <v>2229</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2068</v>
+        <v>2230</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>2234</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2069</v>
+        <v>2235</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -18458,27 +19719,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2070</v>
+        <v>2236</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2071</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>2072</v>
-      </c>
-      <c r="N78" t="s">
-        <v>2073</v>
-      </c>
-      <c r="O78" t="s">
-        <v>2074</v>
-      </c>
-      <c r="P78" s="2" t="s">
-        <v>2075</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2076</v>
+        <v>2238</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -18487,33 +19736,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2077</v>
+        <v>2239</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2078</v>
+        <v>2240</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2079</v>
+        <v>2241</v>
       </c>
       <c r="N79" t="s">
-        <v>2080</v>
+        <v>2242</v>
       </c>
       <c r="O79" t="s">
-        <v>2081</v>
-      </c>
-      <c r="P79" t="s">
-        <v>2082</v>
+        <v>2243</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>2244</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2083</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D80" t="s">
-        <v>2085</v>
+        <v>2245</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -18522,33 +19765,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2086</v>
+        <v>2246</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2087</v>
+        <v>2247</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2088</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>2089</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>2090</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>2091</v>
+        <v>2248</v>
+      </c>
+      <c r="N80" t="s">
+        <v>2249</v>
+      </c>
+      <c r="O80" t="s">
+        <v>2250</v>
+      </c>
+      <c r="P80" t="s">
+        <v>2251</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2092</v>
+        <v>2252</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2093</v>
+        <v>2253</v>
       </c>
       <c r="D81" t="s">
-        <v>2094</v>
+        <v>2254</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -18557,65 +19800,65 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2095</v>
+        <v>2255</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2096</v>
+        <v>2256</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2097</v>
+        <v>2257</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2098</v>
+        <v>2258</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2099</v>
+        <v>2259</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2100</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
-      <c r="A82" s="2" t="s">
-        <v>1650</v>
-      </c>
       <c r="B82" t="s">
-        <v>2101</v>
+        <v>2261</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2263</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2102</v>
+        <v>2264</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2103</v>
+        <v>2265</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2104</v>
+        <v>2266</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2105</v>
+        <v>2267</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2106</v>
+        <v>2268</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2107</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
+      <c r="A83" s="2" t="s">
+        <v>1812</v>
+      </c>
       <c r="B83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="C83" t="s">
-        <v>2109</v>
-      </c>
-      <c r="D83" t="s">
-        <v>2110</v>
+        <v>2270</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -18624,33 +19867,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2111</v>
+        <v>2271</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2112</v>
+        <v>2272</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2113</v>
+        <v>2273</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2114</v>
+        <v>2274</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2115</v>
+        <v>2275</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2116</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2117</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>2118</v>
+        <v>2277</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2279</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -18659,27 +19902,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1890</v>
+        <v>2280</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>1891</v>
+        <v>2281</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2119</v>
+        <v>2282</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2120</v>
+        <v>2283</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2121</v>
+        <v>2284</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2122</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2123</v>
+        <v>2286</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>2287</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -18688,50 +19937,56 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2124</v>
+        <v>2052</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2125</v>
+        <v>2053</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2126</v>
+        <v>2288</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2127</v>
+        <v>2289</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2128</v>
+        <v>2290</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2129</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2130</v>
+        <v>2292</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
       </c>
       <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86" t="s">
-        <v>2131</v>
+        <v>2</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>2293</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2132</v>
+        <v>2294</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>2295</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2133</v>
+        <v>2296</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>2297</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2134</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="B87" t="s">
-        <v>2135</v>
+        <v>2299</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -18739,11 +19994,69 @@
       <c r="F87">
         <v>1</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>2136</v>
+      <c r="G87" t="s">
+        <v>2300</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2137</v>
+        <v>2301</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="88" ht="18" spans="1:16">
+      <c r="B88" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E88" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>2305</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="M88" t="s">
+        <v>2307</v>
+      </c>
+      <c r="N88" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="B89" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E89" t="s">
+        <v>222</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>2310</v>
+      </c>
+      <c r="H89" t="s">
+        <v>2311</v>
+      </c>
+      <c r="M89" t="s">
+        <v>2312</v>
+      </c>
+      <c r="N89" t="s">
+        <v>2313</v>
+      </c>
+      <c r="O89" t="s">
+        <v>2314</v>
+      </c>
+      <c r="P89" t="s">
+        <v>2315</v>
       </c>
     </row>
   </sheetData>
@@ -18769,11 +20082,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="27.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="61.4444444444444" customWidth="1"/>
     <col min="13" max="13" width="14.1111111111111" customWidth="1"/>
     <col min="19" max="19" width="7.66666666666667" customWidth="1"/>
     <col min="20" max="20" width="14.1111111111111" customWidth="1"/>
@@ -18933,16 +20247,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1597</v>
+        <v>1748</v>
       </c>
       <c r="B3" t="s">
-        <v>2138</v>
+        <v>2316</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2139</v>
+        <v>2317</v>
       </c>
       <c r="D3" t="s">
-        <v>2140</v>
+        <v>2318</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -18951,42 +20265,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1593</v>
+        <v>1744</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2141</v>
+        <v>2319</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2142</v>
+        <v>2320</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2143</v>
+        <v>2321</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2144</v>
+        <v>2322</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2145</v>
+        <v>2323</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2146</v>
+        <v>2324</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2147</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2148</v>
+        <v>2326</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2149</v>
+        <v>2327</v>
       </c>
       <c r="D4" t="s">
-        <v>2150</v>
+        <v>2328</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -18995,21 +20309,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2151</v>
+        <v>2329</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2152</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2153</v>
+        <v>2331</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2154</v>
+        <v>2332</v>
       </c>
       <c r="D5" t="s">
-        <v>2155</v>
+        <v>2333</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -19018,33 +20332,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2156</v>
+        <v>2334</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2157</v>
+        <v>2335</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2158</v>
+        <v>2336</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2159</v>
+        <v>2337</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2160</v>
+        <v>2338</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2161</v>
+        <v>2339</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2162</v>
+        <v>2340</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2163</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2164</v>
+        <v>2342</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -19053,62 +20367,115 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2165</v>
+        <v>2343</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2166</v>
+        <v>2344</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2167</v>
+        <v>2345</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2168</v>
+        <v>2346</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2169</v>
+        <v>2347</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2170</v>
+        <v>2348</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2171</v>
+        <v>2349</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2172</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2173</v>
+        <v>2351</v>
+      </c>
+      <c r="E7" t="s">
+        <v>815</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2174</v>
+        <v>2352</v>
       </c>
       <c r="H7" t="s">
-        <v>2175</v>
+        <v>2353</v>
       </c>
       <c r="L7" t="s">
-        <v>2176</v>
+        <v>2354</v>
       </c>
       <c r="M7" t="s">
-        <v>2177</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2173</v>
+        <v>2351</v>
+      </c>
+      <c r="E8" t="s">
+        <v>815</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2178</v>
+        <v>2356</v>
       </c>
       <c r="H8" t="s">
-        <v>2175</v>
+        <v>2353</v>
       </c>
       <c r="L8" t="s">
-        <v>2179</v>
+        <v>2357</v>
       </c>
       <c r="M8" t="s">
-        <v>2177</v>
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:32">
+      <c r="B9" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2361</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2362</v>
+      </c>
+      <c r="L9" t="s">
+        <v>2363</v>
+      </c>
+      <c r="M9" t="s">
+        <v>2364</v>
+      </c>
+      <c r="N9" t="s">
+        <v>2365</v>
+      </c>
+      <c r="O9" t="s">
+        <v>2366</v>
+      </c>
+      <c r="P9" t="s">
+        <v>2367</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>2368</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="2369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="2394">
   <si>
     <r>
       <rPr>
@@ -3065,6 +3065,15 @@
     <t>くるしめた</t>
   </si>
   <si>
+    <t>被打败</t>
+  </si>
+  <si>
+    <t>破れる</t>
+  </si>
+  <si>
+    <t>やぶれる</t>
+  </si>
+  <si>
     <t>离开</t>
   </si>
   <si>
@@ -3141,6 +3150,24 @@
   </si>
   <si>
     <t>しんじた</t>
+  </si>
+  <si>
+    <t>拝む</t>
+  </si>
+  <si>
+    <t>おがむ</t>
+  </si>
+  <si>
+    <t>拝んで</t>
+  </si>
+  <si>
+    <t>おがんで</t>
+  </si>
+  <si>
+    <t>拝んだ</t>
+  </si>
+  <si>
+    <t>おがんだ</t>
   </si>
   <si>
     <t>着く</t>
@@ -4576,6 +4603,44 @@
     <t>ふくらんて</t>
   </si>
   <si>
+    <r>
+      <t>凹陷，退</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>缩</t>
+    </r>
+  </si>
+  <si>
+    <t>ダイエットをして、お腹が少し引っ込んだ</t>
+  </si>
+  <si>
+    <t>减肥后，肚子稍微缩下去了</t>
+  </si>
+  <si>
+    <t>引っ込む</t>
+  </si>
+  <si>
+    <t>ひっこむ</t>
+  </si>
+  <si>
+    <t>引っ込んで</t>
+  </si>
+  <si>
+    <t>ひっこんで</t>
+  </si>
+  <si>
+    <t>引っ込んだ</t>
+  </si>
+  <si>
+    <t>ひっこんだ</t>
+  </si>
+  <si>
     <t>增加，增多</t>
   </si>
   <si>
@@ -5009,6 +5074,27 @@
   </si>
   <si>
     <t>おしえた</t>
+  </si>
+  <si>
+    <t>受教，学习</t>
+  </si>
+  <si>
+    <t>教わる</t>
+  </si>
+  <si>
+    <t>おそわる</t>
+  </si>
+  <si>
+    <t>教わって</t>
+  </si>
+  <si>
+    <t>おそわって</t>
+  </si>
+  <si>
+    <t>教わった</t>
+  </si>
+  <si>
+    <t>おそわった</t>
   </si>
   <si>
     <t>親しむ</t>
@@ -7510,7 +7596,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7774,6 +7860,12 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -8231,7 +8323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8267,9 +8359,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -8645,14 +8734,14 @@
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22" t="s">
+      <c r="I1" s="21"/>
+      <c r="J1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="22"/>
+      <c r="K1" s="21"/>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
@@ -10197,7 +10286,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE93"/>
+  <dimension ref="A1:AE96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="29.8888888888889" customWidth="1"/>
@@ -11184,11 +11273,11 @@
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="19" t="s">
         <v>574</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
       <c r="H33" s="2" t="s">
         <v>575</v>
       </c>
@@ -11206,11 +11295,11 @@
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="19" t="s">
         <v>580</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
       <c r="E34" s="2" t="s">
         <v>571</v>
       </c>
@@ -11225,11 +11314,11 @@
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="19" t="s">
         <v>583</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
       <c r="E35" s="2" t="s">
         <v>571</v>
       </c>
@@ -11256,11 +11345,11 @@
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="19" t="s">
         <v>590</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="2" t="s">
         <v>571</v>
       </c>
@@ -11287,11 +11376,11 @@
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="19" t="s">
         <v>597</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
       <c r="E37" s="2" t="s">
         <v>571</v>
       </c>
@@ -11321,11 +11410,11 @@
       <c r="A38" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="19" t="s">
         <v>605</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
       <c r="E38" s="2" t="s">
         <v>571</v>
       </c>
@@ -11340,11 +11429,11 @@
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="19" t="s">
         <v>605</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="2" t="s">
         <v>571</v>
       </c>
@@ -11362,7 +11451,7 @@
       <c r="A40" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="19" t="s">
         <v>605</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -11380,7 +11469,7 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2"/>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="19" t="s">
         <v>610</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -11410,7 +11499,7 @@
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2"/>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="19" t="s">
         <v>617</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -11446,7 +11535,7 @@
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="A43" s="2"/>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="19" t="s">
         <v>626</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -11484,11 +11573,11 @@
       <c r="A44" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="19" t="s">
         <v>636</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
       <c r="E44" s="2" t="s">
         <v>571</v>
       </c>
@@ -11518,11 +11607,11 @@
       <c r="A45" t="s">
         <v>637</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="19" t="s">
         <v>636</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
       <c r="E45" s="2" t="s">
         <v>571</v>
       </c>
@@ -11549,11 +11638,11 @@
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="19" t="s">
         <v>648</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
       <c r="E46" s="2" t="s">
         <v>571</v>
       </c>
@@ -11583,11 +11672,11 @@
       <c r="A47" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
       <c r="E47" s="2" t="s">
         <v>571</v>
       </c>
@@ -11620,13 +11709,13 @@
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="19" t="s">
         <v>664</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>666</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -11655,11 +11744,11 @@
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="19" t="s">
         <v>673</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="20"/>
+      <c r="D49" s="19"/>
       <c r="E49" s="2" t="s">
         <v>564</v>
       </c>
@@ -11678,13 +11767,13 @@
       <c r="P49" s="2"/>
     </row>
     <row r="50" ht="18" spans="1:16">
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="19" t="s">
         <v>676</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>678</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -11716,11 +11805,11 @@
       <c r="A51" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>686</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
       <c r="E51" s="2" t="s">
         <v>571</v>
       </c>
@@ -11788,7 +11877,7 @@
       <c r="A53" t="s">
         <v>701</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="19" t="s">
         <v>702</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -11808,7 +11897,7 @@
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="19" t="s">
         <v>706</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -11843,7 +11932,7 @@
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="19" t="s">
         <v>715</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -11869,7 +11958,7 @@
       <c r="A56" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="19" t="s">
         <v>720</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -12046,7 +12135,7 @@
       <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="21" t="s">
+      <c r="G62" s="20" t="s">
         <v>757</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -12272,7 +12361,7 @@
       <c r="B70" t="s">
         <v>808</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>809</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -12811,34 +12900,28 @@
       <c r="B90" t="s">
         <v>916</v>
       </c>
-      <c r="C90" t="s">
-        <v>917</v>
-      </c>
-      <c r="D90" t="s">
-        <v>918</v>
-      </c>
       <c r="E90" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H90" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="91" ht="18" spans="1:16">
       <c r="B91" t="s">
+        <v>919</v>
+      </c>
+      <c r="C91" t="s">
+        <v>920</v>
+      </c>
+      <c r="D91" t="s">
         <v>921</v>
-      </c>
-      <c r="C91" t="s">
-        <v>922</v>
-      </c>
-      <c r="D91" t="s">
-        <v>923</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>49</v>
@@ -12847,74 +12930,124 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H91" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:16">
       <c r="B92" t="s">
+        <v>924</v>
+      </c>
+      <c r="C92" t="s">
+        <v>925</v>
+      </c>
+      <c r="D92" t="s">
         <v>926</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
         <v>927</v>
       </c>
-      <c r="D92" t="s">
+      <c r="H92" t="s">
         <v>928</v>
       </c>
-      <c r="E92" s="2" t="s">
+    </row>
+    <row r="93" customFormat="1"/>
+    <row r="94" ht="18" spans="1:16">
+      <c r="B94" t="s">
+        <v>929</v>
+      </c>
+      <c r="C94" t="s">
+        <v>930</v>
+      </c>
+      <c r="D94" t="s">
+        <v>931</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-      <c r="G92" t="s">
-        <v>929</v>
-      </c>
-      <c r="H92" t="s">
-        <v>930</v>
-      </c>
-      <c r="M92" t="s">
-        <v>931</v>
-      </c>
-      <c r="N92" t="s">
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="93" ht="18" spans="1:16">
-      <c r="B93" t="s">
+      <c r="H94" t="s">
         <v>933</v>
       </c>
-      <c r="C93" t="s">
+      <c r="M94" t="s">
         <v>934</v>
       </c>
-      <c r="D93" t="s">
+      <c r="N94" t="s">
         <v>935</v>
       </c>
-      <c r="E93" s="2" t="s">
+    </row>
+    <row r="95" ht="18" spans="1:16">
+      <c r="B95" t="s">
+        <v>936</v>
+      </c>
+      <c r="C95" t="s">
+        <v>937</v>
+      </c>
+      <c r="D95" t="s">
+        <v>938</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93" t="s">
-        <v>936</v>
-      </c>
-      <c r="H93" t="s">
-        <v>937</v>
-      </c>
-      <c r="M93" t="s">
-        <v>938</v>
-      </c>
-      <c r="N93" t="s">
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
         <v>939</v>
       </c>
-      <c r="O93" t="s">
+      <c r="H95" t="s">
         <v>940</v>
       </c>
-      <c r="P93" t="s">
+      <c r="M95" t="s">
         <v>941</v>
+      </c>
+      <c r="N95" t="s">
+        <v>942</v>
+      </c>
+      <c r="O95" t="s">
+        <v>943</v>
+      </c>
+      <c r="P95" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="96" ht="18" spans="1:16">
+      <c r="E96" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>945</v>
+      </c>
+      <c r="H96" t="s">
+        <v>946</v>
+      </c>
+      <c r="M96" t="s">
+        <v>947</v>
+      </c>
+      <c r="N96" t="s">
+        <v>948</v>
+      </c>
+      <c r="O96" t="s">
+        <v>949</v>
+      </c>
+      <c r="P96" t="s">
+        <v>950</v>
       </c>
     </row>
   </sheetData>
@@ -12940,7 +13073,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE74"/>
+  <dimension ref="A1:AE75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -13096,28 +13229,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="H3" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" ht="31.2" customHeight="1" spans="2:31">
@@ -13128,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="2" t="s">
@@ -13146,73 +13279,73 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="F5" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="H5" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="I5" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
     </row>
     <row r="6" ht="18" spans="2:31">
       <c r="C6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="H6" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>959</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>970</v>
+        <v>979</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>550</v>
@@ -13221,16 +13354,16 @@
         <v>551</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>971</v>
+        <v>980</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7" ht="18" spans="2:31">
@@ -13241,7 +13374,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>728</v>
@@ -13250,16 +13383,16 @@
         <v>729</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>977</v>
+        <v>986</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>978</v>
+        <v>987</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>730</v>
@@ -13288,16 +13421,16 @@
         <v>729</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>977</v>
+        <v>986</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>735</v>
@@ -13320,37 +13453,37 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:31">
@@ -13361,38 +13494,38 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>995</v>
+        <v>1004</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>998</v>
+        <v>1007</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>999</v>
+        <v>1008</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1000</v>
+        <v>1009</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1001</v>
+        <v>1010</v>
       </c>
       <c r="O10" t="s">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="P10" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="11" ht="18" spans="2:31">
@@ -13403,16 +13536,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1004</v>
+        <v>1013</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -13423,7 +13556,7 @@
     </row>
     <row r="12" ht="18" spans="2:31">
       <c r="B12" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>49</v>
@@ -13434,25 +13567,25 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" spans="2:31">
       <c r="B13" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>49</v>
@@ -13461,39 +13594,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1015</v>
+        <v>1024</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1022</v>
+        <v>1031</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1023</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="18" spans="2:31">
       <c r="B14" t="s">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>222</v>
@@ -13502,21 +13635,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>1025</v>
+        <v>1034</v>
       </c>
       <c r="F14" t="s">
-        <v>1026</v>
+        <v>1035</v>
       </c>
       <c r="G14" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="H14" t="s">
-        <v>1028</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" ht="18" spans="2:31">
       <c r="B15" t="s">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>49</v>
@@ -13525,18 +13658,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1031</v>
+        <v>1040</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1033</v>
+        <v>1042</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -13545,7 +13678,7 @@
     </row>
     <row r="16" ht="18" spans="2:31">
       <c r="B16" t="s">
-        <v>1034</v>
+        <v>1043</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>49</v>
@@ -13554,10 +13687,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>374</v>
@@ -13568,7 +13701,7 @@
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="B17" t="s">
-        <v>1037</v>
+        <v>1046</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>49</v>
@@ -13577,19 +13710,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1038</v>
+        <v>1047</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>1039</v>
+        <v>1048</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="B18" t="s">
-        <v>1041</v>
+        <v>1050</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>49</v>
@@ -13600,15 +13733,15 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1043</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1044</v>
+        <v>1053</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>49</v>
@@ -13619,15 +13752,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>1045</v>
+        <v>1054</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>49</v>
@@ -13636,10 +13769,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1048</v>
+        <v>1057</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1049</v>
+        <v>1058</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>347</v>
@@ -13656,21 +13789,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1051</v>
+        <v>1060</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1053</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="B22" t="s">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -13679,24 +13812,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1056</v>
+        <v>1065</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="B23" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -13707,30 +13840,30 @@
       <c r="E23" s="2"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1062</v>
+        <v>1071</v>
       </c>
       <c r="M23" t="s">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="N23" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="B24" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>49</v>
@@ -13741,30 +13874,30 @@
       <c r="E24" s="2"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="B25" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>49</v>
@@ -13773,28 +13906,28 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>49</v>
@@ -13803,27 +13936,27 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="M26" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="N26" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -13832,21 +13965,21 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>49</v>
@@ -13855,33 +13988,33 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>49</v>
@@ -13890,39 +14023,39 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="F29" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>222</v>
@@ -13931,21 +14064,21 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="F30" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>49</v>
@@ -13954,15 +14087,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>49</v>
@@ -13971,33 +14104,33 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -14006,39 +14139,39 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F33" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1133</v>
+        <v>1142</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>49</v>
@@ -14047,33 +14180,33 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1145</v>
+        <v>1154</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>49</v>
@@ -14082,33 +14215,33 @@
         <v>1</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>49</v>
@@ -14117,39 +14250,39 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="F36" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1160</v>
+        <v>1169</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1161</v>
+        <v>1170</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1162</v>
+        <v>1171</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1163</v>
+        <v>1172</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1164</v>
+        <v>1173</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1165</v>
+        <v>1174</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1166</v>
+        <v>1175</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1167</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
@@ -14158,33 +14291,33 @@
         <v>1</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1170</v>
+        <v>1179</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1173</v>
+        <v>1182</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1175</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1176</v>
+        <v>1185</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>815</v>
@@ -14193,16 +14326,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>1177</v>
+        <v>1186</v>
       </c>
       <c r="F38" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="G38" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1180</v>
+        <v>1189</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -14213,10 +14346,10 @@
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="A39" t="s">
-        <v>1181</v>
+        <v>1190</v>
       </c>
       <c r="B39" t="s">
-        <v>1182</v>
+        <v>1191</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>49</v>
@@ -14228,30 +14361,30 @@
         <v>701</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1186</v>
+        <v>1195</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>49</v>
@@ -14260,10 +14393,10 @@
         <v>2</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -14274,10 +14407,10 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="B41" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>49</v>
@@ -14286,18 +14419,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="B42" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -14306,10 +14439,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
@@ -14320,10 +14453,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
@@ -14334,33 +14467,33 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="s">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="I44" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="K44" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="B45" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>49</v>
@@ -14369,34 +14502,34 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="F45" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -14405,33 +14538,33 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1216</v>
+        <v>1225</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1217</v>
+        <v>1226</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1218</v>
+        <v>1227</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>1219</v>
+        <v>1228</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1221</v>
+        <v>1230</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1222</v>
+        <v>1231</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1223</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="B47" t="s">
-        <v>1224</v>
+        <v>1233</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>49</v>
@@ -14440,15 +14573,15 @@
         <v>2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1225</v>
+        <v>1234</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1226</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1227</v>
+        <v>1236</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>49</v>
@@ -14457,30 +14590,30 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1228</v>
+        <v>1237</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1229</v>
+        <v>1238</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1230</v>
+        <v>1239</v>
       </c>
       <c r="N48" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1232</v>
+        <v>1241</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1233</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="B49" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>815</v>
@@ -14489,33 +14622,33 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1239</v>
+        <v>1248</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="B50" t="s">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>49</v>
@@ -14524,36 +14657,36 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="K50" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1247</v>
+        <v>1256</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1249</v>
+        <v>1258</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1251</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="B51" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>222</v>
@@ -14562,21 +14695,21 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="F51" t="s">
-        <v>1254</v>
+        <v>1263</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1256</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="B52" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -14585,21 +14718,21 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>1257</v>
+        <v>1266</v>
       </c>
       <c r="F52" t="s">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1259</v>
+        <v>1268</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1260</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="53" ht="27.6" spans="1:16">
       <c r="B53" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>222</v>
@@ -14607,22 +14740,22 @@
       <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>1262</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>1263</v>
+      <c r="E53" s="17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>1272</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="B54" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>49</v>
@@ -14631,33 +14764,33 @@
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1268</v>
+        <v>1277</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>1269</v>
+        <v>1278</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1270</v>
+        <v>1279</v>
       </c>
       <c r="M54" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1273</v>
+        <v>1282</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1274</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="B55" t="s">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>815</v>
@@ -14666,33 +14799,33 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="F55" t="s">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1278</v>
+        <v>1287</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1279</v>
+        <v>1288</v>
       </c>
       <c r="M55" t="s">
-        <v>1280</v>
+        <v>1289</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1281</v>
+        <v>1290</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>1282</v>
+        <v>1291</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>1283</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="B56" t="s">
-        <v>1284</v>
+        <v>1293</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>49</v>
@@ -14701,10 +14834,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>1285</v>
+        <v>1294</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1286</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
@@ -14715,30 +14848,30 @@
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1287</v>
+        <v>1296</v>
       </c>
       <c r="F57" t="s">
-        <v>1288</v>
+        <v>1297</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1289</v>
+        <v>1298</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1290</v>
+        <v>1299</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1291</v>
+        <v>1300</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1292</v>
+        <v>1301</v>
       </c>
       <c r="O57" t="s">
-        <v>1293</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="B58" t="s">
-        <v>1294</v>
+        <v>1303</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>
@@ -14747,39 +14880,39 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1295</v>
+        <v>1304</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1297</v>
+        <v>1306</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1298</v>
+        <v>1307</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1299</v>
+        <v>1308</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1300</v>
+        <v>1309</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1304</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="B59" t="s">
-        <v>1305</v>
+        <v>1314</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>49</v>
@@ -14788,39 +14921,39 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="I59" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="J59" s="2" t="s">
-        <v>1298</v>
-      </c>
       <c r="K59" s="2" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>1300</v>
+        <v>1309</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1304</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="B60" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>815</v>
@@ -14829,39 +14962,39 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>1316</v>
+        <v>1325</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="B61" t="s">
-        <v>1322</v>
+        <v>1331</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>49</v>
@@ -14870,39 +15003,39 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>1323</v>
+        <v>1332</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>1324</v>
+        <v>1333</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1325</v>
+        <v>1334</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1326</v>
+        <v>1335</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>1328</v>
+        <v>1337</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1329</v>
+        <v>1338</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>1331</v>
+        <v>1340</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>49</v>
@@ -14911,21 +15044,21 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="F62" t="s">
-        <v>1335</v>
+        <v>1344</v>
       </c>
       <c r="G62" t="s">
-        <v>1336</v>
+        <v>1345</v>
       </c>
       <c r="H62" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
       <c r="B63" t="s">
-        <v>1338</v>
+        <v>1347</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>815</v>
@@ -14934,33 +15067,33 @@
         <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>1339</v>
+        <v>1348</v>
       </c>
       <c r="H63" t="s">
-        <v>1340</v>
+        <v>1349</v>
       </c>
       <c r="K63" t="s">
-        <v>1341</v>
+        <v>1350</v>
       </c>
       <c r="L63" t="s">
-        <v>1342</v>
+        <v>1351</v>
       </c>
       <c r="M63" t="s">
-        <v>1343</v>
+        <v>1352</v>
       </c>
       <c r="N63" t="s">
-        <v>1344</v>
+        <v>1353</v>
       </c>
       <c r="O63" t="s">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="P63" t="s">
-        <v>1346</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="B64" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>49</v>
@@ -14969,15 +15102,15 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>1348</v>
+        <v>1357</v>
       </c>
       <c r="H64" t="s">
-        <v>1349</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:16">
       <c r="B65" t="s">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>49</v>
@@ -14986,33 +15119,33 @@
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>1351</v>
+        <v>1360</v>
       </c>
       <c r="H65" t="s">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="K65" t="s">
-        <v>1353</v>
+        <v>1362</v>
       </c>
       <c r="L65" t="s">
-        <v>1354</v>
+        <v>1363</v>
       </c>
       <c r="M65" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="N65" t="s">
-        <v>1356</v>
+        <v>1365</v>
       </c>
       <c r="O65" t="s">
-        <v>1357</v>
+        <v>1366</v>
       </c>
       <c r="P65" t="s">
-        <v>1358</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="66" ht="18" spans="1:16">
       <c r="B66" t="s">
-        <v>1359</v>
+        <v>1368</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>49</v>
@@ -15021,36 +15154,36 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>1360</v>
+        <v>1369</v>
       </c>
       <c r="H66" t="s">
-        <v>1361</v>
+        <v>1370</v>
       </c>
       <c r="K66" t="s">
-        <v>1362</v>
+        <v>1371</v>
       </c>
       <c r="L66" t="s">
-        <v>1363</v>
+        <v>1372</v>
       </c>
       <c r="M66" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="N66" t="s">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="O66" t="s">
-        <v>1366</v>
+        <v>1375</v>
       </c>
       <c r="P66" t="s">
-        <v>1367</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="67" ht="27.6" spans="1:16">
       <c r="A67" s="17" t="s">
-        <v>1368</v>
+        <v>1377</v>
       </c>
       <c r="B67" t="s">
-        <v>1369</v>
+        <v>1378</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>49</v>
@@ -15059,33 +15192,33 @@
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>1370</v>
+        <v>1379</v>
       </c>
       <c r="H67" t="s">
-        <v>1371</v>
+        <v>1380</v>
       </c>
       <c r="K67" t="s">
-        <v>1372</v>
+        <v>1381</v>
       </c>
       <c r="L67" t="s">
-        <v>1373</v>
+        <v>1382</v>
       </c>
       <c r="M67" t="s">
-        <v>1374</v>
+        <v>1383</v>
       </c>
       <c r="N67" t="s">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="O67" t="s">
-        <v>1376</v>
+        <v>1385</v>
       </c>
       <c r="P67" t="s">
-        <v>1377</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="B68" t="s">
-        <v>1378</v>
+        <v>1387</v>
       </c>
       <c r="C68" t="s">
         <v>222</v>
@@ -15094,36 +15227,36 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>1379</v>
+        <v>1388</v>
       </c>
       <c r="H68" t="s">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="K68" t="s">
-        <v>1381</v>
+        <v>1390</v>
       </c>
       <c r="L68" t="s">
-        <v>1382</v>
+        <v>1391</v>
       </c>
       <c r="M68" t="s">
-        <v>1383</v>
+        <v>1392</v>
       </c>
       <c r="N68" t="s">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="O68" t="s">
-        <v>1385</v>
+        <v>1394</v>
       </c>
       <c r="P68" t="s">
-        <v>1386</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:16">
       <c r="A69" t="s">
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="B69" t="s">
-        <v>1388</v>
+        <v>1397</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>49</v>
@@ -15132,36 +15265,36 @@
         <v>2</v>
       </c>
       <c r="G69" t="s">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="H69" t="s">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="K69" t="s">
-        <v>1391</v>
+        <v>1400</v>
       </c>
       <c r="L69" t="s">
-        <v>1392</v>
+        <v>1401</v>
       </c>
       <c r="M69" t="s">
-        <v>1393</v>
+        <v>1402</v>
       </c>
       <c r="N69" t="s">
-        <v>1394</v>
+        <v>1403</v>
       </c>
       <c r="O69" t="s">
-        <v>1395</v>
+        <v>1404</v>
       </c>
       <c r="P69" t="s">
-        <v>1396</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="B70" t="s">
-        <v>1397</v>
+        <v>1406</v>
       </c>
       <c r="C70" t="s">
         <v>222</v>
@@ -15170,33 +15303,33 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="H70" t="s">
-        <v>1398</v>
+        <v>1407</v>
       </c>
       <c r="K70" t="s">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="L70" t="s">
-        <v>1400</v>
+        <v>1409</v>
       </c>
       <c r="M70" t="s">
-        <v>1401</v>
+        <v>1410</v>
       </c>
       <c r="N70" t="s">
-        <v>1402</v>
+        <v>1411</v>
       </c>
       <c r="O70" t="s">
-        <v>1403</v>
+        <v>1412</v>
       </c>
       <c r="P70" t="s">
-        <v>1404</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="71" ht="18" spans="1:16">
       <c r="B71" t="s">
-        <v>1405</v>
+        <v>1414</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>49</v>
@@ -15205,27 +15338,27 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>1406</v>
+        <v>1415</v>
       </c>
       <c r="H71" t="s">
-        <v>1407</v>
+        <v>1416</v>
       </c>
       <c r="K71" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="L71" t="s">
-        <v>1409</v>
+        <v>1418</v>
       </c>
       <c r="M71" t="s">
-        <v>1410</v>
+        <v>1419</v>
       </c>
       <c r="N71" t="s">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="72" ht="18" spans="1:16">
-      <c r="B72" t="s">
-        <v>1412</v>
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" ht="18" spans="1:16">
+      <c r="B72" s="2" t="s">
+        <v>1421</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>49</v>
@@ -15233,105 +15366,140 @@
       <c r="D72">
         <v>1</v>
       </c>
+      <c r="E72" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1423</v>
+      </c>
       <c r="G72" t="s">
-        <v>1413</v>
+        <v>1424</v>
       </c>
       <c r="H72" t="s">
-        <v>1414</v>
-      </c>
-      <c r="K72" t="s">
-        <v>1415</v>
-      </c>
-      <c r="L72" t="s">
-        <v>1416</v>
+        <v>1425</v>
       </c>
       <c r="M72" t="s">
-        <v>1417</v>
+        <v>1426</v>
       </c>
       <c r="N72" t="s">
-        <v>1418</v>
+        <v>1427</v>
       </c>
       <c r="O72" t="s">
-        <v>1419</v>
+        <v>1428</v>
       </c>
       <c r="P72" t="s">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="73" ht="18" spans="1:16">
       <c r="B73" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C73" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K73" t="s">
+        <v>1433</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1434</v>
+      </c>
+      <c r="M73" t="s">
+        <v>1435</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1436</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1437</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="B74" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C74" t="s">
         <v>222</v>
       </c>
-      <c r="D73">
+      <c r="D74">
         <v>2</v>
       </c>
-      <c r="E73" t="s">
-        <v>1422</v>
-      </c>
-      <c r="F73" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G73" t="s">
-        <v>1424</v>
-      </c>
-      <c r="H73" t="s">
-        <v>1425</v>
-      </c>
-      <c r="M73" t="s">
-        <v>1426</v>
-      </c>
-      <c r="N73" t="s">
-        <v>1427</v>
-      </c>
-      <c r="O73" t="s">
-        <v>1428</v>
-      </c>
-      <c r="P73" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="74" ht="18" spans="1:16">
-      <c r="B74" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="E74" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M74" t="s">
+        <v>1444</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1445</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1446</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="75" ht="18" spans="1:16">
+      <c r="B75" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F74" t="s">
-        <v>1432</v>
-      </c>
-      <c r="G74" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H74" t="s">
-        <v>1434</v>
-      </c>
-      <c r="K74" t="s">
-        <v>1435</v>
-      </c>
-      <c r="L74" t="s">
-        <v>1436</v>
-      </c>
-      <c r="M74" t="s">
-        <v>1437</v>
-      </c>
-      <c r="N74" t="s">
-        <v>1438</v>
-      </c>
-      <c r="O74" t="s">
-        <v>1439</v>
-      </c>
-      <c r="P74" t="s">
-        <v>1440</v>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1452</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L75" t="s">
+        <v>1454</v>
+      </c>
+      <c r="M75" t="s">
+        <v>1455</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1456</v>
+      </c>
+      <c r="O75" t="s">
+        <v>1457</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1458</v>
       </c>
     </row>
   </sheetData>
@@ -15357,7 +15525,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" ht="18" spans="1:31">
@@ -15504,28 +15672,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1441</v>
+        <v>1459</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1442</v>
+        <v>1460</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1443</v>
+        <v>1461</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1444</v>
+        <v>1462</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1445</v>
+        <v>1463</v>
       </c>
       <c r="N3" t="s">
-        <v>1446</v>
+        <v>1464</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1447</v>
+        <v>1465</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1448</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -15536,28 +15704,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1449</v>
+        <v>1467</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1450</v>
+        <v>1468</v>
       </c>
       <c r="I4" t="s">
-        <v>1451</v>
+        <v>1469</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1452</v>
+        <v>1470</v>
       </c>
       <c r="M4" t="s">
-        <v>1453</v>
+        <v>1471</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1454</v>
+        <v>1472</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1455</v>
+        <v>1473</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1456</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -15568,60 +15736,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1457</v>
+        <v>1475</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1458</v>
+        <v>1476</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1459</v>
+        <v>1477</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1460</v>
+        <v>1478</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1461</v>
+        <v>1479</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1462</v>
+        <v>1480</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1463</v>
+        <v>1481</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1464</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1465</v>
+        <v>1483</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1466</v>
+        <v>1484</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1458</v>
+        <v>1476</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1467</v>
+        <v>1485</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1460</v>
+        <v>1478</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1468</v>
+        <v>1486</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1462</v>
+        <v>1480</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1469</v>
+        <v>1487</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1464</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -15629,21 +15797,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1470</v>
+        <v>1488</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1471</v>
+        <v>1489</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1472</v>
+        <v>1490</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1473</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1474</v>
+        <v>1492</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -15652,15 +15820,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1475</v>
+        <v>1493</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1476</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1474</v>
+        <v>1492</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -15677,7 +15845,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1477</v>
+        <v>1495</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -15686,36 +15854,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1478</v>
+        <v>1496</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1479</v>
+        <v>1497</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1480</v>
+        <v>1498</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1481</v>
+        <v>1499</v>
       </c>
       <c r="M10" t="s">
-        <v>1482</v>
+        <v>1500</v>
       </c>
       <c r="N10" t="s">
-        <v>1483</v>
+        <v>1501</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1484</v>
+        <v>1502</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1485</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1486</v>
+        <v>1504</v>
       </c>
       <c r="B11" t="s">
-        <v>1487</v>
+        <v>1505</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -15724,42 +15892,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1488</v>
+        <v>1506</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1489</v>
+        <v>1507</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1490</v>
+        <v>1508</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1491</v>
+        <v>1509</v>
       </c>
       <c r="M11" t="s">
-        <v>1492</v>
+        <v>1510</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1493</v>
+        <v>1511</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1494</v>
+        <v>1512</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1495</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1488</v>
+        <v>1506</v>
       </c>
       <c r="B12" t="s">
-        <v>1496</v>
+        <v>1514</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1497</v>
+        <v>1515</v>
       </c>
       <c r="D12" t="s">
-        <v>1498</v>
+        <v>1516</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -15768,33 +15936,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1486</v>
+        <v>1504</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1499</v>
+        <v>1517</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1500</v>
+        <v>1518</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1501</v>
+        <v>1519</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1502</v>
+        <v>1520</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1503</v>
+        <v>1521</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1504</v>
+        <v>1522</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1505</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1506</v>
+        <v>1524</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -15803,39 +15971,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1507</v>
+        <v>1525</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1508</v>
+        <v>1526</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1509</v>
+        <v>1527</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1510</v>
+        <v>1528</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1511</v>
+        <v>1529</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1512</v>
+        <v>1530</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1513</v>
+        <v>1531</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1514</v>
+        <v>1532</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1515</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1516</v>
+        <v>1534</v>
       </c>
       <c r="B14" t="s">
-        <v>1517</v>
+        <v>1535</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -15844,22 +16012,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1518</v>
+        <v>1536</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1519</v>
+        <v>1537</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1520</v>
+        <v>1538</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1521</v>
+        <v>1539</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1522</v>
+        <v>1540</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1523</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -15871,33 +16039,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1524</v>
+        <v>1542</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1525</v>
+        <v>1543</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="N15" t="s">
-        <v>1527</v>
+        <v>1545</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1528</v>
+        <v>1546</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1529</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1530</v>
+        <v>1548</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1531</v>
+        <v>1549</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1532</v>
+        <v>1550</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -15906,18 +16074,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1533</v>
+        <v>1551</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1534</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1535</v>
+        <v>1553</v>
       </c>
       <c r="B17" t="s">
-        <v>1536</v>
+        <v>1554</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -15926,30 +16094,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1537</v>
+        <v>1555</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1538</v>
+        <v>1556</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1539</v>
+        <v>1557</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1540</v>
+        <v>1558</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1541</v>
+        <v>1559</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1542</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1543</v>
+        <v>1561</v>
       </c>
       <c r="B18" t="s">
-        <v>1544</v>
+        <v>1562</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -15958,27 +16126,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1545</v>
+        <v>1563</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1546</v>
+        <v>1564</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1547</v>
+        <v>1565</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1548</v>
+        <v>1566</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1549</v>
+        <v>1567</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1550</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1551</v>
+        <v>1569</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -15987,30 +16155,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1543</v>
+        <v>1561</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1552</v>
+        <v>1570</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1553</v>
+        <v>1571</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1554</v>
+        <v>1572</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1555</v>
+        <v>1573</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1556</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
-      <c r="A20" s="2" t="s">
-        <v>1557</v>
-      </c>
       <c r="B20" t="s">
-        <v>1558</v>
+        <v>1575</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -16019,40 +16184,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1559</v>
+        <v>1576</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1560</v>
-      </c>
-      <c r="K20" t="s">
-        <v>1561</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>1562</v>
-      </c>
-      <c r="M20" t="s">
-        <v>1563</v>
+        <v>1577</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>1578</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1564</v>
+        <v>1579</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1565</v>
+        <v>1580</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1566</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>1582</v>
+      </c>
       <c r="B21" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -16061,36 +16216,41 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1571</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>1572</v>
+        <v>1585</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1586</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1573</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>1574</v>
+        <v>1587</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1588</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>1592</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1594</v>
+      </c>
       <c r="E22" t="s">
         <v>222</v>
       </c>
@@ -16098,126 +16258,134 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1579</v>
+        <v>1595</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1581</v>
+        <v>1597</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1582</v>
+        <v>1598</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1585</v>
+        <v>1601</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1586</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
+      <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>1587</v>
-      </c>
+        <v>1603</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="E23" t="s">
         <v>222</v>
       </c>
       <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="24" ht="18" spans="1:16">
+      <c r="B24" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E24" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>1588</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>1590</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>1591</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:16">
-      <c r="A24" s="2" t="s">
-        <v>1559</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G24" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:16">
+      <c r="A25" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E25" t="s">
         <v>49</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>1557</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>1594</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>1595</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>1596</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>1597</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>1598</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>1599</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:16">
-      <c r="B25" t="s">
-        <v>1601</v>
-      </c>
-      <c r="E25" t="s">
-        <v>222</v>
-      </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1602</v>
+        <v>1582</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1603</v>
+        <v>1619</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>1621</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1604</v>
+        <v>1622</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1605</v>
+        <v>1623</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1607</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1608</v>
+        <v>1626</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -16226,268 +16394,262 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1609</v>
+        <v>1627</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1611</v>
+        <v>1628</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1612</v>
+        <v>1629</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1613</v>
+        <v>1630</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1614</v>
+        <v>1631</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1615</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1617</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1618</v>
+        <v>1633</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1619</v>
+        <v>1634</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1620</v>
+        <v>1635</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1636</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1621</v>
+        <v>1637</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1622</v>
+        <v>1638</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1623</v>
+        <v>1639</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1624</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1625</v>
+        <v>1641</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1643</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1626</v>
+        <v>1644</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1627</v>
+        <v>1645</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1628</v>
+        <v>1646</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1629</v>
+        <v>1647</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1630</v>
+        <v>1648</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1631</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1632</v>
+        <v>1650</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1633</v>
+        <v>1651</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1634</v>
+        <v>1652</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>1656</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
+      <c r="B30" t="s">
+        <v>1657</v>
+      </c>
       <c r="E30" t="s">
         <v>222</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1635</v>
+        <v>1658</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1636</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>1637</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>1640</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
-      <c r="B31" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1642</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1643</v>
-      </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1644</v>
+        <v>1660</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1645</v>
+        <v>1661</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>1665</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1646</v>
+        <v>1666</v>
       </c>
       <c r="C32" t="s">
-        <v>1647</v>
+        <v>1667</v>
       </c>
       <c r="D32" t="s">
-        <v>1648</v>
+        <v>1668</v>
       </c>
       <c r="E32" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1649</v>
+        <v>1669</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>1651</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>1654</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1655</v>
+        <v>1671</v>
       </c>
       <c r="C33" t="s">
-        <v>1656</v>
+        <v>1672</v>
       </c>
       <c r="D33" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>815</v>
+        <v>1673</v>
+      </c>
+      <c r="E33" t="s">
+        <v>222</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1659</v>
+        <v>1675</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1660</v>
+        <v>1676</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1661</v>
+        <v>1677</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>1679</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
-      <c r="A34" s="2" t="s">
-        <v>1662</v>
-      </c>
       <c r="B34" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>1664</v>
+        <v>1680</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1681</v>
       </c>
       <c r="D34" t="s">
-        <v>1665</v>
+        <v>1682</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>222</v>
+        <v>815</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1666</v>
+        <v>1683</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>1668</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>1669</v>
+        <v>1684</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1670</v>
+        <v>1685</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>1673</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
+      <c r="A35" s="2" t="s">
+        <v>1687</v>
+      </c>
       <c r="B35" t="s">
-        <v>1674</v>
+        <v>1688</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1690</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -16496,27 +16658,33 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1675</v>
+        <v>1691</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1676</v>
+        <v>1692</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>1694</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1677</v>
+        <v>1695</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1678</v>
+        <v>1696</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1679</v>
+        <v>1697</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1680</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1681</v>
+        <v>1699</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -16525,259 +16693,288 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1682</v>
+        <v>1700</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>1684</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>1685</v>
+        <v>1701</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1686</v>
+        <v>1702</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1687</v>
+        <v>1703</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1688</v>
+        <v>1704</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1689</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1690</v>
+        <v>1706</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>815</v>
+        <v>222</v>
       </c>
       <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1691</v>
-      </c>
-      <c r="H37" t="s">
-        <v>1692</v>
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>1714</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>222</v>
+        <v>815</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1694</v>
+        <v>1716</v>
       </c>
       <c r="H38" t="s">
-        <v>1695</v>
-      </c>
-      <c r="K38" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L38" t="s">
-        <v>1697</v>
-      </c>
-      <c r="M38" t="s">
-        <v>1698</v>
-      </c>
-      <c r="N38" t="s">
-        <v>1699</v>
-      </c>
-      <c r="O38" t="s">
-        <v>1700</v>
-      </c>
-      <c r="P38" t="s">
-        <v>1701</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1702</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1704</v>
+        <v>1718</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1705</v>
+        <v>1719</v>
       </c>
       <c r="H39" t="s">
-        <v>1706</v>
+        <v>1720</v>
       </c>
       <c r="K39" t="s">
-        <v>1707</v>
+        <v>1721</v>
       </c>
       <c r="L39" t="s">
-        <v>1708</v>
+        <v>1722</v>
       </c>
       <c r="M39" t="s">
-        <v>1709</v>
+        <v>1723</v>
       </c>
       <c r="N39" t="s">
-        <v>1710</v>
+        <v>1724</v>
       </c>
       <c r="O39" t="s">
-        <v>1711</v>
+        <v>1725</v>
       </c>
       <c r="P39" t="s">
-        <v>1712</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1713</v>
+        <v>1727</v>
       </c>
       <c r="C40" t="s">
-        <v>1714</v>
+        <v>1728</v>
       </c>
       <c r="D40" t="s">
-        <v>1715</v>
+        <v>1729</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>222</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1716</v>
+        <v>1730</v>
       </c>
       <c r="H40" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+        <v>1731</v>
+      </c>
+      <c r="K40" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1733</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1734</v>
+      </c>
+      <c r="N40" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O40" t="s">
+        <v>1736</v>
+      </c>
+      <c r="P40" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="41" ht="18" spans="1:16">
       <c r="B41" t="s">
-        <v>1718</v>
+        <v>1738</v>
       </c>
       <c r="C41" t="s">
-        <v>1719</v>
+        <v>1739</v>
       </c>
       <c r="D41" t="s">
-        <v>923</v>
-      </c>
-      <c r="E41" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="B42" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D42" t="s">
+        <v>926</v>
+      </c>
+      <c r="E42" t="s">
         <v>49</v>
       </c>
-      <c r="F41">
+      <c r="F42">
         <v>2</v>
       </c>
-      <c r="G41" t="s">
-        <v>1475</v>
-      </c>
-      <c r="H41" t="s">
-        <v>1476</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1720</v>
-      </c>
-      <c r="L41" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="42" ht="18" spans="1:16">
-      <c r="B42" t="s">
-        <v>1722</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
       <c r="G42" t="s">
-        <v>1723</v>
+        <v>1493</v>
       </c>
       <c r="H42" t="s">
-        <v>1724</v>
+        <v>1494</v>
       </c>
       <c r="K42" t="s">
-        <v>1725</v>
+        <v>1745</v>
       </c>
       <c r="L42" t="s">
-        <v>1726</v>
-      </c>
-      <c r="M42" t="s">
-        <v>1727</v>
-      </c>
-      <c r="N42" t="s">
-        <v>1728</v>
-      </c>
-      <c r="O42" t="s">
-        <v>1729</v>
-      </c>
-      <c r="P42" t="s">
-        <v>1730</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1731</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1733</v>
+        <v>1747</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1748</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1749</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1750</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1751</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1752</v>
+      </c>
+      <c r="N43" t="s">
+        <v>1753</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1754</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="44" ht="18" spans="1:16">
+      <c r="B44" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1734</v>
-      </c>
-      <c r="H43" t="s">
-        <v>1735</v>
-      </c>
-      <c r="I43" t="s">
-        <v>1736</v>
-      </c>
-      <c r="J43" t="s">
-        <v>1737</v>
-      </c>
-      <c r="K43" t="s">
-        <v>1738</v>
-      </c>
-      <c r="L43" t="s">
-        <v>1739</v>
-      </c>
-      <c r="M43" t="s">
-        <v>1740</v>
-      </c>
-      <c r="N43" t="s">
-        <v>1741</v>
-      </c>
-      <c r="O43" t="s">
-        <v>1742</v>
-      </c>
-      <c r="P43" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="45" ht="16.8" spans="1:16">
-      <c r="I45" s="16"/>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1759</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1761</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K44" t="s">
+        <v>1763</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1764</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1765</v>
+      </c>
+      <c r="N44" t="s">
+        <v>1766</v>
+      </c>
+      <c r="O44" t="s">
+        <v>1767</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="46" ht="16.8" spans="1:16">
+      <c r="I46" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -16951,16 +17148,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1744</v>
+        <v>1769</v>
       </c>
       <c r="B3" t="s">
-        <v>1745</v>
+        <v>1770</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1746</v>
+        <v>1771</v>
       </c>
       <c r="D3" t="s">
-        <v>1747</v>
+        <v>1772</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -16969,31 +17166,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1748</v>
+        <v>1773</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1749</v>
+        <v>1774</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1751</v>
+        <v>1776</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1752</v>
+        <v>1777</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1753</v>
+        <v>1778</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1754</v>
+        <v>1779</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1755</v>
+        <v>1780</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -17003,42 +17200,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1756</v>
+        <v>1781</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1757</v>
+        <v>1782</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1756</v>
+        <v>1781</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1757</v>
+        <v>1782</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1758</v>
+        <v>1783</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1759</v>
+        <v>1784</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1760</v>
+        <v>1785</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1761</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1762</v>
+        <v>1787</v>
       </c>
       <c r="B4" t="s">
-        <v>1763</v>
+        <v>1788</v>
       </c>
       <c r="C4" t="s">
-        <v>1764</v>
+        <v>1789</v>
       </c>
       <c r="D4" t="s">
-        <v>1765</v>
+        <v>1790</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -17047,37 +17244,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1766</v>
+        <v>1791</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1767</v>
+        <v>1792</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1768</v>
+        <v>1793</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1769</v>
+        <v>1794</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1770</v>
+        <v>1795</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1771</v>
+        <v>1796</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1772</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1763</v>
+        <v>1788</v>
       </c>
       <c r="C5" t="s">
-        <v>1773</v>
+        <v>1798</v>
       </c>
       <c r="D5" t="s">
-        <v>1765</v>
+        <v>1790</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17086,65 +17283,65 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1774</v>
+        <v>1799</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1776</v>
+        <v>1801</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1777</v>
+        <v>1802</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1778</v>
+        <v>1803</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1779</v>
+        <v>1804</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1780</v>
+        <v>1805</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1781</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1782</v>
+        <v>1807</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1783</v>
+        <v>1808</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1784</v>
+        <v>1809</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1785</v>
+        <v>1810</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1786</v>
+        <v>1811</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1787</v>
+        <v>1812</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1788</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>1789</v>
+        <v>1814</v>
       </c>
       <c r="C7" t="s">
-        <v>1790</v>
+        <v>1815</v>
       </c>
       <c r="D7" t="s">
-        <v>1791</v>
+        <v>1816</v>
       </c>
       <c r="E7" t="s">
         <v>222</v>
@@ -17153,28 +17350,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1792</v>
+        <v>1817</v>
       </c>
       <c r="H7" t="s">
-        <v>1793</v>
+        <v>1818</v>
       </c>
       <c r="L7" t="s">
-        <v>1794</v>
+        <v>1819</v>
       </c>
       <c r="M7" t="s">
-        <v>1795</v>
+        <v>1820</v>
       </c>
       <c r="N7" t="s">
-        <v>1796</v>
+        <v>1821</v>
       </c>
       <c r="O7" t="s">
-        <v>1797</v>
+        <v>1822</v>
       </c>
       <c r="P7" t="s">
-        <v>1798</v>
+        <v>1823</v>
       </c>
       <c r="Q7" t="s">
-        <v>1799</v>
+        <v>1824</v>
       </c>
     </row>
   </sheetData>
@@ -17356,30 +17553,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1801</v>
+        <v>1826</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1802</v>
+        <v>1827</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1803</v>
+        <v>1828</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1804</v>
+        <v>1829</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1805</v>
+        <v>1830</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1806</v>
+        <v>1831</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1807</v>
+        <v>1832</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -17389,16 +17586,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1808</v>
+        <v>1833</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1809</v>
+        <v>1834</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1810</v>
+        <v>1835</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1811</v>
+        <v>1836</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -17413,34 +17610,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1812</v>
+        <v>1837</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1813</v>
+        <v>1838</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1814</v>
+        <v>1839</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1815</v>
+        <v>1840</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1816</v>
+        <v>1841</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1817</v>
+        <v>1842</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1818</v>
+        <v>1843</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1819</v>
+        <v>1844</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1820</v>
+        <v>1845</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1821</v>
+        <v>1846</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -17460,7 +17657,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1822</v>
+        <v>1847</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17469,34 +17666,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1823</v>
+        <v>1848</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1824</v>
+        <v>1849</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1826</v>
+        <v>1851</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1827</v>
+        <v>1852</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1828</v>
+        <v>1853</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1829</v>
+        <v>1854</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1830</v>
+        <v>1855</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1831</v>
+        <v>1856</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1832</v>
+        <v>1857</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -17506,16 +17703,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1833</v>
+        <v>1858</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1834</v>
+        <v>1859</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1835</v>
+        <v>1860</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1836</v>
+        <v>1861</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -17524,13 +17721,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1837</v>
+        <v>1862</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1838</v>
+        <v>1863</v>
       </c>
       <c r="D6" t="s">
-        <v>1839</v>
+        <v>1864</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -17539,30 +17736,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1841</v>
+        <v>1866</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1842</v>
+        <v>1867</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1843</v>
+        <v>1868</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1844</v>
+        <v>1869</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1845</v>
+        <v>1870</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1846</v>
+        <v>1871</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1847</v>
+        <v>1872</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -17574,10 +17771,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1848</v>
+        <v>1873</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1849</v>
+        <v>1874</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -17586,13 +17783,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1837</v>
+        <v>1862</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="D7" t="s">
-        <v>1839</v>
+        <v>1864</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -17601,34 +17798,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1848</v>
+        <v>1873</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1849</v>
+        <v>1874</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1851</v>
+        <v>1876</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1852</v>
+        <v>1877</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1853</v>
+        <v>1878</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1854</v>
+        <v>1879</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1855</v>
+        <v>1880</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1856</v>
+        <v>1881</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1857</v>
+        <v>1882</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1858</v>
+        <v>1883</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -17648,7 +17845,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1859</v>
+        <v>1884</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -17657,75 +17854,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1860</v>
+        <v>1885</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1861</v>
+        <v>1886</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1862</v>
+        <v>1887</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1863</v>
+        <v>1888</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1864</v>
+        <v>1889</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1865</v>
+        <v>1890</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1866</v>
+        <v>1891</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1867</v>
+        <v>1892</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1868</v>
+        <v>1893</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1869</v>
+        <v>1894</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1870</v>
+        <v>1895</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1871</v>
+        <v>1896</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1872</v>
+        <v>1897</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1873</v>
+        <v>1898</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1874</v>
+        <v>1899</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1758</v>
+        <v>1783</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1759</v>
+        <v>1784</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1756</v>
+        <v>1781</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1757</v>
+        <v>1782</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1758</v>
+        <v>1783</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1759</v>
+        <v>1784</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1760</v>
+        <v>1785</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1761</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -17733,7 +17930,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -17742,10 +17939,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1876</v>
+        <v>1901</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1877</v>
+        <v>1902</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -17778,7 +17975,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1878</v>
+        <v>1903</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -17787,10 +17984,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1879</v>
+        <v>1904</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1880</v>
+        <v>1905</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -17819,7 +18016,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1881</v>
+        <v>1906</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -17828,37 +18025,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1882</v>
+        <v>1907</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1883</v>
+        <v>1908</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1884</v>
+        <v>1909</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1885</v>
+        <v>1910</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1886</v>
+        <v>1911</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1887</v>
+        <v>1912</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1888</v>
+        <v>1913</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1889</v>
+        <v>1914</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1890</v>
+        <v>1915</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1891</v>
+        <v>1916</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1892</v>
+        <v>1917</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -17871,10 +18068,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1893</v>
+        <v>1918</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1894</v>
+        <v>1919</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -17882,7 +18079,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1895</v>
+        <v>1920</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -17891,20 +18088,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1896</v>
+        <v>1921</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1897</v>
+        <v>1922</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1898</v>
+        <v>1923</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1899</v>
+        <v>1924</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -17926,10 +18123,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="B13" t="s">
-        <v>1901</v>
+        <v>1926</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -17938,20 +18135,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1902</v>
+        <v>1927</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1903</v>
+        <v>1928</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1904</v>
+        <v>1929</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1905</v>
+        <v>1930</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -17973,10 +18170,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1902</v>
+        <v>1927</v>
       </c>
       <c r="B14" t="s">
-        <v>1906</v>
+        <v>1931</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -17985,20 +18182,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1907</v>
+        <v>1932</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1908</v>
+        <v>1933</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1899</v>
+        <v>1924</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -18020,10 +18217,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1909</v>
+        <v>1934</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1910</v>
+        <v>1935</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -18033,39 +18230,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1911</v>
+        <v>1936</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1912</v>
+        <v>1937</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1913</v>
+        <v>1938</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1914</v>
+        <v>1939</v>
       </c>
       <c r="K15" t="s">
-        <v>1915</v>
+        <v>1940</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1916</v>
+        <v>1941</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1917</v>
+        <v>1942</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1918</v>
+        <v>1943</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1919</v>
+        <v>1944</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1920</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1921</v>
+        <v>1946</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -18074,34 +18271,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1922</v>
+        <v>1947</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1923</v>
+        <v>1948</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1924</v>
+        <v>1949</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1926</v>
+        <v>1951</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1927</v>
+        <v>1952</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1928</v>
+        <v>1953</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1929</v>
+        <v>1954</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1930</v>
+        <v>1955</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1931</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -18112,7 +18309,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1932</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -18123,7 +18320,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1933</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -18134,10 +18331,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1934</v>
+        <v>1959</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1935</v>
+        <v>1960</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -18149,18 +18346,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1936</v>
+        <v>1961</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1935</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1937</v>
+        <v>1962</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1938</v>
+        <v>1963</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -18170,42 +18367,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1939</v>
+        <v>1964</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1940</v>
+        <v>1965</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1941</v>
+        <v>1966</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1942</v>
+        <v>1967</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1943</v>
+        <v>1968</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1944</v>
+        <v>1969</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1945</v>
+        <v>1970</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1946</v>
+        <v>1971</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1948</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1949</v>
+        <v>1974</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1950</v>
+        <v>1975</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -18215,39 +18412,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1951</v>
+        <v>1976</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1940</v>
+        <v>1965</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1942</v>
+        <v>1967</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1952</v>
+        <v>1977</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1944</v>
+        <v>1969</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1953</v>
+        <v>1978</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1946</v>
+        <v>1971</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1954</v>
+        <v>1979</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1948</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1956</v>
+        <v>1981</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -18257,27 +18454,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1957</v>
+        <v>1982</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1958</v>
+        <v>1983</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1959</v>
+        <v>1984</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1960</v>
+        <v>1985</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1961</v>
+        <v>1986</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1962</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>1963</v>
+        <v>1988</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -18286,39 +18483,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1964</v>
+        <v>1989</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1965</v>
+        <v>1990</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1966</v>
+        <v>1991</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1967</v>
+        <v>1992</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1968</v>
+        <v>1993</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1969</v>
+        <v>1994</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1970</v>
+        <v>1995</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1971</v>
+        <v>1996</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1972</v>
+        <v>1997</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1973</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>1963</v>
+        <v>1988</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -18327,10 +18524,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1974</v>
+        <v>1999</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1975</v>
+        <v>2000</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -18343,7 +18540,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>1976</v>
+        <v>2001</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -18352,26 +18549,26 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1977</v>
+        <v>2002</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>1978</v>
+        <v>2003</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1979</v>
+        <v>2004</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1980</v>
+        <v>2005</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1981</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -18382,32 +18579,32 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>1982</v>
+        <v>2007</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1979</v>
+        <v>2004</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1983</v>
+        <v>2008</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1981</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
       <c r="B28" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1984</v>
+        <v>2009</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -18417,39 +18614,39 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1985</v>
+        <v>2010</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1986</v>
+        <v>2011</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1989</v>
+        <v>2014</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1990</v>
+        <v>2015</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1991</v>
+        <v>2016</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1993</v>
+        <v>2018</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1994</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
       <c r="B29" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>222</v>
@@ -18458,27 +18655,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1995</v>
+        <v>2020</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1996</v>
+        <v>2021</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>2000</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>2001</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -18487,27 +18684,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2002</v>
+        <v>2027</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2004</v>
+        <v>2029</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2005</v>
+        <v>2030</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2006</v>
+        <v>2031</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>2007</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>2008</v>
+        <v>2033</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -18516,27 +18713,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>2009</v>
+        <v>2034</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2010</v>
+        <v>2035</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2011</v>
+        <v>2036</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2012</v>
+        <v>2037</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2013</v>
+        <v>2038</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>2014</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>2015</v>
+        <v>2040</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -18551,21 +18748,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2016</v>
+        <v>2041</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2017</v>
+        <v>2042</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2018</v>
+        <v>2043</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>2019</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>2020</v>
+        <v>2045</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -18574,22 +18771,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2021</v>
+        <v>2046</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2022</v>
+        <v>2047</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2023</v>
+        <v>2048</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2024</v>
+        <v>2049</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2025</v>
+        <v>2050</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>2026</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -18599,30 +18796,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>2027</v>
+        <v>2052</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2028</v>
+        <v>2053</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>2029</v>
+        <v>2054</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2030</v>
+        <v>2055</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2031</v>
+        <v>2056</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2032</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>2033</v>
+        <v>2058</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -18631,10 +18828,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>2034</v>
+        <v>2059</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2035</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -18645,30 +18842,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2036</v>
+        <v>2061</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2037</v>
+        <v>2062</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>2038</v>
+        <v>2063</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>2039</v>
+        <v>2064</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2040</v>
+        <v>2065</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>2041</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>2042</v>
+        <v>2067</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2043</v>
+        <v>2068</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -18677,30 +18874,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2044</v>
+        <v>2069</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2045</v>
+        <v>2070</v>
       </c>
       <c r="M38" t="s">
-        <v>2046</v>
+        <v>2071</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2047</v>
+        <v>2072</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2048</v>
+        <v>2073</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>2049</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>2050</v>
+        <v>2075</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -18710,18 +18907,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>2052</v>
+        <v>2077</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2053</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>2054</v>
+        <v>2079</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2055</v>
+        <v>2080</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -18731,22 +18928,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1841</v>
+        <v>1866</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1844</v>
+        <v>1869</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1845</v>
+        <v>1870</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1846</v>
+        <v>1871</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1847</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -18759,15 +18956,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2056</v>
+        <v>2081</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2057</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>2058</v>
+        <v>2083</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -18776,54 +18973,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>2059</v>
+        <v>2084</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2060</v>
+        <v>2085</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2061</v>
+        <v>2086</v>
       </c>
       <c r="N42" t="s">
-        <v>2062</v>
+        <v>2087</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2063</v>
+        <v>2088</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2064</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>2065</v>
+        <v>2090</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2066</v>
+        <v>2091</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2060</v>
+        <v>2085</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>2067</v>
+        <v>2092</v>
       </c>
       <c r="N43" t="s">
-        <v>2062</v>
+        <v>2087</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2068</v>
+        <v>2093</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>2064</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>2069</v>
+        <v>2094</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -18832,30 +19029,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>2070</v>
+        <v>2095</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>2060</v>
+        <v>2085</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>2071</v>
+        <v>2096</v>
       </c>
       <c r="N44" t="s">
-        <v>2062</v>
+        <v>2087</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2072</v>
+        <v>2097</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>2064</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>2073</v>
+        <v>2098</v>
       </c>
       <c r="C45" t="s">
-        <v>2074</v>
+        <v>2099</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -18864,7 +19061,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2075</v>
+        <v>2100</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -18872,10 +19069,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>2076</v>
+        <v>2101</v>
       </c>
       <c r="B46" t="s">
-        <v>2077</v>
+        <v>2102</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -18884,24 +19081,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2078</v>
+        <v>2103</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2079</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>2080</v>
+        <v>2105</v>
       </c>
       <c r="B47" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2082</v>
+        <v>2107</v>
       </c>
       <c r="D47" t="s">
-        <v>2083</v>
+        <v>2108</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -18910,33 +19107,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2084</v>
+        <v>2109</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2085</v>
+        <v>2110</v>
       </c>
       <c r="M47" t="s">
-        <v>2086</v>
+        <v>2111</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>2087</v>
+        <v>2112</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>2088</v>
+        <v>2113</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>2089</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>2090</v>
+        <v>2115</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2091</v>
+        <v>2116</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>2092</v>
+        <v>2117</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -18945,18 +19142,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2093</v>
+        <v>2118</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2094</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="B49" t="s">
-        <v>2095</v>
+        <v>2120</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -18965,28 +19162,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2096</v>
+        <v>2121</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2097</v>
+        <v>2122</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>2098</v>
+        <v>2123</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>2099</v>
+        <v>2124</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>2100</v>
+        <v>2125</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2101</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>2095</v>
+        <v>2120</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -18995,30 +19192,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>2102</v>
+        <v>2127</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2097</v>
+        <v>2122</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2103</v>
+        <v>2128</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2099</v>
+        <v>2124</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>2104</v>
+        <v>2129</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2101</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>2105</v>
+        <v>2130</v>
       </c>
       <c r="B51" t="s">
-        <v>2106</v>
+        <v>2131</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -19027,34 +19224,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1516</v>
+        <v>1534</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2107</v>
+        <v>2132</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>2108</v>
+        <v>2133</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>2109</v>
+        <v>2134</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>2110</v>
+        <v>2135</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>2111</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>2112</v>
+        <v>2137</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2113</v>
+        <v>2138</v>
       </c>
       <c r="D52" t="s">
-        <v>2114</v>
+        <v>2139</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -19063,24 +19260,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2056</v>
+        <v>2081</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2057</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>2115</v>
+        <v>2140</v>
       </c>
       <c r="B53" t="s">
-        <v>2116</v>
+        <v>2141</v>
       </c>
       <c r="C53" t="s">
-        <v>2117</v>
+        <v>2142</v>
       </c>
       <c r="D53" t="s">
-        <v>2118</v>
+        <v>2143</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -19089,18 +19286,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2119</v>
+        <v>2144</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2120</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>2121</v>
+        <v>2146</v>
       </c>
       <c r="B54" t="s">
-        <v>2122</v>
+        <v>2147</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -19109,36 +19306,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1478</v>
+        <v>1496</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1479</v>
+        <v>1497</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1482</v>
+        <v>1500</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2123</v>
+        <v>2148</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1484</v>
+        <v>1502</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1485</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>2124</v>
+        <v>2149</v>
       </c>
       <c r="B55" t="s">
-        <v>2125</v>
+        <v>2150</v>
       </c>
       <c r="C55" t="s">
-        <v>2126</v>
+        <v>2151</v>
       </c>
       <c r="D55" t="s">
-        <v>2127</v>
+        <v>2152</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -19147,19 +19344,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2128</v>
+        <v>2153</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2129</v>
+        <v>2154</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1762</v>
+        <v>1787</v>
       </c>
       <c r="B56" t="s">
-        <v>2130</v>
+        <v>2155</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -19168,36 +19365,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2131</v>
+        <v>2156</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2132</v>
+        <v>2157</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>2133</v>
+        <v>2158</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2134</v>
+        <v>2159</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>2135</v>
+        <v>2160</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>2136</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>2137</v>
+        <v>2162</v>
       </c>
       <c r="B57" t="s">
-        <v>2138</v>
+        <v>2163</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>2139</v>
+        <v>2164</v>
       </c>
       <c r="D57" t="s">
-        <v>2140</v>
+        <v>2165</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -19206,36 +19403,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1762</v>
+        <v>1787</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2141</v>
+        <v>2166</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>2142</v>
+        <v>2167</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2143</v>
+        <v>2168</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>2144</v>
+        <v>2169</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>2145</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1559</v>
+        <v>1584</v>
       </c>
       <c r="B58" t="s">
-        <v>2146</v>
+        <v>2171</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2147</v>
+        <v>2172</v>
       </c>
       <c r="D58" t="s">
-        <v>2148</v>
+        <v>2173</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -19244,36 +19441,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2124</v>
+        <v>2149</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2149</v>
+        <v>2174</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>2150</v>
+        <v>2175</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2151</v>
+        <v>2176</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>2152</v>
+        <v>2177</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>2153</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1537</v>
+        <v>1555</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>2154</v>
+        <v>2179</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2155</v>
+        <v>2180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2156</v>
+        <v>2181</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -19282,10 +19479,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2154</v>
+        <v>2179</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2157</v>
+        <v>2182</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -19294,16 +19491,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>2124</v>
+        <v>2149</v>
       </c>
       <c r="B60" t="s">
-        <v>2158</v>
+        <v>2183</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>2159</v>
+        <v>2184</v>
       </c>
       <c r="D60" t="s">
-        <v>2160</v>
+        <v>2185</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -19312,10 +19509,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2161</v>
+        <v>2186</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2162</v>
+        <v>2187</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -19324,16 +19521,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1545</v>
+        <v>1563</v>
       </c>
       <c r="B61" t="s">
-        <v>2163</v>
+        <v>2188</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2164</v>
+        <v>2189</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2165</v>
+        <v>2190</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -19342,27 +19539,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2166</v>
+        <v>2191</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2167</v>
+        <v>2192</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2168</v>
+        <v>2193</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2169</v>
+        <v>2194</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2170</v>
+        <v>2195</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2171</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2172</v>
+        <v>2197</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -19371,10 +19568,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2173</v>
+        <v>2198</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2174</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -19386,24 +19583,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2175</v>
+        <v>2200</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2174</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>2124</v>
+        <v>2149</v>
       </c>
       <c r="B64" t="s">
-        <v>2176</v>
+        <v>2201</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2177</v>
+        <v>2202</v>
       </c>
       <c r="D64" t="s">
-        <v>2178</v>
+        <v>2203</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -19412,10 +19609,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2179</v>
+        <v>2204</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2180</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -19426,15 +19623,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2181</v>
+        <v>2206</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2180</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2182</v>
+        <v>2207</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -19443,15 +19640,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2183</v>
+        <v>2208</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2184</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2185</v>
+        <v>2210</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -19460,15 +19657,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2186</v>
+        <v>2211</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2187</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2188</v>
+        <v>2213</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -19477,15 +19674,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2189</v>
+        <v>2214</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2190</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2188</v>
+        <v>2213</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -19494,15 +19691,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2191</v>
+        <v>2216</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2190</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2192</v>
+        <v>2217</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -19511,27 +19708,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2193</v>
+        <v>2218</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2194</v>
+        <v>2219</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2195</v>
+        <v>2220</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2196</v>
+        <v>2221</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2197</v>
+        <v>2222</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2198</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2199</v>
+        <v>2224</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -19540,27 +19737,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2200</v>
+        <v>2225</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2201</v>
+        <v>2226</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2202</v>
+        <v>2227</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2203</v>
+        <v>2228</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2204</v>
+        <v>2229</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2205</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2206</v>
+        <v>2231</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -19569,7 +19766,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2207</v>
+        <v>2232</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -19577,7 +19774,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2206</v>
+        <v>2231</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -19586,33 +19783,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2208</v>
+        <v>2233</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2209</v>
+        <v>2234</v>
       </c>
       <c r="N73" t="s">
-        <v>2210</v>
+        <v>2235</v>
       </c>
       <c r="O73" t="s">
-        <v>2211</v>
+        <v>2236</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2212</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2213</v>
+        <v>2238</v>
       </c>
       <c r="C74" t="s">
-        <v>2214</v>
+        <v>2239</v>
       </c>
       <c r="D74" t="s">
-        <v>2215</v>
+        <v>2240</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -19621,33 +19818,33 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>2175</v>
+        <v>2200</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2174</v>
+        <v>2199</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>2216</v>
+        <v>2241</v>
       </c>
       <c r="N74" t="s">
-        <v>2217</v>
+        <v>2242</v>
       </c>
       <c r="O74" t="s">
-        <v>2218</v>
+        <v>2243</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>2219</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2220</v>
+        <v>2245</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>2221</v>
+        <v>2246</v>
       </c>
       <c r="D75" t="s">
-        <v>2222</v>
+        <v>2247</v>
       </c>
       <c r="E75" t="s">
         <v>222</v>
@@ -19659,29 +19856,29 @@
         <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2223</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2224</v>
+        <v>2249</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2225</v>
+        <v>2250</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2226</v>
+        <v>2251</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2227</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2228</v>
+        <v>2253</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -19690,27 +19887,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2229</v>
+        <v>2254</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2230</v>
+        <v>2255</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>2231</v>
+        <v>2256</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2232</v>
+        <v>2257</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>2233</v>
+        <v>2258</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>2234</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2235</v>
+        <v>2260</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -19719,15 +19916,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2236</v>
+        <v>2261</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2237</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2238</v>
+        <v>2263</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -19736,27 +19933,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2239</v>
+        <v>2264</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2240</v>
+        <v>2265</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2241</v>
+        <v>2266</v>
       </c>
       <c r="N79" t="s">
-        <v>2242</v>
+        <v>2267</v>
       </c>
       <c r="O79" t="s">
-        <v>2243</v>
+        <v>2268</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>2244</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2245</v>
+        <v>2270</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -19765,33 +19962,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2246</v>
+        <v>2271</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2247</v>
+        <v>2272</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2248</v>
+        <v>2273</v>
       </c>
       <c r="N80" t="s">
-        <v>2249</v>
+        <v>2274</v>
       </c>
       <c r="O80" t="s">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="P80" t="s">
-        <v>2251</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2252</v>
+        <v>2277</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2253</v>
+        <v>2278</v>
       </c>
       <c r="D81" t="s">
-        <v>2254</v>
+        <v>2279</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -19800,33 +19997,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2255</v>
+        <v>2280</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2256</v>
+        <v>2281</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2257</v>
+        <v>2282</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2258</v>
+        <v>2283</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2259</v>
+        <v>2284</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2260</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="B82" t="s">
-        <v>2261</v>
+        <v>2286</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>2262</v>
+        <v>2287</v>
       </c>
       <c r="D82" t="s">
-        <v>2263</v>
+        <v>2288</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -19835,30 +20032,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2264</v>
+        <v>2289</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2265</v>
+        <v>2290</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2266</v>
+        <v>2291</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2267</v>
+        <v>2292</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2268</v>
+        <v>2293</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2269</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="A83" s="2" t="s">
-        <v>1812</v>
+        <v>1837</v>
       </c>
       <c r="B83" t="s">
-        <v>2270</v>
+        <v>2295</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -19867,33 +20064,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2271</v>
+        <v>2296</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2272</v>
+        <v>2297</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2273</v>
+        <v>2298</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2274</v>
+        <v>2299</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2275</v>
+        <v>2300</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2276</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2277</v>
+        <v>2302</v>
       </c>
       <c r="C84" t="s">
-        <v>2278</v>
+        <v>2303</v>
       </c>
       <c r="D84" t="s">
-        <v>2279</v>
+        <v>2304</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -19902,33 +20099,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>2280</v>
+        <v>2305</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2281</v>
+        <v>2306</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2282</v>
+        <v>2307</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2283</v>
+        <v>2308</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2284</v>
+        <v>2309</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2285</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2286</v>
+        <v>2311</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>2287</v>
+        <v>2312</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -19937,27 +20134,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2052</v>
+        <v>2077</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2053</v>
+        <v>2078</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2288</v>
+        <v>2313</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2289</v>
+        <v>2314</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2290</v>
+        <v>2315</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2291</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2292</v>
+        <v>2317</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -19966,27 +20163,27 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2293</v>
+        <v>2318</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2294</v>
+        <v>2319</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>2295</v>
+        <v>2320</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2296</v>
+        <v>2321</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>2297</v>
+        <v>2322</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2298</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="B87" t="s">
-        <v>2299</v>
+        <v>2324</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -19995,21 +20192,21 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>2300</v>
+        <v>2325</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2301</v>
+        <v>2326</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>2302</v>
+        <v>2327</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>2303</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="88" ht="18" spans="1:16">
       <c r="B88" t="s">
-        <v>2304</v>
+        <v>2329</v>
       </c>
       <c r="E88" t="s">
         <v>222</v>
@@ -20018,21 +20215,21 @@
         <v>1</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>2305</v>
+        <v>2330</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>2306</v>
+        <v>2331</v>
       </c>
       <c r="M88" t="s">
-        <v>2307</v>
+        <v>2332</v>
       </c>
       <c r="N88" t="s">
-        <v>2308</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="B89" t="s">
-        <v>2309</v>
+        <v>2334</v>
       </c>
       <c r="E89" t="s">
         <v>222</v>
@@ -20041,22 +20238,22 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>2310</v>
+        <v>2335</v>
       </c>
       <c r="H89" t="s">
-        <v>2311</v>
+        <v>2336</v>
       </c>
       <c r="M89" t="s">
-        <v>2312</v>
+        <v>2337</v>
       </c>
       <c r="N89" t="s">
-        <v>2313</v>
+        <v>2338</v>
       </c>
       <c r="O89" t="s">
-        <v>2314</v>
+        <v>2339</v>
       </c>
       <c r="P89" t="s">
-        <v>2315</v>
+        <v>2340</v>
       </c>
     </row>
   </sheetData>
@@ -20247,16 +20444,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1748</v>
+        <v>1773</v>
       </c>
       <c r="B3" t="s">
-        <v>2316</v>
+        <v>2341</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2317</v>
+        <v>2342</v>
       </c>
       <c r="D3" t="s">
-        <v>2318</v>
+        <v>2343</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -20265,42 +20462,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1744</v>
+        <v>1769</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2319</v>
+        <v>2344</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2320</v>
+        <v>2345</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2321</v>
+        <v>2346</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2322</v>
+        <v>2347</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2323</v>
+        <v>2348</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2324</v>
+        <v>2349</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2325</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2326</v>
+        <v>2351</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2327</v>
+        <v>2352</v>
       </c>
       <c r="D4" t="s">
-        <v>2328</v>
+        <v>2353</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -20309,21 +20506,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2329</v>
+        <v>2354</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2330</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2331</v>
+        <v>2356</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2332</v>
+        <v>2357</v>
       </c>
       <c r="D5" t="s">
-        <v>2333</v>
+        <v>2358</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -20332,33 +20529,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2334</v>
+        <v>2359</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2335</v>
+        <v>2360</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2336</v>
+        <v>2361</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2337</v>
+        <v>2362</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2338</v>
+        <v>2363</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2339</v>
+        <v>2364</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2340</v>
+        <v>2365</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2341</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2342</v>
+        <v>2367</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -20367,33 +20564,33 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2343</v>
+        <v>2368</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2344</v>
+        <v>2369</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2345</v>
+        <v>2370</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2346</v>
+        <v>2371</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2347</v>
+        <v>2372</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2348</v>
+        <v>2373</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2349</v>
+        <v>2374</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2350</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2351</v>
+        <v>2376</v>
       </c>
       <c r="E7" t="s">
         <v>815</v>
@@ -20402,21 +20599,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2352</v>
+        <v>2377</v>
       </c>
       <c r="H7" t="s">
-        <v>2353</v>
+        <v>2378</v>
       </c>
       <c r="L7" t="s">
-        <v>2354</v>
+        <v>2379</v>
       </c>
       <c r="M7" t="s">
-        <v>2355</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2351</v>
+        <v>2376</v>
       </c>
       <c r="E8" t="s">
         <v>815</v>
@@ -20425,27 +20622,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2356</v>
+        <v>2381</v>
       </c>
       <c r="H8" t="s">
-        <v>2353</v>
+        <v>2378</v>
       </c>
       <c r="L8" t="s">
-        <v>2357</v>
+        <v>2382</v>
       </c>
       <c r="M8" t="s">
-        <v>2355</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:32">
       <c r="B9" t="s">
-        <v>2358</v>
+        <v>2383</v>
       </c>
       <c r="C9" t="s">
-        <v>2359</v>
+        <v>2384</v>
       </c>
       <c r="D9" t="s">
-        <v>2360</v>
+        <v>2385</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -20454,28 +20651,28 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>2361</v>
+        <v>2386</v>
       </c>
       <c r="H9" t="s">
-        <v>2362</v>
+        <v>2387</v>
       </c>
       <c r="L9" t="s">
-        <v>2363</v>
+        <v>2388</v>
       </c>
       <c r="M9" t="s">
-        <v>2364</v>
+        <v>2389</v>
       </c>
       <c r="N9" t="s">
-        <v>2365</v>
+        <v>2390</v>
       </c>
       <c r="O9" t="s">
-        <v>2366</v>
+        <v>2391</v>
       </c>
       <c r="P9" t="s">
-        <v>2367</v>
+        <v>2392</v>
       </c>
       <c r="Q9" t="s">
-        <v>2368</v>
+        <v>2393</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="2394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="2415">
   <si>
     <r>
       <rPr>
@@ -3152,6 +3152,9 @@
     <t>しんじた</t>
   </si>
   <si>
+    <t>朝拜</t>
+  </si>
+  <si>
     <t>拝む</t>
   </si>
   <si>
@@ -3168,6 +3171,33 @@
   </si>
   <si>
     <t>おがんだ</t>
+  </si>
+  <si>
+    <t>战胜，越过</t>
+  </si>
+  <si>
+    <t>自動車で丘「おか」を乗り越える</t>
+  </si>
+  <si>
+    <t>坐着汽车越过山冈</t>
+  </si>
+  <si>
+    <t>乗り越える</t>
+  </si>
+  <si>
+    <t>のりこえる</t>
+  </si>
+  <si>
+    <t>乗り越えて</t>
+  </si>
+  <si>
+    <t>のりこえて</t>
+  </si>
+  <si>
+    <t>乗り越えた</t>
+  </si>
+  <si>
+    <t>のりこえた</t>
   </si>
   <si>
     <t>着く</t>
@@ -4604,6 +4634,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>凹陷，退</t>
     </r>
     <r>
@@ -7584,6 +7620,39 @@
   </si>
   <si>
     <t>ことなった</t>
+  </si>
+  <si>
+    <t>达到，波及，影响到，遭到</t>
+  </si>
+  <si>
+    <t>生命に危険を及ぼす</t>
+  </si>
+  <si>
+    <t>使生命遭到危险</t>
+  </si>
+  <si>
+    <t>及ぼす</t>
+  </si>
+  <si>
+    <t>およぼす</t>
+  </si>
+  <si>
+    <t>及ばない</t>
+  </si>
+  <si>
+    <t>およばない</t>
+  </si>
+  <si>
+    <t>及ぼして</t>
+  </si>
+  <si>
+    <t>およぼして</t>
+  </si>
+  <si>
+    <t>及ぼした</t>
+  </si>
+  <si>
+    <t>およぼした</t>
   </si>
 </sst>
 </file>
@@ -7862,17 +7931,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -10286,7 +10355,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="29.8888888888889" customWidth="1"/>
@@ -12959,7 +13028,6 @@
         <v>928</v>
       </c>
     </row>
-    <row r="93" customFormat="1"/>
     <row r="94" ht="18" spans="1:16">
       <c r="B94" t="s">
         <v>929</v>
@@ -13025,6 +13093,9 @@
       </c>
     </row>
     <row r="96" ht="18" spans="1:16">
+      <c r="B96" t="s">
+        <v>945</v>
+      </c>
       <c r="E96" s="2" t="s">
         <v>49</v>
       </c>
@@ -13032,22 +13103,57 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H96" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M96" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="N96" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="O96" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="P96" t="s">
-        <v>950</v>
+        <v>951</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16">
+      <c r="B97" t="s">
+        <v>952</v>
+      </c>
+      <c r="C97" t="s">
+        <v>953</v>
+      </c>
+      <c r="D97" t="s">
+        <v>954</v>
+      </c>
+      <c r="E97" t="s">
+        <v>49</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+      <c r="G97" t="s">
+        <v>955</v>
+      </c>
+      <c r="H97" t="s">
+        <v>956</v>
+      </c>
+      <c r="M97" t="s">
+        <v>957</v>
+      </c>
+      <c r="N97" t="s">
+        <v>958</v>
+      </c>
+      <c r="O97" t="s">
+        <v>959</v>
+      </c>
+      <c r="P97" t="s">
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -13229,28 +13335,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="H3" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
     </row>
     <row r="4" ht="31.2" customHeight="1" spans="2:31">
@@ -13261,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="2" t="s">
@@ -13279,73 +13385,73 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="F5" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="H5" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="I5" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
     </row>
     <row r="6" ht="18" spans="2:31">
       <c r="C6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="H6" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>550</v>
@@ -13354,16 +13460,16 @@
         <v>551</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7" ht="18" spans="2:31">
@@ -13374,7 +13480,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>728</v>
@@ -13383,16 +13489,16 @@
         <v>729</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>730</v>
@@ -13421,16 +13527,16 @@
         <v>729</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>735</v>
@@ -13453,37 +13559,37 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:31">
@@ -13494,38 +13600,38 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>1003</v>
+        <v>1013</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="O10" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="P10" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="11" ht="18" spans="2:31">
@@ -13536,16 +13642,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -13556,7 +13662,7 @@
     </row>
     <row r="12" ht="18" spans="2:31">
       <c r="B12" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>49</v>
@@ -13567,25 +13673,25 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" spans="2:31">
       <c r="B13" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>49</v>
@@ -13594,39 +13700,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="18" spans="2:31">
       <c r="B14" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>222</v>
@@ -13635,21 +13741,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="F14" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="H14" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="15" ht="18" spans="2:31">
       <c r="B15" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>49</v>
@@ -13658,18 +13764,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -13678,7 +13784,7 @@
     </row>
     <row r="16" ht="18" spans="2:31">
       <c r="B16" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>49</v>
@@ -13687,10 +13793,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>374</v>
@@ -13701,7 +13807,7 @@
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="B17" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>49</v>
@@ -13710,19 +13816,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1049</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="B18" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>49</v>
@@ -13733,15 +13839,15 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>49</v>
@@ -13752,15 +13858,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>1054</v>
+        <v>1064</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>49</v>
@@ -13769,10 +13875,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>347</v>
@@ -13789,21 +13895,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="B22" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -13812,24 +13918,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="B23" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -13840,30 +13946,30 @@
       <c r="E23" s="2"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="M23" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
       <c r="N23" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="B24" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>49</v>
@@ -13874,30 +13980,30 @@
       <c r="E24" s="2"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="B25" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>49</v>
@@ -13906,28 +14012,28 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>49</v>
@@ -13936,27 +14042,27 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="M26" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="N26" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -13965,21 +14071,21 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>49</v>
@@ -13988,33 +14094,33 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>49</v>
@@ -14023,39 +14129,39 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="F29" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>222</v>
@@ -14064,21 +14170,21 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="F30" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>49</v>
@@ -14087,15 +14193,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>49</v>
@@ -14104,33 +14210,33 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -14139,39 +14245,39 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="F33" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>49</v>
@@ -14180,33 +14286,33 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>49</v>
@@ -14215,33 +14321,33 @@
         <v>1</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>49</v>
@@ -14250,39 +14356,39 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="F36" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
@@ -14291,33 +14397,33 @@
         <v>1</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1182</v>
+        <v>1192</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1184</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>815</v>
@@ -14326,16 +14432,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
       <c r="F38" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="G38" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -14346,10 +14452,10 @@
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="A39" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="B39" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>49</v>
@@ -14361,30 +14467,30 @@
         <v>701</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1192</v>
+        <v>1202</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>1193</v>
+        <v>1203</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1194</v>
+        <v>1204</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>49</v>
@@ -14393,10 +14499,10 @@
         <v>2</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -14407,10 +14513,10 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="B41" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>49</v>
@@ -14419,18 +14525,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="B42" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -14439,10 +14545,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
@@ -14453,10 +14559,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
@@ -14467,33 +14573,33 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="F44" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="I44" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="K44" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="B45" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>49</v>
@@ -14502,34 +14608,34 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="F45" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -14538,33 +14644,33 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="B47" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>49</v>
@@ -14573,15 +14679,15 @@
         <v>2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>49</v>
@@ -14590,30 +14696,30 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="N48" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="B49" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>815</v>
@@ -14622,33 +14728,33 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="B50" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>49</v>
@@ -14657,36 +14763,36 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
       <c r="K50" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="B51" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>222</v>
@@ -14695,21 +14801,21 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
       <c r="F51" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="B52" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -14718,21 +14824,21 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="F52" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="53" ht="27.6" spans="1:16">
       <c r="B53" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>222</v>
@@ -14741,21 +14847,21 @@
         <v>1</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="B54" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>49</v>
@@ -14764,33 +14870,33 @@
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
       <c r="M54" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="B55" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>815</v>
@@ -14799,33 +14905,33 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="F55" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="M55" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="B56" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>49</v>
@@ -14834,10 +14940,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
@@ -14848,30 +14954,30 @@
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="F57" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="O57" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="B58" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>
@@ -14880,39 +14986,39 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="B59" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>49</v>
@@ -14921,39 +15027,39 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="H59" s="2" t="s">
-        <v>1305</v>
-      </c>
       <c r="I59" s="2" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="B60" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>815</v>
@@ -14962,39 +15068,39 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="B61" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>49</v>
@@ -15003,39 +15109,39 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>49</v>
@@ -15044,21 +15150,21 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="F62" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="G62" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="H62" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
       <c r="B63" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>815</v>
@@ -15067,33 +15173,33 @@
         <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="H63" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="K63" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="L63" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="M63" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="N63" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="O63" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="P63" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="B64" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>49</v>
@@ -15102,15 +15208,15 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="H64" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:16">
       <c r="B65" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>49</v>
@@ -15119,33 +15225,33 @@
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
       <c r="H65" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="K65" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="L65" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="M65" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="N65" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="O65" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="P65" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="66" ht="18" spans="1:16">
       <c r="B66" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>49</v>
@@ -15154,36 +15260,36 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="H66" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="K66" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="L66" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="M66" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="N66" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
       <c r="O66" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="P66" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="67" ht="27.6" spans="1:16">
       <c r="A67" s="17" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="B67" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>49</v>
@@ -15192,33 +15298,33 @@
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="H67" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="K67" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="L67" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="M67" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="N67" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="O67" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="P67" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="B68" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="C68" t="s">
         <v>222</v>
@@ -15227,36 +15333,36 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="H68" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="K68" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="L68" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="M68" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="N68" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="O68" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="P68" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:16">
       <c r="A69" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="B69" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>49</v>
@@ -15265,36 +15371,36 @@
         <v>2</v>
       </c>
       <c r="G69" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="H69" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="K69" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="L69" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="M69" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="N69" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="O69" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="P69" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="B70" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="C70" t="s">
         <v>222</v>
@@ -15303,33 +15409,33 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="H70" t="s">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="K70" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="L70" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="M70" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="N70" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="O70" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="P70" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="71" ht="18" spans="1:16">
       <c r="B71" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>49</v>
@@ -15338,27 +15444,27 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="H71" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="K71" t="s">
-        <v>1417</v>
+        <v>1427</v>
       </c>
       <c r="L71" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="M71" t="s">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="N71" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="72" customFormat="1" ht="18" spans="1:16">
       <c r="B72" s="2" t="s">
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>49</v>
@@ -15367,33 +15473,33 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="F72" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
       <c r="G72" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
       <c r="H72" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="M72" t="s">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="N72" t="s">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="O72" t="s">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="P72" t="s">
-        <v>1429</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="73" ht="18" spans="1:16">
       <c r="B73" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>49</v>
@@ -15402,33 +15508,33 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="H73" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="K73" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="L73" t="s">
-        <v>1434</v>
+        <v>1444</v>
       </c>
       <c r="M73" t="s">
-        <v>1435</v>
+        <v>1445</v>
       </c>
       <c r="N73" t="s">
-        <v>1436</v>
+        <v>1446</v>
       </c>
       <c r="O73" t="s">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="P73" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="B74" t="s">
-        <v>1439</v>
+        <v>1449</v>
       </c>
       <c r="C74" t="s">
         <v>222</v>
@@ -15437,33 +15543,33 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>1440</v>
+        <v>1450</v>
       </c>
       <c r="F74" t="s">
-        <v>1441</v>
+        <v>1451</v>
       </c>
       <c r="G74" t="s">
-        <v>1442</v>
+        <v>1452</v>
       </c>
       <c r="H74" t="s">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="M74" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="N74" t="s">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="O74" t="s">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="P74" t="s">
-        <v>1447</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="75" ht="18" spans="1:16">
       <c r="B75" t="s">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>815</v>
@@ -15472,34 +15578,34 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="F75" t="s">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="G75" t="s">
-        <v>1451</v>
+        <v>1461</v>
       </c>
       <c r="H75" t="s">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="K75" t="s">
-        <v>1453</v>
+        <v>1463</v>
       </c>
       <c r="L75" t="s">
-        <v>1454</v>
+        <v>1464</v>
       </c>
       <c r="M75" t="s">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="N75" t="s">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="O75" t="s">
-        <v>1457</v>
+        <v>1467</v>
       </c>
       <c r="P75" t="s">
-        <v>1458</v>
+        <v>1468</v>
       </c>
     </row>
   </sheetData>
@@ -15672,28 +15778,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1459</v>
+        <v>1469</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1460</v>
+        <v>1470</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1461</v>
+        <v>1471</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1462</v>
+        <v>1472</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="N3" t="s">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1466</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -15704,28 +15810,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="I4" t="s">
-        <v>1469</v>
+        <v>1479</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="M4" t="s">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1472</v>
+        <v>1482</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -15736,60 +15842,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1484</v>
+        <v>1494</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1485</v>
+        <v>1495</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -15797,21 +15903,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -15820,15 +15926,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -15845,7 +15951,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -15854,36 +15960,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="M10" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="N10" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="B11" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -15892,42 +15998,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="M11" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="B12" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="D12" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -15936,33 +16042,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -15971,39 +16077,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="B14" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16012,22 +16118,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -16039,33 +16145,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="N15" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16074,18 +16180,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="B17" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -16094,30 +16200,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="B18" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -16126,27 +16232,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -16155,27 +16261,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -16184,30 +16290,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="B21" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -16216,40 +16322,40 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="K21" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="M21" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="D22" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="E22" t="s">
         <v>222</v>
@@ -16258,34 +16364,34 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1597</v>
+        <v>1607</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1598</v>
+        <v>1608</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1599</v>
+        <v>1609</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1601</v>
+        <v>1611</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" t="s">
@@ -16295,33 +16401,33 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="B24" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="E24" t="s">
         <v>222</v>
@@ -16330,27 +16436,27 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1616</v>
+        <v>1626</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1617</v>
+        <v>1627</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -16359,33 +16465,33 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1619</v>
+        <v>1629</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -16394,27 +16500,27 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
       <c r="E27" t="s">
         <v>222</v>
@@ -16423,36 +16529,36 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="I27" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1640</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
       <c r="C28" t="s">
-        <v>1642</v>
+        <v>1652</v>
       </c>
       <c r="D28" t="s">
-        <v>1643</v>
+        <v>1653</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -16461,27 +16567,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -16490,27 +16596,27 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
       <c r="E30" t="s">
         <v>222</v>
@@ -16519,10 +16625,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
@@ -16533,33 +16639,33 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
       <c r="C32" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="D32" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -16568,21 +16674,21 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1670</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1671</v>
+        <v>1681</v>
       </c>
       <c r="C33" t="s">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="D33" t="s">
-        <v>1673</v>
+        <v>1683</v>
       </c>
       <c r="E33" t="s">
         <v>222</v>
@@ -16591,33 +16697,33 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1675</v>
+        <v>1685</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1677</v>
+        <v>1687</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1678</v>
+        <v>1688</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1679</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="C34" t="s">
-        <v>1681</v>
+        <v>1691</v>
       </c>
       <c r="D34" t="s">
-        <v>1682</v>
+        <v>1692</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>815</v>
@@ -16626,30 +16732,30 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1683</v>
+        <v>1693</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1684</v>
+        <v>1694</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1686</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>1687</v>
+        <v>1697</v>
       </c>
       <c r="B35" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
       <c r="D35" t="s">
-        <v>1690</v>
+        <v>1700</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -16658,33 +16764,33 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1692</v>
+        <v>1702</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1693</v>
+        <v>1703</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1694</v>
+        <v>1704</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1695</v>
+        <v>1705</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1698</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -16693,27 +16799,27 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1705</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1706</v>
+        <v>1716</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>222</v>
@@ -16722,33 +16828,33 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1708</v>
+        <v>1718</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1709</v>
+        <v>1719</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>815</v>
@@ -16757,15 +16863,15 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="H38" t="s">
-        <v>1717</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1718</v>
+        <v>1728</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
@@ -16774,39 +16880,39 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="H39" t="s">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="K39" t="s">
-        <v>1721</v>
+        <v>1731</v>
       </c>
       <c r="L39" t="s">
-        <v>1722</v>
+        <v>1732</v>
       </c>
       <c r="M39" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="N39" t="s">
-        <v>1724</v>
+        <v>1734</v>
       </c>
       <c r="O39" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="P39" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="C40" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
       <c r="D40" t="s">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>222</v>
@@ -16815,39 +16921,39 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="H40" t="s">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="K40" t="s">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="L40" t="s">
-        <v>1733</v>
+        <v>1743</v>
       </c>
       <c r="M40" t="s">
-        <v>1734</v>
+        <v>1744</v>
       </c>
       <c r="N40" t="s">
-        <v>1735</v>
+        <v>1745</v>
       </c>
       <c r="O40" t="s">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="P40" t="s">
-        <v>1737</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="B41" t="s">
-        <v>1738</v>
+        <v>1748</v>
       </c>
       <c r="C41" t="s">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="D41" t="s">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>222</v>
@@ -16856,18 +16962,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>1741</v>
+        <v>1751</v>
       </c>
       <c r="H41" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="B42" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="C42" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="D42" t="s">
         <v>926</v>
@@ -16879,21 +16985,21 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="H42" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="K42" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="L42" t="s">
-        <v>1746</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1747</v>
+        <v>1757</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>815</v>
@@ -16902,39 +17008,39 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="H43" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="K43" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="L43" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="M43" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="N43" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="O43" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="P43" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
       <c r="C44" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="D44" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -16943,34 +17049,34 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="H44" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="I44" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="J44" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="K44" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="L44" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="M44" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="N44" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="O44" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="P44" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="46" ht="16.8" spans="1:16">
@@ -17148,16 +17254,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="B3" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="D3" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -17166,31 +17272,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -17200,42 +17306,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="B4" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="C4" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="D4" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -17244,37 +17350,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="C5" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="D5" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17283,65 +17389,65 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="C7" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="D7" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
       <c r="E7" t="s">
         <v>222</v>
@@ -17350,28 +17456,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="H7" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="L7" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="M7" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="N7" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="O7" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
       <c r="P7" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="Q7" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
     </row>
   </sheetData>
@@ -17553,30 +17659,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1827</v>
+        <v>1837</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1829</v>
+        <v>1839</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -17586,16 +17692,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1836</v>
+        <v>1846</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -17610,34 +17716,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1842</v>
+        <v>1852</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1843</v>
+        <v>1853</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -17657,7 +17763,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17666,34 +17772,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1848</v>
+        <v>1858</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1851</v>
+        <v>1861</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1854</v>
+        <v>1864</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1856</v>
+        <v>1866</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -17703,16 +17809,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1858</v>
+        <v>1868</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -17721,13 +17827,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1863</v>
+        <v>1873</v>
       </c>
       <c r="D6" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -17736,30 +17842,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1868</v>
+        <v>1878</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -17771,10 +17877,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -17783,13 +17889,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="D7" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -17798,34 +17904,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -17845,7 +17951,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -17854,75 +17960,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -17930,7 +18036,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -17939,10 +18045,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -17975,7 +18081,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -17984,10 +18090,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -18016,7 +18122,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -18025,37 +18131,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1908</v>
+        <v>1918</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1911</v>
+        <v>1921</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -18068,10 +18174,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -18079,7 +18185,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -18088,20 +18194,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -18123,10 +18229,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="B13" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -18135,20 +18241,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -18170,10 +18276,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="B14" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -18182,20 +18288,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -18217,10 +18323,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -18230,39 +18336,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1938</v>
+        <v>1948</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="K15" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -18271,34 +18377,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -18309,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -18320,7 +18426,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1958</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -18331,10 +18437,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -18346,18 +18452,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1963</v>
+        <v>1973</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -18367,42 +18473,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -18412,39 +18518,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1976</v>
+        <v>1986</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1978</v>
+        <v>1988</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -18454,27 +18560,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -18483,39 +18589,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -18524,10 +18630,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -18540,7 +18646,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -18549,26 +18655,26 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -18579,32 +18685,32 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
       <c r="B28" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -18614,39 +18720,39 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
       <c r="B29" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>222</v>
@@ -18655,27 +18761,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2023</v>
+        <v>2033</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>2025</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -18684,27 +18790,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>2032</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -18713,27 +18819,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -18748,21 +18854,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -18771,22 +18877,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -18796,30 +18902,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -18828,10 +18934,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -18842,30 +18948,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -18874,30 +18980,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="M38" t="s">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -18907,18 +19013,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -18928,22 +19034,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -18956,15 +19062,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -18973,54 +19079,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="N42" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
       <c r="N43" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -19029,30 +19135,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>2095</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>2085</v>
-      </c>
       <c r="M44" s="2" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="N44" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="C45" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -19061,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -19069,10 +19175,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="B46" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -19081,24 +19187,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2104</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="B47" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="D47" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -19107,33 +19213,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="M47" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>2114</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2116</v>
+        <v>2126</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -19142,18 +19248,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2118</v>
+        <v>2128</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="B49" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -19162,28 +19268,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -19192,30 +19298,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2128</v>
+        <v>2138</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="B51" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -19224,34 +19330,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="D52" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -19260,24 +19366,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="B53" t="s">
-        <v>2141</v>
+        <v>2151</v>
       </c>
       <c r="C53" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="D53" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -19286,18 +19392,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
       <c r="B54" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -19306,36 +19412,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="B55" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="C55" t="s">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="D55" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -19344,19 +19450,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2153</v>
+        <v>2163</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="B56" t="s">
-        <v>2155</v>
+        <v>2165</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -19365,36 +19471,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>2160</v>
+        <v>2170</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>2162</v>
+        <v>2172</v>
       </c>
       <c r="B57" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>2164</v>
+        <v>2174</v>
       </c>
       <c r="D57" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -19403,36 +19509,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2166</v>
+        <v>2176</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>2170</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="B58" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2172</v>
+        <v>2182</v>
       </c>
       <c r="D58" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -19441,36 +19547,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2176</v>
+        <v>2186</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>2178</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2180</v>
+        <v>2190</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -19479,10 +19585,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -19491,16 +19597,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="B60" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>2184</v>
+        <v>2194</v>
       </c>
       <c r="D60" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -19509,10 +19615,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -19521,16 +19627,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="B61" t="s">
-        <v>2188</v>
+        <v>2198</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -19539,27 +19645,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -19568,10 +19674,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -19583,24 +19689,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="B64" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="D64" t="s">
-        <v>2203</v>
+        <v>2213</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -19609,10 +19715,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -19623,15 +19729,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2206</v>
+        <v>2216</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -19640,15 +19746,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2208</v>
+        <v>2218</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -19657,15 +19763,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -19674,15 +19780,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -19691,15 +19797,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -19708,27 +19814,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -19737,27 +19843,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -19766,7 +19872,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -19774,7 +19880,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -19783,33 +19889,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="N73" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
       <c r="O73" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="C74" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="D74" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -19818,33 +19924,33 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="N74" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
       <c r="O74" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="D75" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="E75" t="s">
         <v>222</v>
@@ -19856,29 +19962,29 @@
         <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -19887,27 +19993,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -19916,15 +20022,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -19933,27 +20039,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="N79" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="O79" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -19962,33 +20068,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="N80" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
       <c r="O80" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="P80" t="s">
-        <v>2276</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2278</v>
+        <v>2288</v>
       </c>
       <c r="D81" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -19997,33 +20103,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2280</v>
+        <v>2290</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2284</v>
+        <v>2294</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="B82" t="s">
-        <v>2286</v>
+        <v>2296</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="D82" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -20032,30 +20138,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="A83" s="2" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="B83" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -20064,33 +20170,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="C84" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="D84" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -20099,33 +20205,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -20134,27 +20240,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -20163,27 +20269,27 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="B87" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -20192,21 +20298,21 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="88" ht="18" spans="1:16">
       <c r="B88" t="s">
-        <v>2329</v>
+        <v>2339</v>
       </c>
       <c r="E88" t="s">
         <v>222</v>
@@ -20215,21 +20321,21 @@
         <v>1</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="M88" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="N88" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="B89" t="s">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="E89" t="s">
         <v>222</v>
@@ -20238,22 +20344,22 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="H89" t="s">
-        <v>2336</v>
+        <v>2346</v>
       </c>
       <c r="M89" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="N89" t="s">
-        <v>2338</v>
+        <v>2348</v>
       </c>
       <c r="O89" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
       <c r="P89" t="s">
-        <v>2340</v>
+        <v>2350</v>
       </c>
     </row>
   </sheetData>
@@ -20279,7 +20385,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
@@ -20444,16 +20550,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="B3" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2342</v>
+        <v>2352</v>
       </c>
       <c r="D3" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -20462,42 +20568,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2345</v>
+        <v>2355</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2347</v>
+        <v>2357</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2352</v>
+        <v>2362</v>
       </c>
       <c r="D4" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -20506,21 +20612,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="D5" t="s">
-        <v>2358</v>
+        <v>2368</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -20529,33 +20635,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2364</v>
+        <v>2374</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2365</v>
+        <v>2375</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2366</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -20564,33 +20670,33 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2371</v>
+        <v>2381</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2372</v>
+        <v>2382</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2374</v>
+        <v>2384</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2375</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2376</v>
+        <v>2386</v>
       </c>
       <c r="E7" t="s">
         <v>815</v>
@@ -20599,21 +20705,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2377</v>
+        <v>2387</v>
       </c>
       <c r="H7" t="s">
-        <v>2378</v>
+        <v>2388</v>
       </c>
       <c r="L7" t="s">
-        <v>2379</v>
+        <v>2389</v>
       </c>
       <c r="M7" t="s">
-        <v>2380</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2376</v>
+        <v>2386</v>
       </c>
       <c r="E8" t="s">
         <v>815</v>
@@ -20622,27 +20728,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2381</v>
+        <v>2391</v>
       </c>
       <c r="H8" t="s">
-        <v>2378</v>
+        <v>2388</v>
       </c>
       <c r="L8" t="s">
-        <v>2382</v>
+        <v>2392</v>
       </c>
       <c r="M8" t="s">
-        <v>2380</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:32">
       <c r="B9" t="s">
-        <v>2383</v>
+        <v>2393</v>
       </c>
       <c r="C9" t="s">
-        <v>2384</v>
+        <v>2394</v>
       </c>
       <c r="D9" t="s">
-        <v>2385</v>
+        <v>2395</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -20651,28 +20757,69 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>2386</v>
+        <v>2396</v>
       </c>
       <c r="H9" t="s">
-        <v>2387</v>
+        <v>2397</v>
       </c>
       <c r="L9" t="s">
-        <v>2388</v>
+        <v>2398</v>
       </c>
       <c r="M9" t="s">
-        <v>2389</v>
+        <v>2399</v>
       </c>
       <c r="N9" t="s">
-        <v>2390</v>
+        <v>2400</v>
       </c>
       <c r="O9" t="s">
-        <v>2391</v>
+        <v>2401</v>
       </c>
       <c r="P9" t="s">
-        <v>2392</v>
+        <v>2402</v>
       </c>
       <c r="Q9" t="s">
-        <v>2393</v>
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:32">
+      <c r="B10" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2408</v>
+      </c>
+      <c r="L10" t="s">
+        <v>2409</v>
+      </c>
+      <c r="M10" t="s">
+        <v>2410</v>
+      </c>
+      <c r="N10" t="s">
+        <v>2411</v>
+      </c>
+      <c r="O10" t="s">
+        <v>2412</v>
+      </c>
+      <c r="P10" t="s">
+        <v>2413</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>2414</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="2415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="2434">
   <si>
     <r>
       <rPr>
@@ -4764,6 +4764,36 @@
     <t>せまった</t>
   </si>
   <si>
+    <t>春雨に煙る京都東山</t>
+  </si>
+  <si>
+    <t>春雨朦胧的京都东山</t>
+  </si>
+  <si>
+    <t>煙る</t>
+  </si>
+  <si>
+    <t>けむる</t>
+  </si>
+  <si>
+    <t>煙らない</t>
+  </si>
+  <si>
+    <t>けむらない</t>
+  </si>
+  <si>
+    <t>煙って</t>
+  </si>
+  <si>
+    <t>けむって</t>
+  </si>
+  <si>
+    <t>煙った</t>
+  </si>
+  <si>
+    <t>けむった</t>
+  </si>
+  <si>
     <t>誓う</t>
   </si>
   <si>
@@ -7412,6 +7442,9 @@
     <t>あらためた</t>
   </si>
   <si>
+    <t>鎮める</t>
+  </si>
+  <si>
     <t>煽动</t>
   </si>
   <si>
@@ -7425,6 +7458,30 @@
   </si>
   <si>
     <t>あおいだ</t>
+  </si>
+  <si>
+    <t>镇定</t>
+  </si>
+  <si>
+    <t>鎮める｜沈める｜静める</t>
+  </si>
+  <si>
+    <t>しずめる</t>
+  </si>
+  <si>
+    <t>鎮めて</t>
+  </si>
+  <si>
+    <t>しずめて</t>
+  </si>
+  <si>
+    <t>鎮めた</t>
+  </si>
+  <si>
+    <t>しずめた</t>
+  </si>
+  <si>
+    <t>沈める</t>
   </si>
   <si>
     <t>剥下，揭下</t>
@@ -13179,7 +13236,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE75"/>
+  <dimension ref="A1:AE76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -15606,6 +15663,44 @@
       </c>
       <c r="P75" t="s">
         <v>1468</v>
+      </c>
+    </row>
+    <row r="76" ht="18" spans="1:16">
+      <c r="C76" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1472</v>
+      </c>
+      <c r="K76" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M76" t="s">
+        <v>1475</v>
+      </c>
+      <c r="N76" t="s">
+        <v>1476</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1477</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1478</v>
       </c>
     </row>
   </sheetData>
@@ -15778,28 +15873,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1469</v>
+        <v>1479</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1472</v>
+        <v>1482</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="N3" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -15810,28 +15905,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="I4" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="M4" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1484</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -15842,60 +15937,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1485</v>
+        <v>1495</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -15903,21 +15998,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -15926,15 +16021,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -15951,7 +16046,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -15960,36 +16055,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="M10" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="N10" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="B11" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -15998,42 +16093,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="M11" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="B12" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="D12" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -16042,33 +16137,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -16077,39 +16172,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="B14" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16118,22 +16213,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -16145,33 +16240,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="N15" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16180,18 +16275,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="B17" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -16200,30 +16295,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="B18" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -16232,27 +16327,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -16261,27 +16356,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -16290,30 +16385,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="B21" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -16322,40 +16417,40 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="K21" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1597</v>
+        <v>1607</v>
       </c>
       <c r="M21" t="s">
-        <v>1598</v>
+        <v>1608</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1599</v>
+        <v>1609</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1601</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="D22" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="E22" t="s">
         <v>222</v>
@@ -16364,34 +16459,34 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" t="s">
@@ -16401,33 +16496,33 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1616</v>
+        <v>1626</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1617</v>
+        <v>1627</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1619</v>
+        <v>1629</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1621</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="B24" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="E24" t="s">
         <v>222</v>
@@ -16436,27 +16531,27 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -16465,33 +16560,33 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -16500,27 +16595,27 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1642</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1643</v>
+        <v>1653</v>
       </c>
       <c r="E27" t="s">
         <v>222</v>
@@ -16529,36 +16624,36 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
       <c r="I27" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
       <c r="C28" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
       <c r="D28" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -16567,27 +16662,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -16596,27 +16691,27 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="E30" t="s">
         <v>222</v>
@@ -16625,10 +16720,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
@@ -16639,33 +16734,33 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1671</v>
+        <v>1681</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1673</v>
+        <v>1683</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1675</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="C32" t="s">
-        <v>1677</v>
+        <v>1687</v>
       </c>
       <c r="D32" t="s">
-        <v>1678</v>
+        <v>1688</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -16674,21 +16769,21 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1679</v>
+        <v>1689</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1681</v>
+        <v>1691</v>
       </c>
       <c r="C33" t="s">
-        <v>1682</v>
+        <v>1692</v>
       </c>
       <c r="D33" t="s">
-        <v>1683</v>
+        <v>1693</v>
       </c>
       <c r="E33" t="s">
         <v>222</v>
@@ -16697,33 +16792,33 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1684</v>
+        <v>1694</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1686</v>
+        <v>1696</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1687</v>
+        <v>1697</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1690</v>
+        <v>1700</v>
       </c>
       <c r="C34" t="s">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="D34" t="s">
-        <v>1692</v>
+        <v>1702</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>815</v>
@@ -16732,30 +16827,30 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1693</v>
+        <v>1703</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1694</v>
+        <v>1704</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1695</v>
+        <v>1705</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="B35" t="s">
-        <v>1698</v>
+        <v>1708</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="D35" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -16764,33 +16859,33 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1705</v>
+        <v>1715</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1706</v>
+        <v>1716</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1708</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1709</v>
+        <v>1719</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -16799,27 +16894,27 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>222</v>
@@ -16828,33 +16923,33 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1717</v>
+        <v>1727</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1718</v>
+        <v>1728</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1721</v>
+        <v>1731</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1722</v>
+        <v>1732</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1724</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>815</v>
@@ -16863,15 +16958,15 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
       <c r="H38" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
@@ -16880,39 +16975,39 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="H39" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="K39" t="s">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="L39" t="s">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="M39" t="s">
-        <v>1733</v>
+        <v>1743</v>
       </c>
       <c r="N39" t="s">
-        <v>1734</v>
+        <v>1744</v>
       </c>
       <c r="O39" t="s">
-        <v>1735</v>
+        <v>1745</v>
       </c>
       <c r="P39" t="s">
-        <v>1736</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="C40" t="s">
-        <v>1738</v>
+        <v>1748</v>
       </c>
       <c r="D40" t="s">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>222</v>
@@ -16921,39 +17016,39 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="H40" t="s">
-        <v>1741</v>
+        <v>1751</v>
       </c>
       <c r="K40" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="L40" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="M40" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="N40" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="O40" t="s">
-        <v>1746</v>
+        <v>1756</v>
       </c>
       <c r="P40" t="s">
-        <v>1747</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="B41" t="s">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="C41" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="D41" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>222</v>
@@ -16962,18 +17057,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="H41" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="B42" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="C42" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="D42" t="s">
         <v>926</v>
@@ -16985,21 +17080,21 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="H42" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="K42" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="L42" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>815</v>
@@ -17008,39 +17103,39 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="H43" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="K43" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="L43" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="M43" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="N43" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="O43" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="P43" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="C44" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="D44" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -17049,34 +17144,34 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="H44" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="I44" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="J44" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="K44" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="L44" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="M44" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="N44" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="O44" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="P44" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="46" ht="16.8" spans="1:16">
@@ -17254,16 +17349,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="B3" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="D3" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -17272,31 +17367,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -17306,42 +17401,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="B4" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="C4" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="D4" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -17350,37 +17445,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="C5" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="D5" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17389,65 +17484,65 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
       <c r="C7" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="D7" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="E7" t="s">
         <v>222</v>
@@ -17456,28 +17551,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1827</v>
+        <v>1837</v>
       </c>
       <c r="H7" t="s">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="L7" t="s">
-        <v>1829</v>
+        <v>1839</v>
       </c>
       <c r="M7" t="s">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="N7" t="s">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="O7" t="s">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="P7" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
       <c r="Q7" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
     </row>
   </sheetData>
@@ -17503,7 +17598,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" customWidth="1"/>
@@ -17659,30 +17754,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1836</v>
+        <v>1846</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1842</v>
+        <v>1852</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -17692,16 +17787,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1843</v>
+        <v>1853</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -17716,34 +17811,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1848</v>
+        <v>1858</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1851</v>
+        <v>1861</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1854</v>
+        <v>1864</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1856</v>
+        <v>1866</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -17763,7 +17858,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17772,34 +17867,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1858</v>
+        <v>1868</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1863</v>
+        <v>1873</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -17809,16 +17904,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1868</v>
+        <v>1878</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -17827,13 +17922,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="D6" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -17842,30 +17937,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -17877,10 +17972,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -17889,13 +17984,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="D7" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -17904,34 +17999,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -17951,7 +18046,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -17960,75 +18055,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1908</v>
+        <v>1918</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -18036,7 +18131,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -18045,10 +18140,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1911</v>
+        <v>1921</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -18081,7 +18176,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -18090,10 +18185,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -18122,7 +18217,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -18131,37 +18226,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -18174,10 +18269,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -18185,7 +18280,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -18194,20 +18289,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -18229,10 +18324,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="B13" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -18241,20 +18336,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1938</v>
+        <v>1948</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -18276,10 +18371,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="B14" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -18288,20 +18383,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -18323,10 +18418,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -18336,39 +18431,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="K15" t="s">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -18377,34 +18472,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1963</v>
+        <v>1973</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -18415,7 +18510,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -18426,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -18437,10 +18532,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -18452,18 +18547,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -18473,42 +18568,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1976</v>
+        <v>1986</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1978</v>
+        <v>1988</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -18518,39 +18613,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -18560,27 +18655,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -18589,39 +18684,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -18630,10 +18725,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -18646,7 +18741,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -18655,7 +18750,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>1026</v>
@@ -18665,16 +18760,16 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -18693,16 +18788,16 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
@@ -18710,7 +18805,7 @@
         <v>1066</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -18720,34 +18815,34 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>2023</v>
+        <v>2033</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>2025</v>
+        <v>2035</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
@@ -18761,27 +18856,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2032</v>
+        <v>2042</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -18790,27 +18885,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -18819,27 +18914,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -18854,21 +18949,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -18877,22 +18972,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -18902,30 +18997,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -18934,10 +19029,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -18948,30 +19043,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -18980,30 +19075,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="M38" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -19013,18 +19108,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -19034,22 +19129,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -19062,15 +19157,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -19079,54 +19174,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="N42" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="N43" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>2104</v>
+        <v>2114</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -19135,30 +19230,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>2105</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>2095</v>
-      </c>
       <c r="M44" s="2" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="N44" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
       <c r="C45" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -19167,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -19175,10 +19270,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="B46" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -19187,24 +19282,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2114</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="B47" t="s">
-        <v>2116</v>
+        <v>2126</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="D47" t="s">
-        <v>2118</v>
+        <v>2128</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -19213,33 +19308,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="M47" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -19248,10 +19343,10 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2128</v>
+        <v>2138</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
@@ -19259,7 +19354,7 @@
         <v>1136</v>
       </c>
       <c r="B49" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -19268,28 +19363,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -19298,30 +19393,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="B51" t="s">
-        <v>2141</v>
+        <v>2151</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -19330,34 +19425,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="D52" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -19366,24 +19461,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="B53" t="s">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="C53" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="D53" t="s">
-        <v>2153</v>
+        <v>2163</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -19392,18 +19487,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2155</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="B54" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -19412,36 +19507,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="B55" t="s">
-        <v>2160</v>
+        <v>2170</v>
       </c>
       <c r="C55" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
       <c r="D55" t="s">
-        <v>2162</v>
+        <v>2172</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -19450,19 +19545,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2164</v>
+        <v>2174</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="B56" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -19471,36 +19566,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2166</v>
+        <v>2176</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>2172</v>
+        <v>2182</v>
       </c>
       <c r="B57" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="D57" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -19509,36 +19604,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2176</v>
+        <v>2186</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2178</v>
+        <v>2188</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>2180</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="B58" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="D58" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -19547,36 +19642,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2184</v>
+        <v>2194</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>2188</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -19585,10 +19680,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -19597,16 +19692,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="B60" t="s">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="D60" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -19615,10 +19710,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -19627,16 +19722,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="B61" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -19645,27 +19740,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2203</v>
+        <v>2213</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2206</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -19674,10 +19769,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2208</v>
+        <v>2218</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -19689,24 +19784,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="B64" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="D64" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -19715,10 +19810,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -19729,15 +19824,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -19746,15 +19841,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -19763,15 +19858,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -19780,15 +19875,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -19797,15 +19892,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -19814,27 +19909,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -19843,27 +19938,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -19872,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -19880,7 +19975,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -19889,33 +19984,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="N73" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="O73" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="C74" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="D74" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -19924,33 +20019,33 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="N74" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
       <c r="O74" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="D75" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
       <c r="E75" t="s">
         <v>222</v>
@@ -19962,29 +20057,29 @@
         <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -19993,27 +20088,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -20022,15 +20117,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -20039,27 +20134,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2276</v>
+        <v>2286</v>
       </c>
       <c r="N79" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="O79" t="s">
-        <v>2278</v>
+        <v>2288</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2280</v>
+        <v>2290</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -20068,33 +20163,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="N80" t="s">
-        <v>2284</v>
+        <v>2294</v>
       </c>
       <c r="O80" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
       <c r="P80" t="s">
-        <v>2286</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="D81" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -20103,33 +20198,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="B82" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="D82" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -20138,30 +20233,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="A83" s="2" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="B83" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -20170,33 +20265,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="C84" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="D84" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -20205,33 +20300,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -20240,27 +20335,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -20269,27 +20364,30 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2329</v>
+        <v>2339</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
+      <c r="A87" t="s">
+        <v>2344</v>
+      </c>
       <c r="B87" t="s">
-        <v>2334</v>
+        <v>2345</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -20298,68 +20396,105 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>2335</v>
+        <v>2346</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2336</v>
+        <v>2347</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>2337</v>
+        <v>2348</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="88" ht="18" spans="1:16">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" t="s">
+        <v>2346</v>
+      </c>
       <c r="B88" t="s">
-        <v>2339</v>
+        <v>2350</v>
       </c>
       <c r="E88" t="s">
         <v>222</v>
       </c>
       <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>2340</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>2341</v>
+        <v>2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>2351</v>
+      </c>
+      <c r="H88" t="s">
+        <v>2352</v>
       </c>
       <c r="M88" t="s">
-        <v>2342</v>
+        <v>2353</v>
       </c>
       <c r="N88" t="s">
-        <v>2343</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16">
-      <c r="B89" t="s">
-        <v>2344</v>
-      </c>
-      <c r="E89" t="s">
+        <v>2354</v>
+      </c>
+      <c r="O88" t="s">
+        <v>2355</v>
+      </c>
+      <c r="P88" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="1:16">
+      <c r="G89" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="90" ht="18" spans="1:16">
+      <c r="B90" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E90" t="s">
         <v>222</v>
       </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89" t="s">
-        <v>2345</v>
-      </c>
-      <c r="H89" t="s">
-        <v>2346</v>
-      </c>
-      <c r="M89" t="s">
-        <v>2347</v>
-      </c>
-      <c r="N89" t="s">
-        <v>2348</v>
-      </c>
-      <c r="O89" t="s">
-        <v>2349</v>
-      </c>
-      <c r="P89" t="s">
-        <v>2350</v>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>2359</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>2360</v>
+      </c>
+      <c r="M90" t="s">
+        <v>2361</v>
+      </c>
+      <c r="N90" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="B91" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E91" t="s">
+        <v>222</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>2364</v>
+      </c>
+      <c r="H91" t="s">
+        <v>2365</v>
+      </c>
+      <c r="M91" t="s">
+        <v>2366</v>
+      </c>
+      <c r="N91" t="s">
+        <v>2367</v>
+      </c>
+      <c r="O91" t="s">
+        <v>2368</v>
+      </c>
+      <c r="P91" t="s">
+        <v>2369</v>
       </c>
     </row>
   </sheetData>
@@ -20550,16 +20685,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="B3" t="s">
-        <v>2351</v>
+        <v>2370</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2352</v>
+        <v>2371</v>
       </c>
       <c r="D3" t="s">
-        <v>2353</v>
+        <v>2372</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -20568,42 +20703,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2354</v>
+        <v>2373</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2355</v>
+        <v>2374</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2356</v>
+        <v>2375</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2357</v>
+        <v>2376</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2358</v>
+        <v>2377</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2359</v>
+        <v>2378</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2360</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2361</v>
+        <v>2380</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2362</v>
+        <v>2381</v>
       </c>
       <c r="D4" t="s">
-        <v>2363</v>
+        <v>2382</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -20612,21 +20747,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2364</v>
+        <v>2383</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2365</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2366</v>
+        <v>2385</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2367</v>
+        <v>2386</v>
       </c>
       <c r="D5" t="s">
-        <v>2368</v>
+        <v>2387</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -20635,33 +20770,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2369</v>
+        <v>2388</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2370</v>
+        <v>2389</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2371</v>
+        <v>2390</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2372</v>
+        <v>2391</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2373</v>
+        <v>2392</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2374</v>
+        <v>2393</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2375</v>
+        <v>2394</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2376</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2377</v>
+        <v>2396</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -20670,33 +20805,33 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2378</v>
+        <v>2397</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2379</v>
+        <v>2398</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2380</v>
+        <v>2399</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2381</v>
+        <v>2400</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2382</v>
+        <v>2401</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2383</v>
+        <v>2402</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2384</v>
+        <v>2403</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2385</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2386</v>
+        <v>2405</v>
       </c>
       <c r="E7" t="s">
         <v>815</v>
@@ -20705,21 +20840,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2387</v>
+        <v>2406</v>
       </c>
       <c r="H7" t="s">
-        <v>2388</v>
+        <v>2407</v>
       </c>
       <c r="L7" t="s">
-        <v>2389</v>
+        <v>2408</v>
       </c>
       <c r="M7" t="s">
-        <v>2390</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2386</v>
+        <v>2405</v>
       </c>
       <c r="E8" t="s">
         <v>815</v>
@@ -20728,27 +20863,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2391</v>
+        <v>2410</v>
       </c>
       <c r="H8" t="s">
-        <v>2388</v>
+        <v>2407</v>
       </c>
       <c r="L8" t="s">
-        <v>2392</v>
+        <v>2411</v>
       </c>
       <c r="M8" t="s">
-        <v>2390</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:32">
       <c r="B9" t="s">
-        <v>2393</v>
+        <v>2412</v>
       </c>
       <c r="C9" t="s">
-        <v>2394</v>
+        <v>2413</v>
       </c>
       <c r="D9" t="s">
-        <v>2395</v>
+        <v>2414</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -20757,39 +20892,39 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>2396</v>
+        <v>2415</v>
       </c>
       <c r="H9" t="s">
-        <v>2397</v>
+        <v>2416</v>
       </c>
       <c r="L9" t="s">
-        <v>2398</v>
+        <v>2417</v>
       </c>
       <c r="M9" t="s">
-        <v>2399</v>
+        <v>2418</v>
       </c>
       <c r="N9" t="s">
-        <v>2400</v>
+        <v>2419</v>
       </c>
       <c r="O9" t="s">
-        <v>2401</v>
+        <v>2420</v>
       </c>
       <c r="P9" t="s">
-        <v>2402</v>
+        <v>2421</v>
       </c>
       <c r="Q9" t="s">
-        <v>2403</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:32">
       <c r="B10" t="s">
-        <v>2404</v>
+        <v>2423</v>
       </c>
       <c r="C10" t="s">
-        <v>2405</v>
+        <v>2424</v>
       </c>
       <c r="D10" t="s">
-        <v>2406</v>
+        <v>2425</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>49</v>
@@ -20798,28 +20933,28 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>2407</v>
+        <v>2426</v>
       </c>
       <c r="H10" t="s">
-        <v>2408</v>
+        <v>2427</v>
       </c>
       <c r="L10" t="s">
-        <v>2409</v>
+        <v>2428</v>
       </c>
       <c r="M10" t="s">
-        <v>2410</v>
+        <v>2429</v>
       </c>
       <c r="N10" t="s">
-        <v>2411</v>
+        <v>2430</v>
       </c>
       <c r="O10" t="s">
-        <v>2412</v>
+        <v>2431</v>
       </c>
       <c r="P10" t="s">
-        <v>2413</v>
+        <v>2432</v>
       </c>
       <c r="Q10" t="s">
-        <v>2414</v>
+        <v>2433</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="2434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="2462">
   <si>
     <r>
       <rPr>
@@ -3200,6 +3200,36 @@
     <t>のりこえた</t>
   </si>
   <si>
+    <t>后悔</t>
+  </si>
+  <si>
+    <t>前非を悔いる</t>
+  </si>
+  <si>
+    <t>痛改前非</t>
+  </si>
+  <si>
+    <t>悔いる</t>
+  </si>
+  <si>
+    <t>くいる</t>
+  </si>
+  <si>
+    <t>违反</t>
+  </si>
+  <si>
+    <t>規則と法律に反する行為</t>
+  </si>
+  <si>
+    <t>违反规则和法律的行为</t>
+  </si>
+  <si>
+    <t>反する</t>
+  </si>
+  <si>
+    <t>はんする</t>
+  </si>
+  <si>
     <t>着く</t>
   </si>
   <si>
@@ -7520,6 +7550,33 @@
     <t>ひっぱった</t>
   </si>
   <si>
+    <t>挪用</t>
+  </si>
+  <si>
+    <t>会議の終わりに、彼が急に予算の話を持ち出した</t>
+  </si>
+  <si>
+    <t>会议快结束时，他突然提出了预算的事情</t>
+  </si>
+  <si>
+    <t>持ち出す</t>
+  </si>
+  <si>
+    <t>もちだす</t>
+  </si>
+  <si>
+    <t>持ち出して</t>
+  </si>
+  <si>
+    <t>もちだして</t>
+  </si>
+  <si>
+    <t>持ち出した</t>
+  </si>
+  <si>
+    <t>もちだした</t>
+  </si>
+  <si>
     <t>支撑</t>
   </si>
   <si>
@@ -7710,6 +7767,33 @@
   </si>
   <si>
     <t>およぼした</t>
+  </si>
+  <si>
+    <t>夹住，穿插</t>
+  </si>
+  <si>
+    <t>挟む</t>
+  </si>
+  <si>
+    <t>はさむ</t>
+  </si>
+  <si>
+    <t>挟まない</t>
+  </si>
+  <si>
+    <t>はさまない</t>
+  </si>
+  <si>
+    <t>挟んで</t>
+  </si>
+  <si>
+    <t>はさんで</t>
+  </si>
+  <si>
+    <t>挟んだ</t>
+  </si>
+  <si>
+    <t>はさんだ</t>
   </si>
 </sst>
 </file>
@@ -7988,17 +8072,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -10412,7 +10496,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE97"/>
+  <dimension ref="A1:AE99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="29.8888888888889" customWidth="1"/>
@@ -13211,6 +13295,52 @@
       </c>
       <c r="P97" t="s">
         <v>960</v>
+      </c>
+    </row>
+    <row r="98" ht="18" spans="2:16">
+      <c r="B98" t="s">
+        <v>961</v>
+      </c>
+      <c r="C98" t="s">
+        <v>962</v>
+      </c>
+      <c r="D98" t="s">
+        <v>963</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>964</v>
+      </c>
+      <c r="H98" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16">
+      <c r="B99" t="s">
+        <v>966</v>
+      </c>
+      <c r="C99" t="s">
+        <v>967</v>
+      </c>
+      <c r="D99" t="s">
+        <v>968</v>
+      </c>
+      <c r="E99" t="s">
+        <v>49</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>969</v>
+      </c>
+      <c r="H99" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -13392,28 +13522,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="H3" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
     </row>
     <row r="4" ht="31.2" customHeight="1" spans="2:31">
@@ -13424,7 +13554,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="2" t="s">
@@ -13442,73 +13572,73 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="F5" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="H5" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="I5" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6" ht="18" spans="2:31">
       <c r="C6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="H6" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>550</v>
@@ -13517,16 +13647,16 @@
         <v>551</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7" ht="18" spans="2:31">
@@ -13537,7 +13667,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>728</v>
@@ -13546,16 +13676,16 @@
         <v>729</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>730</v>
@@ -13584,16 +13714,16 @@
         <v>729</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>735</v>
@@ -13616,37 +13746,37 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1003</v>
+        <v>1013</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:31">
@@ -13657,38 +13787,38 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="O10" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="P10" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11" ht="18" spans="2:31">
@@ -13699,16 +13829,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -13719,7 +13849,7 @@
     </row>
     <row r="12" ht="18" spans="2:31">
       <c r="B12" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>49</v>
@@ -13730,25 +13860,25 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" spans="2:31">
       <c r="B13" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>49</v>
@@ -13757,39 +13887,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1042</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="18" spans="2:31">
       <c r="B14" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>222</v>
@@ -13798,21 +13928,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="F14" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="G14" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="H14" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" ht="18" spans="2:31">
       <c r="B15" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>49</v>
@@ -13821,18 +13951,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1049</v>
+        <v>1059</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -13841,7 +13971,7 @@
     </row>
     <row r="16" ht="18" spans="2:31">
       <c r="B16" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>49</v>
@@ -13850,10 +13980,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1054</v>
+        <v>1064</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>374</v>
@@ -13864,7 +13994,7 @@
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="B17" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>49</v>
@@ -13873,19 +14003,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="B18" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>49</v>
@@ -13896,15 +14026,15 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>49</v>
@@ -13915,15 +14045,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>49</v>
@@ -13932,10 +14062,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>347</v>
@@ -13952,21 +14082,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="B22" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -13975,24 +14105,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="B23" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -14003,30 +14133,30 @@
       <c r="E23" s="2"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="M23" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="N23" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="B24" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>49</v>
@@ -14037,30 +14167,30 @@
       <c r="E24" s="2"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="B25" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>49</v>
@@ -14069,28 +14199,28 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>49</v>
@@ -14099,27 +14229,27 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="M26" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="N26" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -14128,21 +14258,21 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>49</v>
@@ -14151,33 +14281,33 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>49</v>
@@ -14186,39 +14316,39 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="F29" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>222</v>
@@ -14227,21 +14357,21 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="F30" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="B31" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>49</v>
@@ -14250,15 +14380,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>49</v>
@@ -14267,33 +14397,33 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -14302,39 +14432,39 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
       <c r="F33" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>49</v>
@@ -14343,33 +14473,33 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>49</v>
@@ -14378,33 +14508,33 @@
         <v>1</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>49</v>
@@ -14413,39 +14543,39 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="F36" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1182</v>
+        <v>1192</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1184</v>
+        <v>1194</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
@@ -14454,33 +14584,33 @@
         <v>1</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1192</v>
+        <v>1202</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1193</v>
+        <v>1203</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1194</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>815</v>
@@ -14489,16 +14619,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="F38" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="G38" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -14509,10 +14639,10 @@
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="A39" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="B39" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>49</v>
@@ -14524,30 +14654,30 @@
         <v>701</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>49</v>
@@ -14556,10 +14686,10 @@
         <v>2</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -14570,10 +14700,10 @@
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="B41" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>49</v>
@@ -14582,18 +14712,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="B42" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -14602,10 +14732,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
@@ -14616,10 +14746,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
@@ -14630,33 +14760,33 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="F44" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="I44" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="K44" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="B45" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>49</v>
@@ -14665,34 +14795,34 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
       <c r="F45" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -14701,33 +14831,33 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="B47" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>49</v>
@@ -14736,15 +14866,15 @@
         <v>2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>49</v>
@@ -14753,30 +14883,30 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
       <c r="N48" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
       <c r="B49" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>815</v>
@@ -14785,33 +14915,33 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="B50" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>49</v>
@@ -14820,36 +14950,36 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="K50" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="B51" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>222</v>
@@ -14858,21 +14988,21 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="F51" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="B52" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -14881,21 +15011,21 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="F52" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="53" ht="27.6" spans="1:16">
       <c r="B53" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>222</v>
@@ -14904,21 +15034,21 @@
         <v>1</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="B54" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>49</v>
@@ -14927,33 +15057,33 @@
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="M54" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="B55" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>815</v>
@@ -14962,33 +15092,33 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
       <c r="F55" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="M55" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="B56" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>49</v>
@@ -14997,10 +15127,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
@@ -15011,30 +15141,30 @@
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
       <c r="F57" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="O57" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="B58" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>
@@ -15043,39 +15173,39 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="B59" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>49</v>
@@ -15084,39 +15214,39 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="H59" s="2" t="s">
-        <v>1315</v>
-      </c>
       <c r="I59" s="2" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="B60" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>815</v>
@@ -15125,39 +15255,39 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="B61" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>49</v>
@@ -15166,39 +15296,39 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>49</v>
@@ -15207,21 +15337,21 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="F62" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="G62" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="H62" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
       <c r="B63" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>815</v>
@@ -15230,33 +15360,33 @@
         <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="H63" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="K63" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
       <c r="L63" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="M63" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="N63" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="O63" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="P63" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="B64" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>49</v>
@@ -15265,15 +15395,15 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="H64" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:16">
       <c r="B65" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>49</v>
@@ -15282,33 +15412,33 @@
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="H65" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="K65" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="L65" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="M65" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
       <c r="N65" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="O65" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="P65" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="66" ht="18" spans="1:16">
       <c r="B66" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>49</v>
@@ -15317,36 +15447,36 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="H66" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="K66" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="L66" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="M66" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="N66" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="O66" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="P66" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="67" ht="27.6" spans="1:16">
       <c r="A67" s="17" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="B67" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>49</v>
@@ -15355,33 +15485,33 @@
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="H67" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="K67" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="L67" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="M67" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="N67" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="O67" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="P67" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="B68" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="C68" t="s">
         <v>222</v>
@@ -15390,36 +15520,36 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="H68" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="K68" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="L68" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="M68" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="N68" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="O68" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="P68" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="69" ht="18" spans="1:16">
       <c r="A69" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="B69" t="s">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>49</v>
@@ -15428,36 +15558,36 @@
         <v>2</v>
       </c>
       <c r="G69" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="H69" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="K69" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="L69" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="M69" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="N69" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
       <c r="O69" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="P69" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="B70" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="C70" t="s">
         <v>222</v>
@@ -15466,33 +15596,33 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="H70" t="s">
-        <v>1417</v>
+        <v>1427</v>
       </c>
       <c r="K70" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="L70" t="s">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="M70" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="N70" t="s">
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="O70" t="s">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="P70" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="71" ht="18" spans="1:16">
       <c r="B71" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>49</v>
@@ -15501,27 +15631,27 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="H71" t="s">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="K71" t="s">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="L71" t="s">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="M71" t="s">
-        <v>1429</v>
+        <v>1439</v>
       </c>
       <c r="N71" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="72" customFormat="1" ht="18" spans="1:16">
       <c r="B72" s="2" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>49</v>
@@ -15530,33 +15660,33 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="F72" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="G72" t="s">
-        <v>1434</v>
+        <v>1444</v>
       </c>
       <c r="H72" t="s">
-        <v>1435</v>
+        <v>1445</v>
       </c>
       <c r="M72" t="s">
-        <v>1436</v>
+        <v>1446</v>
       </c>
       <c r="N72" t="s">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="O72" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
       <c r="P72" t="s">
-        <v>1439</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="73" ht="18" spans="1:16">
       <c r="B73" t="s">
-        <v>1440</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>49</v>
@@ -15565,33 +15695,33 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>1441</v>
+        <v>1451</v>
       </c>
       <c r="H73" t="s">
-        <v>1442</v>
+        <v>1452</v>
       </c>
       <c r="K73" t="s">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="L73" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="M73" t="s">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="N73" t="s">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="O73" t="s">
-        <v>1447</v>
+        <v>1457</v>
       </c>
       <c r="P73" t="s">
-        <v>1448</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="B74" t="s">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="C74" t="s">
         <v>222</v>
@@ -15600,33 +15730,33 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="F74" t="s">
-        <v>1451</v>
+        <v>1461</v>
       </c>
       <c r="G74" t="s">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="H74" t="s">
-        <v>1453</v>
+        <v>1463</v>
       </c>
       <c r="M74" t="s">
-        <v>1454</v>
+        <v>1464</v>
       </c>
       <c r="N74" t="s">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="O74" t="s">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="P74" t="s">
-        <v>1457</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="75" ht="18" spans="1:16">
       <c r="B75" t="s">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>815</v>
@@ -15635,34 +15765,34 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>1459</v>
+        <v>1469</v>
       </c>
       <c r="F75" t="s">
-        <v>1460</v>
+        <v>1470</v>
       </c>
       <c r="G75" t="s">
-        <v>1461</v>
+        <v>1471</v>
       </c>
       <c r="H75" t="s">
-        <v>1462</v>
+        <v>1472</v>
       </c>
       <c r="K75" t="s">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="L75" t="s">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="M75" t="s">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="N75" t="s">
-        <v>1466</v>
+        <v>1476</v>
       </c>
       <c r="O75" t="s">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="P75" t="s">
-        <v>1468</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="76" ht="18" spans="1:16">
@@ -15673,34 +15803,34 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>1469</v>
+        <v>1479</v>
       </c>
       <c r="F76" t="s">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="G76" t="s">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="H76" t="s">
-        <v>1472</v>
+        <v>1482</v>
       </c>
       <c r="K76" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="L76" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
       <c r="M76" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="N76" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="O76" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
       <c r="P76" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>
@@ -15873,28 +16003,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="N3" t="s">
-        <v>1484</v>
+        <v>1494</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1485</v>
+        <v>1495</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -15905,28 +16035,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="I4" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="M4" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -15937,60 +16067,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -15998,21 +16128,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -16021,15 +16151,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -16046,7 +16176,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -16055,36 +16185,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="M10" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="N10" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="B11" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -16093,42 +16223,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="M11" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="B12" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="D12" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -16137,33 +16267,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -16172,39 +16302,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="B14" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16213,22 +16343,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -16240,33 +16370,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="N15" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16275,18 +16405,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="B17" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -16295,30 +16425,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="B18" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -16327,27 +16457,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -16356,27 +16486,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -16385,30 +16515,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1597</v>
+        <v>1607</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1598</v>
+        <v>1608</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1599</v>
+        <v>1609</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1601</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="B21" t="s">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -16417,40 +16547,40 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="K21" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="M21" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="D22" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="E22" t="s">
         <v>222</v>
@@ -16459,34 +16589,34 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1616</v>
+        <v>1626</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1617</v>
+        <v>1627</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1619</v>
+        <v>1629</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" t="s">
@@ -16496,33 +16626,33 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="B24" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="E24" t="s">
         <v>222</v>
@@ -16531,27 +16661,27 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -16560,33 +16690,33 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1642</v>
+        <v>1652</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1643</v>
+        <v>1653</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -16595,27 +16725,27 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
       <c r="E27" t="s">
         <v>222</v>
@@ -16624,36 +16754,36 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
       <c r="I27" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="C28" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
       <c r="D28" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -16662,27 +16792,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -16691,27 +16821,27 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1671</v>
+        <v>1681</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1673</v>
+        <v>1683</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1675</v>
+        <v>1685</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1676</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1677</v>
+        <v>1687</v>
       </c>
       <c r="E30" t="s">
         <v>222</v>
@@ -16720,10 +16850,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1678</v>
+        <v>1688</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1679</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
@@ -16734,33 +16864,33 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1681</v>
+        <v>1691</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1682</v>
+        <v>1692</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1683</v>
+        <v>1693</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1684</v>
+        <v>1694</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1685</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1686</v>
+        <v>1696</v>
       </c>
       <c r="C32" t="s">
-        <v>1687</v>
+        <v>1697</v>
       </c>
       <c r="D32" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -16769,21 +16899,21 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1690</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="C33" t="s">
-        <v>1692</v>
+        <v>1702</v>
       </c>
       <c r="D33" t="s">
-        <v>1693</v>
+        <v>1703</v>
       </c>
       <c r="E33" t="s">
         <v>222</v>
@@ -16792,33 +16922,33 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1694</v>
+        <v>1704</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1695</v>
+        <v>1705</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1698</v>
+        <v>1708</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
       <c r="C34" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="D34" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>815</v>
@@ -16827,30 +16957,30 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1705</v>
+        <v>1715</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1706</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="B35" t="s">
-        <v>1708</v>
+        <v>1718</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1709</v>
+        <v>1719</v>
       </c>
       <c r="D35" t="s">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -16859,33 +16989,33 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1717</v>
+        <v>1727</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1718</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -16894,27 +17024,27 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1721</v>
+        <v>1731</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1722</v>
+        <v>1732</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1724</v>
+        <v>1734</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>222</v>
@@ -16923,33 +17053,33 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1733</v>
+        <v>1743</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1734</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1735</v>
+        <v>1745</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>815</v>
@@ -16958,15 +17088,15 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="H38" t="s">
-        <v>1737</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1738</v>
+        <v>1748</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
@@ -16975,39 +17105,39 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="H39" t="s">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="K39" t="s">
-        <v>1741</v>
+        <v>1751</v>
       </c>
       <c r="L39" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="M39" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="N39" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="O39" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="P39" t="s">
-        <v>1746</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1747</v>
+        <v>1757</v>
       </c>
       <c r="C40" t="s">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="D40" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>222</v>
@@ -17016,39 +17146,39 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="H40" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="K40" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="L40" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="M40" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="N40" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="O40" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
       <c r="P40" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="B41" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="C41" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="D41" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>222</v>
@@ -17057,18 +17187,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="H41" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="B42" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="C42" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="D42" t="s">
         <v>926</v>
@@ -17080,21 +17210,21 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
       <c r="H42" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="K42" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="L42" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>815</v>
@@ -17103,39 +17233,39 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="H43" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="K43" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="L43" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="M43" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="N43" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="O43" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="P43" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="C44" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="D44" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -17144,34 +17274,34 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="H44" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="I44" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="J44" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="K44" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="L44" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="M44" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="N44" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="O44" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="P44" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="46" ht="16.8" spans="1:16">
@@ -17349,16 +17479,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="B3" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="D3" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -17367,31 +17497,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -17401,42 +17531,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="B4" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="C4" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="D4" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -17445,37 +17575,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="C5" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="D5" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17484,65 +17614,65 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1827</v>
+        <v>1837</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1829</v>
+        <v>1839</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
       <c r="C7" t="s">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="D7" t="s">
-        <v>1836</v>
+        <v>1846</v>
       </c>
       <c r="E7" t="s">
         <v>222</v>
@@ -17551,28 +17681,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="H7" t="s">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="L7" t="s">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="M7" t="s">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="N7" t="s">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="O7" t="s">
-        <v>1842</v>
+        <v>1852</v>
       </c>
       <c r="P7" t="s">
-        <v>1843</v>
+        <v>1853</v>
       </c>
       <c r="Q7" t="s">
-        <v>1844</v>
+        <v>1854</v>
       </c>
     </row>
   </sheetData>
@@ -17598,7 +17728,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE91"/>
+  <dimension ref="A1:AE92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" customWidth="1"/>
@@ -17754,30 +17884,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1848</v>
+        <v>1858</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1851</v>
+        <v>1861</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -17787,16 +17917,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1854</v>
+        <v>1864</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1856</v>
+        <v>1866</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -17811,34 +17941,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1858</v>
+        <v>1868</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1863</v>
+        <v>1873</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -17858,7 +17988,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17867,34 +17997,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1868</v>
+        <v>1878</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -17904,16 +18034,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -17922,13 +18052,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="D6" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -17937,30 +18067,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -17972,10 +18102,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -17984,13 +18114,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="D7" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -17999,34 +18129,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -18046,7 +18176,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -18055,75 +18185,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1908</v>
+        <v>1918</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1911</v>
+        <v>1921</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -18131,7 +18261,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -18140,10 +18270,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -18176,7 +18306,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -18185,10 +18315,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -18217,7 +18347,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -18226,37 +18356,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -18269,10 +18399,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1938</v>
+        <v>1948</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -18280,7 +18410,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -18289,20 +18419,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -18324,10 +18454,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="B13" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -18336,20 +18466,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -18371,10 +18501,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="B14" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -18383,20 +18513,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -18418,10 +18548,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -18431,39 +18561,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="K15" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1963</v>
+        <v>1973</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -18472,34 +18602,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1976</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -18510,7 +18640,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -18521,7 +18651,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1978</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -18532,10 +18662,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -18547,18 +18677,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -18568,42 +18698,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -18613,39 +18743,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -18655,27 +18785,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -18684,39 +18814,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -18725,10 +18855,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -18741,7 +18871,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -18750,26 +18880,26 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>2023</v>
+        <v>2033</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2025</v>
+        <v>2035</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -18780,32 +18910,32 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
       <c r="B28" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -18815,39 +18945,39 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2032</v>
+        <v>2042</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
       <c r="B29" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>222</v>
@@ -18856,27 +18986,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -18885,27 +19015,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -18914,27 +19044,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -18949,21 +19079,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -18972,22 +19102,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>2071</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -18997,30 +19127,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -19029,10 +19159,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2080</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -19043,30 +19173,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -19075,30 +19205,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="M38" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -19108,18 +19238,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -19129,22 +19259,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -19157,15 +19287,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -19174,54 +19304,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>2104</v>
+        <v>2114</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="N42" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
       <c r="N43" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>2114</v>
+        <v>2124</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -19230,30 +19360,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>2115</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>2105</v>
-      </c>
       <c r="M44" s="2" t="s">
-        <v>2116</v>
+        <v>2126</v>
       </c>
       <c r="N44" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>2118</v>
+        <v>2128</v>
       </c>
       <c r="C45" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -19262,7 +19392,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -19270,10 +19400,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="B46" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -19282,24 +19412,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="B47" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="D47" t="s">
-        <v>2128</v>
+        <v>2138</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -19308,33 +19438,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="M47" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -19343,18 +19473,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="B49" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -19363,28 +19493,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2141</v>
+        <v>2151</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -19393,30 +19523,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="B51" t="s">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -19425,34 +19555,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>2153</v>
+        <v>2163</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>2155</v>
+        <v>2165</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="D52" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -19461,24 +19591,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>2160</v>
+        <v>2170</v>
       </c>
       <c r="B53" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
       <c r="C53" t="s">
-        <v>2162</v>
+        <v>2172</v>
       </c>
       <c r="D53" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -19487,18 +19617,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2164</v>
+        <v>2174</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>2166</v>
+        <v>2176</v>
       </c>
       <c r="B54" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -19507,36 +19637,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="B55" t="s">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="C55" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
       <c r="D55" t="s">
-        <v>2172</v>
+        <v>2182</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -19545,19 +19675,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="B56" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -19566,36 +19696,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2176</v>
+        <v>2186</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>2178</v>
+        <v>2188</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>2180</v>
+        <v>2190</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="B57" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>2184</v>
+        <v>2194</v>
       </c>
       <c r="D57" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -19604,36 +19734,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2188</v>
+        <v>2198</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>2190</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="B58" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="D58" t="s">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -19642,36 +19772,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -19680,10 +19810,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -19692,16 +19822,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="B60" t="s">
-        <v>2203</v>
+        <v>2213</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
       <c r="D60" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -19710,10 +19840,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2206</v>
+        <v>2216</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -19722,16 +19852,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="B61" t="s">
-        <v>2208</v>
+        <v>2218</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -19740,27 +19870,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -19769,10 +19899,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -19784,24 +19914,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="B64" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
       <c r="D64" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -19810,10 +19940,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -19824,15 +19954,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -19841,15 +19971,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -19858,15 +19988,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -19875,15 +20005,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -19892,15 +20022,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -19909,27 +20039,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -19938,27 +20068,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -19967,7 +20097,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -19975,7 +20105,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -19984,33 +20114,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
       <c r="N73" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="O73" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="C74" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
       <c r="D74" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -20019,33 +20149,33 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="N74" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="O74" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="D75" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="E75" t="s">
         <v>222</v>
@@ -20057,29 +20187,29 @@
         <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -20088,27 +20218,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>2276</v>
+        <v>2286</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>2278</v>
+        <v>2288</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2280</v>
+        <v>2290</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -20117,15 +20247,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -20134,27 +20264,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2284</v>
+        <v>2294</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2286</v>
+        <v>2296</v>
       </c>
       <c r="N79" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="O79" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -20163,33 +20293,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="N80" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="O80" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="P80" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="D81" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -20198,33 +20328,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="B82" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="D82" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -20233,30 +20363,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="A83" s="2" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="B83" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -20265,33 +20395,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="C84" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="D84" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -20300,33 +20430,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2329</v>
+        <v>2339</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -20335,27 +20465,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2336</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -20364,30 +20494,30 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2338</v>
+        <v>2348</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>2340</v>
+        <v>2350</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>2342</v>
+        <v>2352</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="A87" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="B87" t="s">
-        <v>2345</v>
+        <v>2355</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -20396,24 +20526,24 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2347</v>
+        <v>2357</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>2349</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="B88" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
       <c r="E88" t="s">
         <v>222</v>
@@ -20422,32 +20552,32 @@
         <v>2</v>
       </c>
       <c r="G88" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="H88" t="s">
-        <v>2352</v>
+        <v>2362</v>
       </c>
       <c r="M88" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
       <c r="N88" t="s">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="O88" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="P88" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="1:16">
       <c r="G89" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="90" ht="18" spans="1:16">
       <c r="B90" t="s">
-        <v>2358</v>
+        <v>2368</v>
       </c>
       <c r="E90" t="s">
         <v>222</v>
@@ -20456,21 +20586,21 @@
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="M90" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="N90" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="B91" t="s">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="E91" t="s">
         <v>222</v>
@@ -20479,22 +20609,57 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>2364</v>
+        <v>2374</v>
       </c>
       <c r="H91" t="s">
-        <v>2365</v>
+        <v>2375</v>
       </c>
       <c r="M91" t="s">
-        <v>2366</v>
+        <v>2376</v>
       </c>
       <c r="N91" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="O91" t="s">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="P91" t="s">
-        <v>2369</v>
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="B92" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D92" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E92" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>2383</v>
+      </c>
+      <c r="H92" t="s">
+        <v>2384</v>
+      </c>
+      <c r="M92" t="s">
+        <v>2385</v>
+      </c>
+      <c r="N92" t="s">
+        <v>2386</v>
+      </c>
+      <c r="O92" t="s">
+        <v>2387</v>
+      </c>
+      <c r="P92" t="s">
+        <v>2388</v>
       </c>
     </row>
   </sheetData>
@@ -20520,7 +20685,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
@@ -20685,16 +20850,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="B3" t="s">
-        <v>2370</v>
+        <v>2389</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2371</v>
+        <v>2390</v>
       </c>
       <c r="D3" t="s">
-        <v>2372</v>
+        <v>2391</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -20703,42 +20868,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2373</v>
+        <v>2392</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2374</v>
+        <v>2393</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2375</v>
+        <v>2394</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2376</v>
+        <v>2395</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2377</v>
+        <v>2396</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2378</v>
+        <v>2397</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2379</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2380</v>
+        <v>2399</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2381</v>
+        <v>2400</v>
       </c>
       <c r="D4" t="s">
-        <v>2382</v>
+        <v>2401</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -20747,21 +20912,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2383</v>
+        <v>2402</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2384</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2385</v>
+        <v>2404</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2386</v>
+        <v>2405</v>
       </c>
       <c r="D5" t="s">
-        <v>2387</v>
+        <v>2406</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -20770,33 +20935,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2388</v>
+        <v>2407</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2389</v>
+        <v>2408</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2390</v>
+        <v>2409</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2391</v>
+        <v>2410</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2392</v>
+        <v>2411</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2393</v>
+        <v>2412</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2394</v>
+        <v>2413</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2395</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2396</v>
+        <v>2415</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -20805,33 +20970,33 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2397</v>
+        <v>2416</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2398</v>
+        <v>2417</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2399</v>
+        <v>2418</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2400</v>
+        <v>2419</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2401</v>
+        <v>2420</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2402</v>
+        <v>2421</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2403</v>
+        <v>2422</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2404</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2405</v>
+        <v>2424</v>
       </c>
       <c r="E7" t="s">
         <v>815</v>
@@ -20840,21 +21005,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2406</v>
+        <v>2425</v>
       </c>
       <c r="H7" t="s">
-        <v>2407</v>
+        <v>2426</v>
       </c>
       <c r="L7" t="s">
-        <v>2408</v>
+        <v>2427</v>
       </c>
       <c r="M7" t="s">
-        <v>2409</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2405</v>
+        <v>2424</v>
       </c>
       <c r="E8" t="s">
         <v>815</v>
@@ -20863,27 +21028,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2410</v>
+        <v>2429</v>
       </c>
       <c r="H8" t="s">
-        <v>2407</v>
+        <v>2426</v>
       </c>
       <c r="L8" t="s">
-        <v>2411</v>
+        <v>2430</v>
       </c>
       <c r="M8" t="s">
-        <v>2409</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:32">
       <c r="B9" t="s">
-        <v>2412</v>
+        <v>2431</v>
       </c>
       <c r="C9" t="s">
-        <v>2413</v>
+        <v>2432</v>
       </c>
       <c r="D9" t="s">
-        <v>2414</v>
+        <v>2433</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -20892,39 +21057,39 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>2415</v>
+        <v>2434</v>
       </c>
       <c r="H9" t="s">
-        <v>2416</v>
+        <v>2435</v>
       </c>
       <c r="L9" t="s">
-        <v>2417</v>
+        <v>2436</v>
       </c>
       <c r="M9" t="s">
-        <v>2418</v>
+        <v>2437</v>
       </c>
       <c r="N9" t="s">
-        <v>2419</v>
+        <v>2438</v>
       </c>
       <c r="O9" t="s">
-        <v>2420</v>
+        <v>2439</v>
       </c>
       <c r="P9" t="s">
-        <v>2421</v>
+        <v>2440</v>
       </c>
       <c r="Q9" t="s">
-        <v>2422</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:32">
       <c r="B10" t="s">
-        <v>2423</v>
+        <v>2442</v>
       </c>
       <c r="C10" t="s">
-        <v>2424</v>
+        <v>2443</v>
       </c>
       <c r="D10" t="s">
-        <v>2425</v>
+        <v>2444</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>49</v>
@@ -20933,28 +21098,63 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>2426</v>
+        <v>2445</v>
       </c>
       <c r="H10" t="s">
-        <v>2427</v>
+        <v>2446</v>
       </c>
       <c r="L10" t="s">
-        <v>2428</v>
+        <v>2447</v>
       </c>
       <c r="M10" t="s">
-        <v>2429</v>
+        <v>2448</v>
       </c>
       <c r="N10" t="s">
-        <v>2430</v>
+        <v>2449</v>
       </c>
       <c r="O10" t="s">
-        <v>2431</v>
+        <v>2450</v>
       </c>
       <c r="P10" t="s">
-        <v>2432</v>
+        <v>2451</v>
       </c>
       <c r="Q10" t="s">
-        <v>2433</v>
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="B11" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2454</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2455</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2456</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2457</v>
+      </c>
+      <c r="N11" t="s">
+        <v>2458</v>
+      </c>
+      <c r="O11" t="s">
+        <v>2459</v>
+      </c>
+      <c r="P11" t="s">
+        <v>2460</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>2461</v>
       </c>
     </row>
   </sheetData>

--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="6"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="2462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="2500">
   <si>
     <r>
       <rPr>
@@ -4794,6 +4794,9 @@
     <t>せまった</t>
   </si>
   <si>
+    <t>冒烟的</t>
+  </si>
+  <si>
     <t>春雨に煙る京都東山</t>
   </si>
   <si>
@@ -4822,6 +4825,33 @@
   </si>
   <si>
     <t>けむった</t>
+  </si>
+  <si>
+    <t>即将灭绝，消失</t>
+  </si>
+  <si>
+    <t>消えゆく</t>
+  </si>
+  <si>
+    <t>きえゆく</t>
+  </si>
+  <si>
+    <t>消えゆかない</t>
+  </si>
+  <si>
+    <t>きえゆかない</t>
+  </si>
+  <si>
+    <t>消えゆいて</t>
+  </si>
+  <si>
+    <t>きえゆいて</t>
+  </si>
+  <si>
+    <t>消えゆいた</t>
+  </si>
+  <si>
+    <t>きえゆいた</t>
   </si>
   <si>
     <t>誓う</t>
@@ -7577,6 +7607,75 @@
     <t>もちだした</t>
   </si>
   <si>
+    <t>拿起，采纳</t>
+  </si>
+  <si>
+    <t>取り上げる</t>
+  </si>
+  <si>
+    <t>とりあげる</t>
+  </si>
+  <si>
+    <t>取り上げて</t>
+  </si>
+  <si>
+    <t>とりあげて</t>
+  </si>
+  <si>
+    <t>取り上げた</t>
+  </si>
+  <si>
+    <t>とりあげた</t>
+  </si>
+  <si>
+    <t>收回，恢复</t>
+  </si>
+  <si>
+    <t>取り戻す</t>
+  </si>
+  <si>
+    <t>とりもどす</t>
+  </si>
+  <si>
+    <t>取り戻して</t>
+  </si>
+  <si>
+    <t>とりもどして</t>
+  </si>
+  <si>
+    <t>取り戻した</t>
+  </si>
+  <si>
+    <t>とりもどした</t>
+  </si>
+  <si>
+    <t>分娩，创作出，新生</t>
+  </si>
+  <si>
+    <t>卵を産む</t>
+  </si>
+  <si>
+    <t>产卵</t>
+  </si>
+  <si>
+    <t>産む</t>
+  </si>
+  <si>
+    <t>うむ</t>
+  </si>
+  <si>
+    <t>産んで</t>
+  </si>
+  <si>
+    <t>うんで</t>
+  </si>
+  <si>
+    <t>産んだ</t>
+  </si>
+  <si>
+    <t>うんだ</t>
+  </si>
+  <si>
     <t>支撑</t>
   </si>
   <si>
@@ -7794,6 +7893,21 @@
   </si>
   <si>
     <t>はさんだ</t>
+  </si>
+  <si>
+    <t>反射，反照</t>
+  </si>
+  <si>
+    <t>照り返す陽光を明かりに、</t>
+  </si>
+  <si>
+    <t>在反射的阳光下</t>
+  </si>
+  <si>
+    <t>照り返す</t>
+  </si>
+  <si>
+    <t>てりかえす</t>
   </si>
 </sst>
 </file>
@@ -13366,7 +13480,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE76"/>
+  <dimension ref="A1:AE77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -15796,6 +15910,9 @@
       </c>
     </row>
     <row r="76" ht="18" spans="1:16">
+      <c r="B76" t="s">
+        <v>1479</v>
+      </c>
       <c r="C76" s="2" t="s">
         <v>49</v>
       </c>
@@ -15803,34 +15920,69 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="F76" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="G76" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H76" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="K76" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="L76" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="M76" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="N76" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="O76" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="P76" t="s">
-        <v>1488</v>
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="77" ht="18" spans="1:16">
+      <c r="B77" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K77" t="s">
+        <v>1493</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1494</v>
+      </c>
+      <c r="M77" t="s">
+        <v>1495</v>
+      </c>
+      <c r="N77" t="s">
+        <v>1496</v>
+      </c>
+      <c r="O77" t="s">
+        <v>1497</v>
+      </c>
+      <c r="P77" t="s">
+        <v>1498</v>
       </c>
     </row>
   </sheetData>
@@ -16003,28 +16155,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="N3" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:31">
@@ -16035,28 +16187,28 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="I4" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="M4" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:31">
@@ -16067,60 +16219,60 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="E6" s="2" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:31">
@@ -16128,21 +16280,21 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -16151,15 +16303,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
       <c r="B9" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -16176,7 +16328,7 @@
     </row>
     <row r="10" ht="18" spans="1:31">
       <c r="B10" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -16185,36 +16337,36 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="M10" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="N10" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="B11" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -16223,42 +16375,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="M11" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="B12" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="D12" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -16267,33 +16419,33 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="B13" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -16302,39 +16454,39 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="B14" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -16343,22 +16495,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:31">
@@ -16370,33 +16522,33 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
       <c r="N15" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -16405,18 +16557,18 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="B17" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="E17" t="s">
         <v>222</v>
@@ -16425,30 +16577,30 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="B18" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="E18" t="s">
         <v>222</v>
@@ -16457,27 +16609,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1597</v>
+        <v>1607</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1598</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="B19" t="s">
-        <v>1599</v>
+        <v>1609</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -16486,27 +16638,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1601</v>
+        <v>1611</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="B20" t="s">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
@@ -16515,30 +16667,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="B21" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
@@ -16547,40 +16699,40 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="K21" t="s">
-        <v>1616</v>
+        <v>1626</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1617</v>
+        <v>1627</v>
       </c>
       <c r="M21" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1619</v>
+        <v>1629</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1621</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="D22" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="E22" t="s">
         <v>222</v>
@@ -16589,34 +16741,34 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" t="s">
@@ -16626,33 +16778,33 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="B24" t="s">
-        <v>1642</v>
+        <v>1652</v>
       </c>
       <c r="E24" t="s">
         <v>222</v>
@@ -16661,27 +16813,27 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1643</v>
+        <v>1653</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -16690,33 +16842,33 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="B26" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
       <c r="E26" t="s">
         <v>222</v>
@@ -16725,27 +16877,27 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="B27" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="E27" t="s">
         <v>222</v>
@@ -16754,36 +16906,36 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="I27" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1670</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="B28" t="s">
-        <v>1671</v>
+        <v>1681</v>
       </c>
       <c r="C28" t="s">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="D28" t="s">
-        <v>1673</v>
+        <v>1683</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -16792,27 +16944,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1675</v>
+        <v>1685</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1677</v>
+        <v>1687</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1678</v>
+        <v>1688</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1679</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="B29" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
@@ -16821,27 +16973,27 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1681</v>
+        <v>1691</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1682</v>
+        <v>1692</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1683</v>
+        <v>1693</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1684</v>
+        <v>1694</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1686</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="B30" t="s">
-        <v>1687</v>
+        <v>1697</v>
       </c>
       <c r="E30" t="s">
         <v>222</v>
@@ -16850,10 +17002,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
@@ -16864,33 +17016,33 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1690</v>
+        <v>1700</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1692</v>
+        <v>1702</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1693</v>
+        <v>1703</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1694</v>
+        <v>1704</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1695</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="B32" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
       <c r="C32" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="D32" t="s">
-        <v>1698</v>
+        <v>1708</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -16899,21 +17051,21 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="C33" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="D33" t="s">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="E33" t="s">
         <v>222</v>
@@ -16922,33 +17074,33 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1705</v>
+        <v>1715</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1706</v>
+        <v>1716</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1708</v>
+        <v>1718</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1709</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
       <c r="B34" t="s">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="C34" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="D34" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>815</v>
@@ -16957,30 +17109,30 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>1717</v>
+        <v>1727</v>
       </c>
       <c r="B35" t="s">
-        <v>1718</v>
+        <v>1728</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="D35" t="s">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>222</v>
@@ -16989,33 +17141,33 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1721</v>
+        <v>1731</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1722</v>
+        <v>1732</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1724</v>
+        <v>1734</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -17024,27 +17176,27 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1733</v>
+        <v>1743</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1734</v>
+        <v>1744</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1735</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
       <c r="B37" t="s">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>222</v>
@@ -17053,33 +17205,33 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1738</v>
+        <v>1748</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1741</v>
+        <v>1751</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>815</v>
@@ -17088,15 +17240,15 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>1746</v>
+        <v>1756</v>
       </c>
       <c r="H38" t="s">
-        <v>1747</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>222</v>
@@ -17105,39 +17257,39 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="H39" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="K39" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="L39" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="M39" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="N39" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="O39" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="P39" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="C40" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="D40" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>222</v>
@@ -17146,39 +17298,39 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="H40" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="K40" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="L40" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="M40" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="N40" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="O40" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="P40" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
       <c r="B41" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="C41" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="D41" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>222</v>
@@ -17187,18 +17339,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="H41" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="B42" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="C42" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="D42" t="s">
         <v>926</v>
@@ -17210,21 +17362,21 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="H42" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="K42" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="L42" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>815</v>
@@ -17233,39 +17385,39 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="H43" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="K43" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="L43" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="M43" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="N43" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="O43" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="P43" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="C44" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="D44" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -17274,34 +17426,34 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="H44" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="I44" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="J44" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="K44" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="L44" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="M44" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="N44" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="O44" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="P44" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="46" ht="16.8" spans="1:16">
@@ -17479,16 +17631,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="B3" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="D3" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -17497,31 +17649,31 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -17531,42 +17683,42 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="A4" s="2" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="B4" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="C4" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="D4" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
@@ -17575,37 +17727,37 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1827</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="C5" t="s">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="D5" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17614,65 +17766,65 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1829</v>
+        <v>1839</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1836</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1842</v>
+        <v>1852</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1843</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="C7" t="s">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="D7" t="s">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="E7" t="s">
         <v>222</v>
@@ -17681,28 +17833,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="H7" t="s">
-        <v>1848</v>
+        <v>1858</v>
       </c>
       <c r="L7" t="s">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="M7" t="s">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="N7" t="s">
-        <v>1851</v>
+        <v>1861</v>
       </c>
       <c r="O7" t="s">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="P7" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="Q7" t="s">
-        <v>1854</v>
+        <v>1864</v>
       </c>
     </row>
   </sheetData>
@@ -17728,7 +17880,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AE95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" customWidth="1"/>
@@ -17884,30 +18036,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1856</v>
+        <v>1866</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1858</v>
+        <v>1868</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
@@ -17917,16 +18069,16 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="9" t="s">
-        <v>1863</v>
+        <v>1873</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -17941,34 +18093,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1868</v>
+        <v>1878</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="7"/>
@@ -17988,7 +18140,7 @@
     </row>
     <row r="5" ht="18" spans="1:31">
       <c r="B5" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -17997,34 +18149,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="7"/>
@@ -18034,16 +18186,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="9" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -18052,13 +18204,13 @@
     </row>
     <row r="6" ht="18" spans="1:31">
       <c r="B6" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="D6" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="E6" t="s">
         <v>222</v>
@@ -18067,30 +18219,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="7"/>
@@ -18102,10 +18254,10 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="9" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -18114,13 +18266,13 @@
     </row>
     <row r="7" ht="18" spans="1:31">
       <c r="B7" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="D7" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -18129,34 +18281,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1908</v>
+        <v>1918</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1911</v>
+        <v>1921</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="7"/>
@@ -18176,7 +18328,7 @@
     </row>
     <row r="8" ht="18" spans="1:31">
       <c r="B8" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
       <c r="E8" t="s">
         <v>222</v>
@@ -18185,75 +18337,75 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:31">
@@ -18261,7 +18413,7 @@
         <v>573</v>
       </c>
       <c r="B9" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="E9" t="s">
         <v>222</v>
@@ -18270,10 +18422,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -18306,7 +18458,7 @@
     <row r="10" ht="18" spans="1:31">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="E10" t="s">
         <v>222</v>
@@ -18315,10 +18467,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -18347,7 +18499,7 @@
     <row r="11" ht="18" spans="1:31">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>815</v>
@@ -18356,37 +18508,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1938</v>
+        <v>1948</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -18399,10 +18551,10 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -18410,7 +18562,7 @@
     <row r="12" ht="18" spans="1:31">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="E12" t="s">
         <v>222</v>
@@ -18419,20 +18571,20 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -18454,10 +18606,10 @@
     </row>
     <row r="13" ht="18" spans="1:31">
       <c r="A13" s="2" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="B13" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -18466,20 +18618,20 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -18501,10 +18653,10 @@
     </row>
     <row r="14" ht="18" spans="1:31">
       <c r="A14" s="2" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="B14" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="E14" t="s">
         <v>222</v>
@@ -18513,20 +18665,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>1963</v>
+        <v>1973</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -18548,10 +18700,10 @@
     </row>
     <row r="15" ht="18" spans="1:31">
       <c r="B15" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s">
@@ -18561,39 +18713,39 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="K15" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:31">
       <c r="B16" t="s">
-        <v>1976</v>
+        <v>1986</v>
       </c>
       <c r="E16" t="s">
         <v>222</v>
@@ -18602,34 +18754,34 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1978</v>
+        <v>1988</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1986</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="17" ht="18" spans="2:16">
@@ -18640,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:16">
@@ -18651,7 +18803,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="19" ht="18" spans="2:16">
@@ -18662,10 +18814,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -18677,18 +18829,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:16">
       <c r="B21" t="s">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s">
@@ -18698,42 +18850,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="22" ht="18" spans="2:16">
       <c r="B22" s="2" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -18743,39 +18895,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="23" ht="18" spans="2:16">
       <c r="B23" t="s">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s">
@@ -18785,27 +18937,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="24" ht="18" spans="2:16">
       <c r="B24" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>222</v>
@@ -18814,39 +18966,39 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>2023</v>
+        <v>2033</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2025</v>
+        <v>2035</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="25" ht="18" spans="2:16">
       <c r="B25" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>222</v>
@@ -18855,10 +19007,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -18871,7 +19023,7 @@
     </row>
     <row r="26" ht="18" spans="2:16">
       <c r="B26" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>222</v>
@@ -18880,7 +19032,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2032</v>
+        <v>2042</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>1036</v>
@@ -18890,16 +19042,16 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="27" ht="18" spans="2:16">
@@ -18918,16 +19070,16 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="28" ht="18" spans="2:16">
@@ -18935,7 +19087,7 @@
         <v>1076</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s">
@@ -18945,34 +19097,34 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="29" ht="18" spans="2:16">
@@ -18986,27 +19138,27 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="30" ht="18" spans="2:16">
       <c r="B30" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>222</v>
@@ -19015,27 +19167,27 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="31" ht="18" spans="2:16">
       <c r="B31" t="s">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>222</v>
@@ -19044,27 +19196,27 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>2069</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="32" ht="18" spans="2:16">
       <c r="B32" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>222</v>
@@ -19079,21 +19231,21 @@
         <v>439</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:16">
       <c r="B33" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>222</v>
@@ -19102,22 +19254,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:16">
@@ -19127,30 +19279,30 @@
     </row>
     <row r="35" ht="18" spans="1:16">
       <c r="B35" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:16">
       <c r="B36" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>222</v>
@@ -19159,10 +19311,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:16">
@@ -19173,30 +19325,30 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:16">
       <c r="B38" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>222</v>
@@ -19205,30 +19357,30 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="M38" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>2104</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:16">
       <c r="B39" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
@@ -19238,18 +19390,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:16">
       <c r="B40" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
@@ -19259,22 +19411,22 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:16">
@@ -19287,15 +19439,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:16">
       <c r="B42" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>222</v>
@@ -19304,54 +19456,54 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>2114</v>
+        <v>2124</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2116</v>
+        <v>2126</v>
       </c>
       <c r="N42" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2118</v>
+        <v>2128</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:16">
       <c r="B43" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="N43" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:16">
       <c r="B44" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>222</v>
@@ -19360,30 +19512,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>2125</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>2115</v>
-      </c>
       <c r="M44" s="2" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
       <c r="N44" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:16">
       <c r="B45" t="s">
-        <v>2128</v>
+        <v>2138</v>
       </c>
       <c r="C45" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>222</v>
@@ -19392,7 +19544,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>316</v>
@@ -19400,10 +19552,10 @@
     </row>
     <row r="46" ht="18" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="B46" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>222</v>
@@ -19412,24 +19564,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="B47" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="D47" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>222</v>
@@ -19438,33 +19590,33 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="M47" t="s">
-        <v>2141</v>
+        <v>2151</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:16">
       <c r="B48" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>222</v>
@@ -19473,10 +19625,10 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:16">
@@ -19484,7 +19636,7 @@
         <v>1146</v>
       </c>
       <c r="B49" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>222</v>
@@ -19493,28 +19645,28 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>2153</v>
+        <v>2163</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>2155</v>
+        <v>2165</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>222</v>
@@ -19523,30 +19675,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>2160</v>
+        <v>2170</v>
       </c>
       <c r="B51" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>222</v>
@@ -19555,34 +19707,34 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2162</v>
+        <v>2172</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>2164</v>
+        <v>2174</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>2166</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="D52" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>222</v>
@@ -19591,24 +19743,24 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="B53" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
       <c r="C53" t="s">
-        <v>2172</v>
+        <v>2182</v>
       </c>
       <c r="D53" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>222</v>
@@ -19617,18 +19769,18 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>2176</v>
+        <v>2186</v>
       </c>
       <c r="B54" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>222</v>
@@ -19637,36 +19789,36 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2178</v>
+        <v>2188</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="B55" t="s">
-        <v>2180</v>
+        <v>2190</v>
       </c>
       <c r="C55" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
       <c r="D55" t="s">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>222</v>
@@ -19675,19 +19827,19 @@
         <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2184</v>
+        <v>2194</v>
       </c>
       <c r="P55" s="2"/>
     </row>
     <row r="56" ht="18" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="B56" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>222</v>
@@ -19696,36 +19848,36 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>2188</v>
+        <v>2198</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="B57" t="s">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="D57" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>222</v>
@@ -19734,36 +19886,36 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="B58" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="D58" t="s">
-        <v>2203</v>
+        <v>2213</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>222</v>
@@ -19772,36 +19924,36 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2206</v>
+        <v>2216</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>2208</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>222</v>
@@ -19810,10 +19962,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -19822,16 +19974,16 @@
     </row>
     <row r="60" ht="18" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="B60" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="D60" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>222</v>
@@ -19840,10 +19992,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -19852,16 +20004,16 @@
     </row>
     <row r="61" ht="18" spans="1:16">
       <c r="A61" s="2" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="B61" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>222</v>
@@ -19870,27 +20022,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:16">
       <c r="B62" s="15" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>222</v>
@@ -19899,10 +20051,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="63" ht="18" spans="1:16">
@@ -19914,24 +20066,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="64" ht="18" spans="1:16">
       <c r="A64" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="B64" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="D64" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>222</v>
@@ -19940,10 +20092,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="65" ht="18" spans="2:16">
@@ -19954,15 +20106,15 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="66" ht="18" spans="2:16">
       <c r="B66" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>222</v>
@@ -19971,15 +20123,15 @@
         <v>2</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="67" ht="18" spans="2:16">
       <c r="B67" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>222</v>
@@ -19988,15 +20140,15 @@
         <v>2</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" ht="18" spans="2:16">
       <c r="B68" s="8" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>222</v>
@@ -20005,15 +20157,15 @@
         <v>2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="69" ht="18" spans="2:16">
       <c r="B69" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>222</v>
@@ -20022,15 +20174,15 @@
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="70" ht="18" spans="2:16">
       <c r="B70" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>222</v>
@@ -20039,27 +20191,27 @@
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="71" ht="18" spans="2:16">
       <c r="B71" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>222</v>
@@ -20068,27 +20220,27 @@
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="72" ht="18" spans="2:16">
       <c r="B72" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="E72" t="s">
         <v>222</v>
@@ -20097,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>502</v>
@@ -20105,7 +20257,7 @@
     </row>
     <row r="73" ht="18" spans="2:16">
       <c r="B73" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -20114,33 +20266,33 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>502</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="N73" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="O73" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="74" ht="18" spans="2:16">
       <c r="B74" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="C74" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="D74" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="E74" t="s">
         <v>222</v>
@@ -20149,33 +20301,33 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="N74" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="O74" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="75" ht="18" spans="2:16">
       <c r="B75" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>2276</v>
+        <v>2286</v>
       </c>
       <c r="D75" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="E75" t="s">
         <v>222</v>
@@ -20187,29 +20339,29 @@
         <v>737</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2278</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="76" ht="18" spans="2:16">
       <c r="B76" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2280</v>
+        <v>2290</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="77" ht="18" spans="2:16">
       <c r="B77" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="E77" t="s">
         <v>222</v>
@@ -20218,27 +20370,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>2284</v>
+        <v>2294</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>2286</v>
+        <v>2296</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="78" ht="18" spans="2:16">
       <c r="B78" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="E78" t="s">
         <v>222</v>
@@ -20247,15 +20399,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="79" ht="18" spans="2:16">
       <c r="B79" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -20264,27 +20416,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
       <c r="N79" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="O79" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="80" ht="18" spans="2:16">
       <c r="B80" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="E80" t="s">
         <v>222</v>
@@ -20293,33 +20445,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="N80" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="O80" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="P80" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="81" ht="18" spans="1:16">
       <c r="B81" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="D81" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="E81" t="s">
         <v>222</v>
@@ -20328,33 +20480,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="82" ht="18" spans="1:16">
       <c r="B82" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="D82" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="E82" t="s">
         <v>222</v>
@@ -20363,30 +20515,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="83" ht="18" spans="1:16">
       <c r="A83" s="2" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="B83" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="E83" t="s">
         <v>222</v>
@@ -20395,33 +20547,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>2329</v>
+        <v>2339</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="84" ht="18" spans="1:16">
       <c r="B84" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="C84" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="D84" t="s">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="E84" t="s">
         <v>222</v>
@@ -20430,33 +20582,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2336</v>
+        <v>2346</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>2338</v>
+        <v>2348</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>2340</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="85" ht="18" spans="1:16">
       <c r="B85" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>2342</v>
+        <v>2352</v>
       </c>
       <c r="E85" t="s">
         <v>222</v>
@@ -20465,27 +20617,27 @@
         <v>2</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>2345</v>
+        <v>2355</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="86" ht="18" spans="1:16">
       <c r="B86" t="s">
-        <v>2347</v>
+        <v>2357</v>
       </c>
       <c r="E86" t="s">
         <v>222</v>
@@ -20494,30 +20646,30 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>2352</v>
+        <v>2362</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="87" ht="18" spans="1:16">
       <c r="A87" t="s">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="B87" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="E87" t="s">
         <v>222</v>
@@ -20526,24 +20678,24 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>2358</v>
+        <v>2368</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
       <c r="B88" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="E88" t="s">
         <v>222</v>
@@ -20552,32 +20704,32 @@
         <v>2</v>
       </c>
       <c r="G88" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="H88" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
       <c r="M88" t="s">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="N88" t="s">
-        <v>2364</v>
+        <v>2374</v>
       </c>
       <c r="O88" t="s">
-        <v>2365</v>
+        <v>2375</v>
       </c>
       <c r="P88" t="s">
-        <v>2366</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="1:16">
       <c r="G89" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="90" ht="18" spans="1:16">
       <c r="B90" t="s">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="E90" t="s">
         <v>222</v>
@@ -20586,21 +20738,21 @@
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="M90" t="s">
-        <v>2371</v>
+        <v>2381</v>
       </c>
       <c r="N90" t="s">
-        <v>2372</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="B91" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="E91" t="s">
         <v>222</v>
@@ -20609,33 +20761,33 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>2374</v>
+        <v>2384</v>
       </c>
       <c r="H91" t="s">
-        <v>2375</v>
+        <v>2385</v>
       </c>
       <c r="M91" t="s">
-        <v>2376</v>
+        <v>2386</v>
       </c>
       <c r="N91" t="s">
-        <v>2377</v>
+        <v>2387</v>
       </c>
       <c r="O91" t="s">
-        <v>2378</v>
+        <v>2388</v>
       </c>
       <c r="P91" t="s">
-        <v>2379</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="B92" t="s">
-        <v>2380</v>
+        <v>2390</v>
       </c>
       <c r="C92" t="s">
-        <v>2381</v>
+        <v>2391</v>
       </c>
       <c r="D92" t="s">
-        <v>2382</v>
+        <v>2392</v>
       </c>
       <c r="E92" t="s">
         <v>222</v>
@@ -20644,22 +20796,115 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>2383</v>
+        <v>2393</v>
       </c>
       <c r="H92" t="s">
-        <v>2384</v>
+        <v>2394</v>
       </c>
       <c r="M92" t="s">
-        <v>2385</v>
+        <v>2395</v>
       </c>
       <c r="N92" t="s">
-        <v>2386</v>
+        <v>2396</v>
       </c>
       <c r="O92" t="s">
-        <v>2387</v>
+        <v>2397</v>
       </c>
       <c r="P92" t="s">
-        <v>2388</v>
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="B93" t="s">
+        <v>2399</v>
+      </c>
+      <c r="E93" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>2400</v>
+      </c>
+      <c r="H93" t="s">
+        <v>2401</v>
+      </c>
+      <c r="M93" t="s">
+        <v>2402</v>
+      </c>
+      <c r="N93" t="s">
+        <v>2403</v>
+      </c>
+      <c r="O93" t="s">
+        <v>2404</v>
+      </c>
+      <c r="P93" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="B94" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E94" t="s">
+        <v>222</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H94" t="s">
+        <v>2408</v>
+      </c>
+      <c r="M94" t="s">
+        <v>2409</v>
+      </c>
+      <c r="N94" t="s">
+        <v>2410</v>
+      </c>
+      <c r="O94" t="s">
+        <v>2411</v>
+      </c>
+      <c r="P94" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="B95" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E95" t="s">
+        <v>222</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H95" t="s">
+        <v>2417</v>
+      </c>
+      <c r="M95" t="s">
+        <v>2418</v>
+      </c>
+      <c r="N95" t="s">
+        <v>2419</v>
+      </c>
+      <c r="O95" t="s">
+        <v>2420</v>
+      </c>
+      <c r="P95" t="s">
+        <v>2421</v>
       </c>
     </row>
   </sheetData>
@@ -20685,7 +20930,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
@@ -20850,16 +21095,16 @@
     </row>
     <row r="3" ht="18" spans="1:32">
       <c r="A3" s="2" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="B3" t="s">
-        <v>2389</v>
+        <v>2422</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2390</v>
+        <v>2423</v>
       </c>
       <c r="D3" t="s">
-        <v>2391</v>
+        <v>2424</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -20868,42 +21113,42 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2392</v>
+        <v>2425</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>2393</v>
+        <v>2426</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2394</v>
+        <v>2427</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>2395</v>
+        <v>2428</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2396</v>
+        <v>2429</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>2397</v>
+        <v>2430</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>2398</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:32">
       <c r="B4" t="s">
-        <v>2399</v>
+        <v>2432</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2400</v>
+        <v>2433</v>
       </c>
       <c r="D4" t="s">
-        <v>2401</v>
+        <v>2434</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -20912,21 +21157,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2402</v>
+        <v>2435</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2403</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:32">
       <c r="B5" t="s">
-        <v>2404</v>
+        <v>2437</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2405</v>
+        <v>2438</v>
       </c>
       <c r="D5" t="s">
-        <v>2406</v>
+        <v>2439</v>
       </c>
       <c r="E5" t="s">
         <v>222</v>
@@ -20935,33 +21180,33 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>2407</v>
+        <v>2440</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2408</v>
+        <v>2441</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2409</v>
+        <v>2442</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2410</v>
+        <v>2443</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2411</v>
+        <v>2444</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2412</v>
+        <v>2445</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2413</v>
+        <v>2446</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>2414</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:32">
       <c r="B6" t="s">
-        <v>2415</v>
+        <v>2448</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -20970,33 +21215,33 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>2416</v>
+        <v>2449</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2417</v>
+        <v>2450</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2418</v>
+        <v>2451</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2419</v>
+        <v>2452</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2420</v>
+        <v>2453</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2421</v>
+        <v>2454</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2422</v>
+        <v>2455</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>2423</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" t="s">
-        <v>2424</v>
+        <v>2457</v>
       </c>
       <c r="E7" t="s">
         <v>815</v>
@@ -21005,21 +21250,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>2425</v>
+        <v>2458</v>
       </c>
       <c r="H7" t="s">
-        <v>2426</v>
+        <v>2459</v>
       </c>
       <c r="L7" t="s">
-        <v>2427</v>
+        <v>2460</v>
       </c>
       <c r="M7" t="s">
-        <v>2428</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" t="s">
-        <v>2424</v>
+        <v>2457</v>
       </c>
       <c r="E8" t="s">
         <v>815</v>
@@ -21028,27 +21273,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2429</v>
+        <v>2462</v>
       </c>
       <c r="H8" t="s">
-        <v>2426</v>
+        <v>2459</v>
       </c>
       <c r="L8" t="s">
-        <v>2430</v>
+        <v>2463</v>
       </c>
       <c r="M8" t="s">
-        <v>2428</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:32">
       <c r="B9" t="s">
-        <v>2431</v>
+        <v>2464</v>
       </c>
       <c r="C9" t="s">
-        <v>2432</v>
+        <v>2465</v>
       </c>
       <c r="D9" t="s">
-        <v>2433</v>
+        <v>2466</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -21057,39 +21302,39 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>2434</v>
+        <v>2467</v>
       </c>
       <c r="H9" t="s">
-        <v>2435</v>
+        <v>2468</v>
       </c>
       <c r="L9" t="s">
-        <v>2436</v>
+        <v>2469</v>
       </c>
       <c r="M9" t="s">
-        <v>2437</v>
+        <v>2470</v>
       </c>
       <c r="N9" t="s">
-        <v>2438</v>
+        <v>2471</v>
       </c>
       <c r="O9" t="s">
-        <v>2439</v>
+        <v>2472</v>
       </c>
       <c r="P9" t="s">
-        <v>2440</v>
+        <v>2473</v>
       </c>
       <c r="Q9" t="s">
-        <v>2441</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:32">
       <c r="B10" t="s">
-        <v>2442</v>
+        <v>2475</v>
       </c>
       <c r="C10" t="s">
-        <v>2443</v>
+        <v>2476</v>
       </c>
       <c r="D10" t="s">
-        <v>2444</v>
+        <v>2477</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>49</v>
@@ -21098,33 +21343,33 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>2445</v>
+        <v>2478</v>
       </c>
       <c r="H10" t="s">
-        <v>2446</v>
+        <v>2479</v>
       </c>
       <c r="L10" t="s">
-        <v>2447</v>
+        <v>2480</v>
       </c>
       <c r="M10" t="s">
-        <v>2448</v>
+        <v>2481</v>
       </c>
       <c r="N10" t="s">
-        <v>2449</v>
+        <v>2482</v>
       </c>
       <c r="O10" t="s">
-        <v>2450</v>
+        <v>2483</v>
       </c>
       <c r="P10" t="s">
-        <v>2451</v>
+        <v>2484</v>
       </c>
       <c r="Q10" t="s">
-        <v>2452</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="11" spans="1:32">
       <c r="B11" t="s">
-        <v>2453</v>
+        <v>2486</v>
       </c>
       <c r="E11" t="s">
         <v>222</v>
@@ -21133,28 +21378,51 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>2454</v>
+        <v>2487</v>
       </c>
       <c r="H11" t="s">
-        <v>2455</v>
+        <v>2488</v>
       </c>
       <c r="L11" t="s">
-        <v>2456</v>
+        <v>2489</v>
       </c>
       <c r="M11" t="s">
-        <v>2457</v>
+        <v>2490</v>
       </c>
       <c r="N11" t="s">
-        <v>2458</v>
+        <v>2491</v>
       </c>
       <c r="O11" t="s">
-        <v>2459</v>
+        <v>2492</v>
       </c>
       <c r="P11" t="s">
-        <v>2460</v>
+        <v>2493</v>
       </c>
       <c r="Q11" t="s">
-        <v>2461</v>
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="B12" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E12" t="s">
+        <v>222</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2498</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>
